--- a/Engine_Map.xlsx
+++ b/Engine_Map.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>3771 lines, 158 functions and classes, 65 sections</t>
+          <t>3785 lines, 158 functions and classes, 65 sections</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>823-827</t>
+          <t>832-836</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
@@ -2407,15 +2407,15 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>829-834</t>
+          <t>838-844</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>The environment a Docling process runs in: its folder first on the path, ahead of the runtime's packages.</t>
+          <t>The environment a Docling process runs in: its folder first on the path, ahead of the runtime's packages, and</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>836-847</t>
+          <t>846-857</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>849-859</t>
+          <t>859-869</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>861-883</t>
+          <t>871-893</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>885-909</t>
+          <t>895-919</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>911-921</t>
+          <t>921-931</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>923-928</t>
+          <t>933-938</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>932-951</t>
+          <t>942-961</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>953-954</t>
+          <t>963-964</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>956-999</t>
+          <t>966-1009</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1002-1004</t>
+          <t>1012-1014</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1006-1020</t>
+          <t>1016-1030</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1023-1025</t>
+          <t>1033-1035</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>1027-1029</t>
+          <t>1037-1039</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>1037-1038</t>
+          <t>1047-1048</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>1043-1046</t>
+          <t>1053-1056</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>1048-1069</t>
+          <t>1058-1079</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>1071-1083</t>
+          <t>1081-1093</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>1085-1105</t>
+          <t>1095-1115</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>1107-1112</t>
+          <t>1117-1122</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>1114-1123</t>
+          <t>1124-1133</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>1126-1130</t>
+          <t>1136-1140</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>1138-1144</t>
+          <t>1148-1154</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>1154-1169</t>
+          <t>1164-1179</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1171-1174</t>
+          <t>1181-1184</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1176-1185</t>
+          <t>1186-1195</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>1187-1213</t>
+          <t>1197-1223</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1215-1238</t>
+          <t>1225-1248</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>1240-1244</t>
+          <t>1250-1254</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1251-1334</t>
+          <t>1261-1344</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>1337-1339</t>
+          <t>1347-1349</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>1341-1345</t>
+          <t>1351-1355</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>1347-1352</t>
+          <t>1357-1362</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1364-1369</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>1361-1367</t>
+          <t>1371-1377</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>1369-1393</t>
+          <t>1379-1403</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1395-1416</t>
+          <t>1405-1426</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>1418-1443</t>
+          <t>1428-1453</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>1455-1458</t>
+          <t>1465-1468</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1461-1469</t>
+          <t>1471-1479</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1471-1486</t>
+          <t>1481-1496</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>1488-1522</t>
+          <t>1498-1532</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>1524-1542</t>
+          <t>1534-1552</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>1545-1557</t>
+          <t>1555-1567</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>1559-1596</t>
+          <t>1569-1606</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>1598-1621</t>
+          <t>1608-1631</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>1623-1642</t>
+          <t>1633-1652</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>1647-1657</t>
+          <t>1657-1667</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>1659-1681</t>
+          <t>1669-1691</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>1683-1736</t>
+          <t>1693-1746</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>1739-1745</t>
+          <t>1749-1755</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>1747-1763</t>
+          <t>1757-1773</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>1765-1794</t>
+          <t>1775-1804</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>1796-1801</t>
+          <t>1806-1811</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>1804-1834</t>
+          <t>1814-1844</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>1839-1844</t>
+          <t>1849-1854</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>1846-1848</t>
+          <t>1856-1858</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>1851-1885</t>
+          <t>1861-1895</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>1887-1908</t>
+          <t>1897-1918</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>1910-1929</t>
+          <t>1920-1939</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>1931-1948</t>
+          <t>1941-1958</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>1951-2026</t>
+          <t>1961-2036</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>2065-2090</t>
+          <t>2075-2100</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>2092-2114</t>
+          <t>2102-2124</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>2116-2473</t>
+          <t>2126-2483</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>2476-2481</t>
+          <t>2486-2491</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>2483-2498</t>
+          <t>2493-2508</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>2501-2529</t>
+          <t>2511-2539</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>2572-2573</t>
+          <t>2582-2583</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>2593-2602</t>
+          <t>2603-2612</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>2610-2616</t>
+          <t>2620-2626</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>2618-2623</t>
+          <t>2628-2633</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>2625-2642</t>
+          <t>2635-2652</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>2644-2651</t>
+          <t>2654-2661</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>2653-2679</t>
+          <t>2663-2689</t>
         </is>
       </c>
       <c r="F111" s="3" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>2681-2701</t>
+          <t>2691-2711</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>2705-2737</t>
+          <t>2715-2747</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>2744-2754</t>
+          <t>2754-2764</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>2757-2863</t>
+          <t>2767-2873</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>2865-2867</t>
+          <t>2875-2877</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>2871-2877</t>
+          <t>2881-2887</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>2888-2907</t>
+          <t>2898-2917</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>2909-2914</t>
+          <t>2919-2924</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>2917-2936</t>
+          <t>2927-2946</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>2938-2960</t>
+          <t>2948-2970</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>2962-2971</t>
+          <t>2972-2981</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>2973-2980</t>
+          <t>2983-2990</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>2982-2985</t>
+          <t>2992-2995</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>2991-2996</t>
+          <t>3001-3006</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>2998-3008</t>
+          <t>3008-3018</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>3010-3039</t>
+          <t>3020-3049</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>3041-3049</t>
+          <t>3051-3059</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>3058-3076</t>
+          <t>3068-3086</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>3079-3082</t>
+          <t>3089-3092</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>3084-3107</t>
+          <t>3094-3117</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>3117-3240</t>
+          <t>3127-3250</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>3242-3247</t>
+          <t>3252-3257</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>3250-3253</t>
+          <t>3260-3263</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>3256-3259</t>
+          <t>3266-3269</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>3262-3268</t>
+          <t>3272-3278</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>3270-3279</t>
+          <t>3280-3289</t>
         </is>
       </c>
       <c r="F137" s="3" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>3335-3337</t>
+          <t>3345-3347</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>3339-3384</t>
+          <t>3349-3394</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>3386-3402</t>
+          <t>3396-3412</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>3405-3408</t>
+          <t>3415-3418</t>
         </is>
       </c>
       <c r="F141" s="3" t="n">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>3411-3418</t>
+          <t>3421-3428</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>3420-3441</t>
+          <t>3430-3451</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>3444-3461</t>
+          <t>3454-3471</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>3463-3504</t>
+          <t>3473-3514</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>3506-3522</t>
+          <t>3516-3532</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>3524-3527</t>
+          <t>3534-3537</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>3529-3531</t>
+          <t>3539-3541</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>3556-3565</t>
+          <t>3566-3575</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>3567-3572</t>
+          <t>3577-3582</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
@@ -8060,11 +8060,11 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>3574-3628</t>
+          <t>3584-3640</t>
         </is>
       </c>
       <c r="F151" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>3630-3632</t>
+          <t>3642-3644</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
@@ -8154,11 +8154,11 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>3634-3644</t>
+          <t>3646-3657</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -8201,15 +8201,15 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>3646-3693</t>
+          <t>3659-3707</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>Install what the engine needs from the index named in widget 06, the runtime's own packages pinned</t>
+          <t>Install what the engine needs - from a staged folder of wheels when there is one, else from the index named in</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>3695-3698</t>
+          <t>3709-3712</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>3700-3720</t>
+          <t>3714-3734</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>3722-3735</t>
+          <t>3736-3749</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>3737-3758</t>
+          <t>3751-3772</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>3760-3770</t>
+          <t>3774-3784</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>3010-3039</t>
+          <t>3020-3049</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>2998-3008</t>
+          <t>3008-3018</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>3405-3408</t>
+          <t>3415-3418</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>2991-2996</t>
+          <t>3001-3006</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>3041-3049</t>
+          <t>3051-3059</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>3524-3527</t>
+          <t>3534-3537</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>3506-3522</t>
+          <t>3516-3532</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>1027-1029</t>
+          <t>1037-1039</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>885-909</t>
+          <t>895-919</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>861-883</t>
+          <t>871-893</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
@@ -10141,15 +10141,15 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>829-834</t>
+          <t>838-844</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>The environment a Docling process runs in: its folder first on the path, ahead of the runtime's packages.</t>
+          <t>The environment a Docling process runs in: its folder first on the path, ahead of the runtime's packages, and</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>836-847</t>
+          <t>846-857</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
@@ -10279,15 +10279,15 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>829-834</t>
+          <t>838-844</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>The environment a Docling process runs in: its folder first on the path, ahead of the runtime's packages.</t>
+          <t>The environment a Docling process runs in: its folder first on the path, ahead of the runtime's packages, and</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr"/>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>823-827</t>
+          <t>832-836</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>953-954</t>
+          <t>963-964</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>1006-1020</t>
+          <t>1016-1030</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>1002-1004</t>
+          <t>1012-1014</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>911-921</t>
+          <t>921-931</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>923-928</t>
+          <t>933-938</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>932-951</t>
+          <t>942-961</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>956-999</t>
+          <t>966-1009</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>932-951</t>
+          <t>942-961</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>953-954</t>
+          <t>963-964</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>1023-1025</t>
+          <t>1033-1035</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>885-909</t>
+          <t>895-919</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>1951-2026</t>
+          <t>1961-2036</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>1804-1834</t>
+          <t>1814-1844</t>
         </is>
       </c>
       <c r="P56" s="3" t="n">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>1347-1352</t>
+          <t>1357-1362</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>1418-1443</t>
+          <t>1428-1453</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1364-1369</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>1347-1352</t>
+          <t>1357-1362</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>1341-1345</t>
+          <t>1351-1355</t>
         </is>
       </c>
       <c r="P61" s="3" t="n">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>1851-1885</t>
+          <t>1861-1895</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>1765-1794</t>
+          <t>1775-1804</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>1037-1038</t>
+          <t>1047-1048</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>1747-1763</t>
+          <t>1757-1773</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P67" s="3" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>1739-1745</t>
+          <t>1749-1755</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>1683-1736</t>
+          <t>1693-1746</t>
         </is>
       </c>
       <c r="P69" s="3" t="n">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>1659-1681</t>
+          <t>1669-1691</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>1796-1801</t>
+          <t>1806-1811</t>
         </is>
       </c>
       <c r="P72" s="3" t="n">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>1747-1763</t>
+          <t>1757-1773</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P75" s="3" t="n">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>1647-1657</t>
+          <t>1657-1667</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>1037-1038</t>
+          <t>1047-1048</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>1598-1621</t>
+          <t>1608-1631</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>1545-1557</t>
+          <t>1555-1567</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>1839-1844</t>
+          <t>1849-1854</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>1846-1848</t>
+          <t>1856-1858</t>
         </is>
       </c>
       <c r="P85" s="3" t="n">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>3737-3758</t>
+          <t>3751-3772</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>3695-3698</t>
+          <t>3709-3712</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>2593-2602</t>
+          <t>2603-2612</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>3722-3735</t>
+          <t>3736-3749</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>2681-2701</t>
+          <t>2691-2711</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>2610-2616</t>
+          <t>2620-2626</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>953-954</t>
+          <t>963-964</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>2644-2651</t>
+          <t>2654-2661</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>2653-2679</t>
+          <t>2663-2689</t>
         </is>
       </c>
       <c r="P94" s="3" t="n">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>2625-2642</t>
+          <t>2635-2652</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>2618-2623</t>
+          <t>2628-2633</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>2625-2642</t>
+          <t>2635-2652</t>
         </is>
       </c>
       <c r="P98" s="3" t="n">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>2871-2877</t>
+          <t>2881-2887</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>2757-2863</t>
+          <t>2767-2873</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>2744-2754</t>
+          <t>2754-2764</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>2865-2867</t>
+          <t>2875-2877</t>
         </is>
       </c>
       <c r="P105" s="3" t="n">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>2917-2936</t>
+          <t>2927-2946</t>
         </is>
       </c>
       <c r="P108" s="3" t="n">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>2888-2907</t>
+          <t>2898-2917</t>
         </is>
       </c>
       <c r="P109" s="3" t="n">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>2871-2877</t>
+          <t>2881-2887</t>
         </is>
       </c>
       <c r="P110" s="3" t="n">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>3420-3441</t>
+          <t>3430-3451</t>
         </is>
       </c>
       <c r="P111" s="3" t="n">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>3386-3402</t>
+          <t>3396-3412</t>
         </is>
       </c>
       <c r="P112" s="3" t="n">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>3270-3279</t>
+          <t>3280-3289</t>
         </is>
       </c>
       <c r="P114" s="3" t="n">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>2572-2573</t>
+          <t>2582-2583</t>
         </is>
       </c>
       <c r="P115" s="3" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>3737-3758</t>
+          <t>3751-3772</t>
         </is>
       </c>
       <c r="P116" s="3" t="n">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>3737-3758</t>
+          <t>3751-3772</t>
         </is>
       </c>
       <c r="P117" s="3" t="n">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>3335-3337</t>
+          <t>3345-3347</t>
         </is>
       </c>
       <c r="P118" s="3" t="n">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>953-954</t>
+          <t>963-964</t>
         </is>
       </c>
       <c r="P119" s="3" t="n">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
-          <t>3079-3082</t>
+          <t>3089-3092</t>
         </is>
       </c>
       <c r="P120" s="3" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>3262-3268</t>
+          <t>3272-3278</t>
         </is>
       </c>
       <c r="P121" s="3" t="n">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>3117-3240</t>
+          <t>3127-3250</t>
         </is>
       </c>
       <c r="P122" s="3" t="n">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>3242-3247</t>
+          <t>3252-3257</t>
         </is>
       </c>
       <c r="P123" s="3" t="n">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>2501-2529</t>
+          <t>2511-2539</t>
         </is>
       </c>
       <c r="P124" s="3" t="n">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>1647-1657</t>
+          <t>1657-1667</t>
         </is>
       </c>
       <c r="P125" s="3" t="n">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>3250-3253</t>
+          <t>3260-3263</t>
         </is>
       </c>
       <c r="P126" s="3" t="n">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>3256-3259</t>
+          <t>3266-3269</t>
         </is>
       </c>
       <c r="P127" s="3" t="n">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>3084-3107</t>
+          <t>3094-3117</t>
         </is>
       </c>
       <c r="P128" s="3" t="n">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>3079-3082</t>
+          <t>3089-3092</t>
         </is>
       </c>
       <c r="P130" s="3" t="n">
@@ -17921,7 +17921,7 @@
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>3339-3384</t>
+          <t>3349-3394</t>
         </is>
       </c>
       <c r="P132" s="3" t="n">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>3058-3076</t>
+          <t>3068-3086</t>
         </is>
       </c>
       <c r="P133" s="3" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>2982-2985</t>
+          <t>2992-2995</t>
         </is>
       </c>
       <c r="P135" s="3" t="n">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>2744-2754</t>
+          <t>2754-2764</t>
         </is>
       </c>
       <c r="P139" s="3" t="n">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>3405-3408</t>
+          <t>3415-3418</t>
         </is>
       </c>
       <c r="P140" s="3" t="n">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>953-954</t>
+          <t>963-964</t>
         </is>
       </c>
       <c r="P141" s="3" t="n">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>2982-2985</t>
+          <t>2992-2995</t>
         </is>
       </c>
       <c r="P142" s="3" t="n">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>3411-3418</t>
+          <t>3421-3428</t>
         </is>
       </c>
       <c r="P143" s="3" t="n">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>2909-2914</t>
+          <t>2919-2924</t>
         </is>
       </c>
       <c r="P144" s="3" t="n">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>2938-2960</t>
+          <t>2948-2970</t>
         </is>
       </c>
       <c r="P145" s="3" t="n">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>3420-3441</t>
+          <t>3430-3451</t>
         </is>
       </c>
       <c r="P152" s="3" t="n">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="O153" s="3" t="inlineStr">
         <is>
-          <t>2973-2980</t>
+          <t>2983-2990</t>
         </is>
       </c>
       <c r="P153" s="3" t="n">
@@ -19667,7 +19667,7 @@
       </c>
       <c r="O154" s="3" t="inlineStr">
         <is>
-          <t>2962-2971</t>
+          <t>2972-2981</t>
         </is>
       </c>
       <c r="P154" s="3" t="n">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="O155" s="3" t="inlineStr">
         <is>
-          <t>3737-3758</t>
+          <t>3751-3772</t>
         </is>
       </c>
       <c r="P155" s="3" t="n">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="O156" s="3" t="inlineStr">
         <is>
-          <t>1488-1522</t>
+          <t>1498-1532</t>
         </is>
       </c>
       <c r="P156" s="3" t="n">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P157" s="3" t="n">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="O158" s="3" t="inlineStr">
         <is>
-          <t>1240-1244</t>
+          <t>1250-1254</t>
         </is>
       </c>
       <c r="P158" s="3" t="n">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="O159" s="3" t="inlineStr">
         <is>
-          <t>1215-1238</t>
+          <t>1225-1248</t>
         </is>
       </c>
       <c r="P159" s="3" t="n">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="O160" s="3" t="inlineStr">
         <is>
-          <t>1154-1169</t>
+          <t>1164-1179</t>
         </is>
       </c>
       <c r="P160" s="3" t="n">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="O161" s="3" t="inlineStr">
         <is>
-          <t>1171-1174</t>
+          <t>1181-1184</t>
         </is>
       </c>
       <c r="P161" s="3" t="n">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="O162" s="3" t="inlineStr">
         <is>
-          <t>2065-2090</t>
+          <t>2075-2100</t>
         </is>
       </c>
       <c r="P162" s="3" t="n">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="O163" s="3" t="inlineStr">
         <is>
-          <t>3405-3408</t>
+          <t>3415-3418</t>
         </is>
       </c>
       <c r="P163" s="3" t="n">
@@ -20417,7 +20417,7 @@
       </c>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>2092-2114</t>
+          <t>2102-2124</t>
         </is>
       </c>
       <c r="P164" s="3" t="n">
@@ -20502,7 +20502,7 @@
       </c>
       <c r="O165" s="3" t="inlineStr">
         <is>
-          <t>1154-1169</t>
+          <t>1164-1179</t>
         </is>
       </c>
       <c r="P165" s="3" t="n">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="O166" s="3" t="inlineStr">
         <is>
-          <t>3737-3758</t>
+          <t>3751-3772</t>
         </is>
       </c>
       <c r="P166" s="3" t="n">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="O167" s="3" t="inlineStr">
         <is>
-          <t>1176-1185</t>
+          <t>1186-1195</t>
         </is>
       </c>
       <c r="P167" s="3" t="n">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="O168" s="3" t="inlineStr">
         <is>
-          <t>1251-1334</t>
+          <t>1261-1344</t>
         </is>
       </c>
       <c r="P168" s="3" t="n">
@@ -20830,7 +20830,7 @@
       </c>
       <c r="O169" s="3" t="inlineStr">
         <is>
-          <t>1138-1144</t>
+          <t>1148-1154</t>
         </is>
       </c>
       <c r="P169" s="3" t="n">
@@ -20911,7 +20911,7 @@
       </c>
       <c r="O170" s="3" t="inlineStr">
         <is>
-          <t>1337-1339</t>
+          <t>1347-1349</t>
         </is>
       </c>
       <c r="P170" s="3" t="n">
@@ -21000,7 +21000,7 @@
       </c>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>1138-1144</t>
+          <t>1148-1154</t>
         </is>
       </c>
       <c r="P171" s="3" t="n">
@@ -21069,7 +21069,7 @@
       </c>
       <c r="O172" s="3" t="inlineStr">
         <is>
-          <t>1559-1596</t>
+          <t>1569-1606</t>
         </is>
       </c>
       <c r="P172" s="3" t="n">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="O173" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1364-1369</t>
         </is>
       </c>
       <c r="P173" s="3" t="n">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="O174" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P174" s="3" t="n">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>1524-1542</t>
+          <t>1534-1552</t>
         </is>
       </c>
       <c r="P175" s="3" t="n">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="O176" s="3" t="inlineStr">
         <is>
-          <t>1471-1486</t>
+          <t>1481-1496</t>
         </is>
       </c>
       <c r="P176" s="3" t="n">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="O177" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1364-1369</t>
         </is>
       </c>
       <c r="P177" s="3" t="n">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="O178" s="3" t="inlineStr">
         <is>
-          <t>1347-1352</t>
+          <t>1357-1362</t>
         </is>
       </c>
       <c r="P178" s="3" t="n">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="O179" s="3" t="inlineStr">
         <is>
-          <t>1455-1458</t>
+          <t>1465-1468</t>
         </is>
       </c>
       <c r="P179" s="3" t="n">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="O180" s="3" t="inlineStr">
         <is>
-          <t>1418-1443</t>
+          <t>1428-1453</t>
         </is>
       </c>
       <c r="P180" s="3" t="n">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P181" s="3" t="n">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="O182" s="3" t="inlineStr">
         <is>
-          <t>1461-1469</t>
+          <t>1471-1479</t>
         </is>
       </c>
       <c r="P182" s="3" t="n">
@@ -21872,7 +21872,7 @@
       </c>
       <c r="O183" s="3" t="inlineStr">
         <is>
-          <t>1455-1458</t>
+          <t>1465-1468</t>
         </is>
       </c>
       <c r="P183" s="3" t="n">
@@ -21953,7 +21953,7 @@
       </c>
       <c r="O184" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P184" s="3" t="n">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="O185" s="3" t="inlineStr">
         <is>
-          <t>1126-1130</t>
+          <t>1136-1140</t>
         </is>
       </c>
       <c r="P185" s="3" t="n">
@@ -22103,7 +22103,7 @@
       </c>
       <c r="O186" s="3" t="inlineStr">
         <is>
-          <t>1369-1393</t>
+          <t>1379-1403</t>
         </is>
       </c>
       <c r="P186" s="3" t="n">
@@ -22172,7 +22172,7 @@
       </c>
       <c r="O187" s="3" t="inlineStr">
         <is>
-          <t>1395-1416</t>
+          <t>1405-1426</t>
         </is>
       </c>
       <c r="P187" s="3" t="n">
@@ -22249,7 +22249,7 @@
       </c>
       <c r="O188" s="3" t="inlineStr">
         <is>
-          <t>1347-1352</t>
+          <t>1357-1362</t>
         </is>
       </c>
       <c r="P188" s="3" t="n">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="O189" s="3" t="inlineStr">
         <is>
-          <t>1361-1367</t>
+          <t>1371-1377</t>
         </is>
       </c>
       <c r="P189" s="3" t="n">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="O192" s="3" t="inlineStr">
         <is>
-          <t>1341-1345</t>
+          <t>1351-1355</t>
         </is>
       </c>
       <c r="P192" s="3" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="O193" s="3" t="inlineStr">
         <is>
-          <t>1176-1185</t>
+          <t>1186-1195</t>
         </is>
       </c>
       <c r="P193" s="3" t="n">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="O194" s="3" t="inlineStr">
         <is>
-          <t>1623-1642</t>
+          <t>1633-1652</t>
         </is>
       </c>
       <c r="P194" s="3" t="n">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="O195" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P195" s="3" t="n">
@@ -22845,7 +22845,7 @@
       </c>
       <c r="O196" s="3" t="inlineStr">
         <is>
-          <t>1488-1522</t>
+          <t>1498-1532</t>
         </is>
       </c>
       <c r="P196" s="3" t="n">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="O197" s="3" t="inlineStr">
         <is>
-          <t>1910-1929</t>
+          <t>1920-1939</t>
         </is>
       </c>
       <c r="P197" s="3" t="n">
@@ -23507,7 +23507,7 @@
       </c>
       <c r="O206" s="3" t="inlineStr">
         <is>
-          <t>3405-3408</t>
+          <t>3415-3418</t>
         </is>
       </c>
       <c r="P206" s="3" t="n">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="O210" s="3" t="inlineStr">
         <is>
-          <t>1447-1453</t>
+          <t>1457-1463</t>
         </is>
       </c>
       <c r="P210" s="3" t="n">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="O211" s="3" t="inlineStr">
         <is>
-          <t>3405-3408</t>
+          <t>3415-3418</t>
         </is>
       </c>
       <c r="P211" s="3" t="n">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="O213" s="3" t="inlineStr">
         <is>
-          <t>1187-1213</t>
+          <t>1197-1223</t>
         </is>
       </c>
       <c r="P213" s="3" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="O215" s="3" t="inlineStr">
         <is>
-          <t>1154-1169</t>
+          <t>1164-1179</t>
         </is>
       </c>
       <c r="P215" s="3" t="n">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="O216" s="3" t="inlineStr">
         <is>
-          <t>1171-1174</t>
+          <t>1181-1184</t>
         </is>
       </c>
       <c r="P216" s="3" t="n">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="O217" s="3" t="inlineStr">
         <is>
-          <t>2065-2090</t>
+          <t>2075-2100</t>
         </is>
       </c>
       <c r="P217" s="3" t="n">
@@ -24295,7 +24295,7 @@
       </c>
       <c r="O218" s="3" t="inlineStr">
         <is>
-          <t>1240-1244</t>
+          <t>1250-1254</t>
         </is>
       </c>
       <c r="P218" s="3" t="n">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="O219" s="3" t="inlineStr">
         <is>
-          <t>1176-1185</t>
+          <t>1186-1195</t>
         </is>
       </c>
       <c r="P219" s="3" t="n">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="O220" s="3" t="inlineStr">
         <is>
-          <t>1043-1046</t>
+          <t>1053-1056</t>
         </is>
       </c>
       <c r="P220" s="3" t="n">
@@ -24486,7 +24486,7 @@
       </c>
       <c r="O221" s="3" t="inlineStr">
         <is>
-          <t>1846-1848</t>
+          <t>1856-1858</t>
         </is>
       </c>
       <c r="P221" s="3" t="n">
@@ -24547,7 +24547,7 @@
       </c>
       <c r="O222" s="3" t="inlineStr">
         <is>
-          <t>1887-1908</t>
+          <t>1897-1918</t>
         </is>
       </c>
       <c r="P222" s="3" t="n">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="O223" s="3" t="inlineStr">
         <is>
-          <t>1071-1083</t>
+          <t>1081-1093</t>
         </is>
       </c>
       <c r="P223" s="3" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="O224" s="3" t="inlineStr">
         <is>
-          <t>1931-1948</t>
+          <t>1941-1958</t>
         </is>
       </c>
       <c r="P224" s="3" t="n">
@@ -24718,7 +24718,7 @@
       </c>
       <c r="O225" s="3" t="inlineStr">
         <is>
-          <t>1114-1123</t>
+          <t>1124-1133</t>
         </is>
       </c>
       <c r="P225" s="3" t="n">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="O228" s="3" t="inlineStr">
         <is>
-          <t>1107-1112</t>
+          <t>1117-1122</t>
         </is>
       </c>
       <c r="P228" s="3" t="n">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="O231" s="3" t="inlineStr">
         <is>
-          <t>1085-1105</t>
+          <t>1095-1115</t>
         </is>
       </c>
       <c r="P231" s="3" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="O232" s="3" t="inlineStr">
         <is>
-          <t>1048-1069</t>
+          <t>1058-1079</t>
         </is>
       </c>
       <c r="P232" s="3" t="n">
@@ -25186,7 +25186,7 @@
       </c>
       <c r="O233" s="3" t="inlineStr">
         <is>
-          <t>3529-3531</t>
+          <t>3539-3541</t>
         </is>
       </c>
       <c r="P233" s="3" t="n">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="O234" s="3" t="inlineStr">
         <is>
-          <t>2483-2498</t>
+          <t>2493-2508</t>
         </is>
       </c>
       <c r="P234" s="3" t="n">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="O235" s="3" t="inlineStr">
         <is>
-          <t>2116-2473</t>
+          <t>2126-2483</t>
         </is>
       </c>
       <c r="P235" s="3" t="n">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="O236" s="3" t="inlineStr">
         <is>
-          <t>1138-1144</t>
+          <t>1148-1154</t>
         </is>
       </c>
       <c r="P236" s="3" t="n">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="O237" s="3" t="inlineStr">
         <is>
-          <t>1347-1352</t>
+          <t>1357-1362</t>
         </is>
       </c>
       <c r="P237" s="3" t="n">
@@ -25499,7 +25499,7 @@
       </c>
       <c r="O238" s="3" t="inlineStr">
         <is>
-          <t>2092-2114</t>
+          <t>2102-2124</t>
         </is>
       </c>
       <c r="P238" s="3" t="n">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="O239" s="3" t="inlineStr">
         <is>
-          <t>2065-2090</t>
+          <t>2075-2100</t>
         </is>
       </c>
       <c r="P239" s="3" t="n">
@@ -25637,7 +25637,7 @@
       </c>
       <c r="O240" s="3" t="inlineStr">
         <is>
-          <t>1240-1244</t>
+          <t>1250-1254</t>
         </is>
       </c>
       <c r="P240" s="3" t="n">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="O241" s="3" t="inlineStr">
         <is>
-          <t>1215-1238</t>
+          <t>1225-1248</t>
         </is>
       </c>
       <c r="P241" s="3" t="n">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="O242" s="3" t="inlineStr">
         <is>
-          <t>2476-2481</t>
+          <t>2486-2491</t>
         </is>
       </c>
       <c r="P242" s="3" t="n">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O244" s="3" t="inlineStr">
         <is>
-          <t>2065-2090</t>
+          <t>2075-2100</t>
         </is>
       </c>
       <c r="P244" s="3" t="n">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="O245" s="3" t="inlineStr">
         <is>
-          <t>3386-3402</t>
+          <t>3396-3412</t>
         </is>
       </c>
       <c r="P245" s="3" t="n">
@@ -26007,7 +26007,7 @@
       </c>
       <c r="O246" s="3" t="inlineStr">
         <is>
-          <t>2917-2936</t>
+          <t>2927-2946</t>
         </is>
       </c>
       <c r="P246" s="3" t="n">
@@ -26064,11 +26064,11 @@
       </c>
       <c r="O247" s="3" t="inlineStr">
         <is>
-          <t>3574-3628</t>
+          <t>3584-3640</t>
         </is>
       </c>
       <c r="P247" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q247" s="3" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="O248" s="3" t="inlineStr">
         <is>
-          <t>823-827</t>
+          <t>832-836</t>
         </is>
       </c>
       <c r="P248" s="3" t="n">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="O249" s="3" t="inlineStr">
         <is>
-          <t>849-859</t>
+          <t>859-869</t>
         </is>
       </c>
       <c r="P249" s="3" t="n">
@@ -26243,7 +26243,7 @@
       </c>
       <c r="O250" s="3" t="inlineStr">
         <is>
-          <t>823-827</t>
+          <t>832-836</t>
         </is>
       </c>
       <c r="P250" s="3" t="n">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="O251" s="3" t="inlineStr">
         <is>
-          <t>3630-3632</t>
+          <t>3642-3644</t>
         </is>
       </c>
       <c r="P251" s="3" t="n">
@@ -26365,15 +26365,15 @@
       </c>
       <c r="O252" s="3" t="inlineStr">
         <is>
-          <t>3646-3693</t>
+          <t>3659-3707</t>
         </is>
       </c>
       <c r="P252" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q252" s="3" t="inlineStr">
         <is>
-          <t>Install what the engine needs from the index named in widget 06, the runtime's own packages pinned</t>
+          <t>Install what the engine needs - from a staged folder of wheels when there is one, else from the index named in</t>
         </is>
       </c>
       <c r="R252" s="3" t="inlineStr">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="O253" s="3" t="inlineStr">
         <is>
-          <t>3630-3632</t>
+          <t>3642-3644</t>
         </is>
       </c>
       <c r="P253" s="3" t="n">
@@ -26495,11 +26495,11 @@
       </c>
       <c r="O254" s="3" t="inlineStr">
         <is>
-          <t>3634-3644</t>
+          <t>3646-3657</t>
         </is>
       </c>
       <c r="P254" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q254" s="3" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
       </c>
       <c r="O255" s="3" t="inlineStr">
         <is>
-          <t>836-847</t>
+          <t>846-857</t>
         </is>
       </c>
       <c r="P255" s="3" t="n">
@@ -26609,7 +26609,7 @@
       </c>
       <c r="O256" s="3" t="inlineStr">
         <is>
-          <t>2065-2090</t>
+          <t>2075-2100</t>
         </is>
       </c>
       <c r="P256" s="3" t="n">
@@ -26670,15 +26670,15 @@
       </c>
       <c r="O257" s="3" t="inlineStr">
         <is>
-          <t>3646-3693</t>
+          <t>3659-3707</t>
         </is>
       </c>
       <c r="P257" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q257" s="3" t="inlineStr">
         <is>
-          <t>Install what the engine needs from the index named in widget 06, the runtime's own packages pinned</t>
+          <t>Install what the engine needs - from a staged folder of wheels when there is one, else from the index named in</t>
         </is>
       </c>
       <c r="R257" s="3" t="inlineStr">
@@ -26731,7 +26731,7 @@
       </c>
       <c r="O258" s="3" t="inlineStr">
         <is>
-          <t>3556-3565</t>
+          <t>3566-3575</t>
         </is>
       </c>
       <c r="P258" s="3" t="n">
@@ -26792,7 +26792,7 @@
       </c>
       <c r="O259" s="3" t="inlineStr">
         <is>
-          <t>2705-2737</t>
+          <t>2715-2747</t>
         </is>
       </c>
       <c r="P259" s="3" t="n">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="O260" s="3" t="inlineStr">
         <is>
-          <t>3556-3565</t>
+          <t>3566-3575</t>
         </is>
       </c>
       <c r="P260" s="3" t="n">
@@ -26918,7 +26918,7 @@
       </c>
       <c r="O261" s="3" t="inlineStr">
         <is>
-          <t>3567-3572</t>
+          <t>3577-3582</t>
         </is>
       </c>
       <c r="P261" s="3" t="n">
@@ -26971,11 +26971,11 @@
       </c>
       <c r="O262" s="3" t="inlineStr">
         <is>
-          <t>3634-3644</t>
+          <t>3646-3657</t>
         </is>
       </c>
       <c r="P262" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q262" s="3" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
       </c>
       <c r="O263" s="3" t="inlineStr">
         <is>
-          <t>3737-3758</t>
+          <t>3751-3772</t>
         </is>
       </c>
       <c r="P263" s="3" t="n">
@@ -27085,7 +27085,7 @@
       </c>
       <c r="O264" s="3" t="inlineStr">
         <is>
-          <t>3700-3720</t>
+          <t>3714-3734</t>
         </is>
       </c>
       <c r="P264" s="3" t="n">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="O265" s="3" t="inlineStr">
         <is>
-          <t>2625-2642</t>
+          <t>2635-2652</t>
         </is>
       </c>
       <c r="P265" s="3" t="n">
@@ -27199,7 +27199,7 @@
       </c>
       <c r="O266" s="3" t="inlineStr">
         <is>
-          <t>3737-3758</t>
+          <t>3751-3772</t>
         </is>
       </c>
       <c r="P266" s="3" t="n">
@@ -27256,7 +27256,7 @@
       </c>
       <c r="O267" s="3" t="inlineStr">
         <is>
-          <t>3760-3770</t>
+          <t>3774-3784</t>
         </is>
       </c>
       <c r="P267" s="3" t="n">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="O268" s="3" t="inlineStr">
         <is>
-          <t>2705-2737</t>
+          <t>2715-2747</t>
         </is>
       </c>
       <c r="P268" s="3" t="n">
@@ -27374,7 +27374,7 @@
       </c>
       <c r="O269" s="3" t="inlineStr">
         <is>
-          <t>3556-3565</t>
+          <t>3566-3575</t>
         </is>
       </c>
       <c r="P269" s="3" t="n">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="O270" s="3" t="inlineStr">
         <is>
-          <t>3695-3698</t>
+          <t>3709-3712</t>
         </is>
       </c>
       <c r="P270" s="3" t="n">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="O271" s="3" t="inlineStr">
         <is>
-          <t>3463-3504</t>
+          <t>3473-3514</t>
         </is>
       </c>
       <c r="P271" s="3" t="n">
@@ -27557,7 +27557,7 @@
       </c>
       <c r="O272" s="3" t="inlineStr">
         <is>
-          <t>2757-2863</t>
+          <t>2767-2873</t>
         </is>
       </c>
       <c r="P272" s="3" t="n">
@@ -27752,7 +27752,7 @@
       </c>
       <c r="O275" s="3" t="inlineStr">
         <is>
-          <t>3444-3461</t>
+          <t>3454-3471</t>
         </is>
       </c>
       <c r="P275" s="3" t="n">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="O276" s="3" t="inlineStr">
         <is>
-          <t>2998-3008</t>
+          <t>3008-3018</t>
         </is>
       </c>
       <c r="P276" s="3" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="O277" s="3" t="inlineStr">
         <is>
-          <t>3405-3408</t>
+          <t>3415-3418</t>
         </is>
       </c>
       <c r="P277" s="3" t="n">
@@ -28004,7 +28004,7 @@
       </c>
       <c r="O279" s="3" t="inlineStr">
         <is>
-          <t>3556-3565</t>
+          <t>3566-3575</t>
         </is>
       </c>
       <c r="P279" s="3" t="n">
@@ -28069,7 +28069,7 @@
       </c>
       <c r="O280" s="3" t="inlineStr">
         <is>
-          <t>1027-1029</t>
+          <t>1037-1039</t>
         </is>
       </c>
       <c r="P280" s="3" t="n">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="O281" s="3" t="inlineStr">
         <is>
-          <t>1023-1025</t>
+          <t>1033-1035</t>
         </is>
       </c>
       <c r="P281" s="3" t="n">
@@ -28199,7 +28199,7 @@
       </c>
       <c r="O282" s="3" t="inlineStr">
         <is>
-          <t>1951-2026</t>
+          <t>1961-2036</t>
         </is>
       </c>
       <c r="P282" s="3" t="n">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="O283" s="3" t="inlineStr">
         <is>
-          <t>3079-3082</t>
+          <t>3089-3092</t>
         </is>
       </c>
       <c r="P283" s="3" t="n">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="O285" s="3" t="inlineStr">
         <is>
-          <t>3556-3565</t>
+          <t>3566-3575</t>
         </is>
       </c>
       <c r="P285" s="3" t="n">
@@ -29308,7 +29308,7 @@
         <v>780</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>15</v>
@@ -29326,7 +29326,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>1033</v>
+        <v>1043</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>7</v>
@@ -29347,7 +29347,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>92</v>
@@ -29368,7 +29368,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1132</v>
+        <v>1142</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>4</v>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>13</v>
@@ -29406,7 +29406,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1149</v>
+        <v>1159</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>297</v>
@@ -29427,7 +29427,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>1446</v>
+        <v>1456</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>98</v>
@@ -29448,7 +29448,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>100</v>
@@ -29469,7 +29469,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>1644</v>
+        <v>1654</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>159</v>
@@ -29490,7 +29490,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>33</v>
@@ -29511,7 +29511,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>1836</v>
+        <v>1846</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>192</v>
@@ -29532,7 +29532,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>2028</v>
+        <v>2038</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>23</v>
@@ -29549,7 +29549,7 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>2051</v>
+        <v>2061</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>484</v>
@@ -29570,7 +29570,7 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>2535</v>
+        <v>2545</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>2</v>
@@ -29587,7 +29587,7 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>2537</v>
+        <v>2547</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>6</v>
@@ -29604,7 +29604,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2543</v>
+        <v>2553</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>8</v>
@@ -29621,7 +29621,7 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>2551</v>
+        <v>2561</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>3</v>
@@ -29638,7 +29638,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>2554</v>
+        <v>2564</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>9</v>
@@ -29655,7 +29655,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>2563</v>
+        <v>2573</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>4</v>
@@ -29672,7 +29672,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>2567</v>
+        <v>2577</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>4</v>
@@ -29689,7 +29689,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>2571</v>
+        <v>2581</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>5</v>
@@ -29710,7 +29710,7 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2576</v>
+        <v>2586</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>4</v>
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>2580</v>
+        <v>2590</v>
       </c>
       <c r="C55" s="3" t="n">
         <v>24</v>
@@ -29748,7 +29748,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>2604</v>
+        <v>2614</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>99</v>
@@ -29769,7 +29769,7 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>2703</v>
+        <v>2713</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>36</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>2739</v>
+        <v>2749</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>140</v>
@@ -29811,7 +29811,7 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>2879</v>
+        <v>2889</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>8</v>
@@ -29828,7 +29828,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>2887</v>
+        <v>2897</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>100</v>
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>2987</v>
+        <v>2997</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>64</v>
@@ -29870,7 +29870,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>3051</v>
+        <v>3061</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>230</v>
@@ -29891,7 +29891,7 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>3281</v>
+        <v>3291</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>123</v>
@@ -29912,7 +29912,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>3404</v>
+        <v>3414</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>39</v>
@@ -29933,7 +29933,7 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>3443</v>
+        <v>3453</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>100</v>
@@ -29954,10 +29954,10 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>3543</v>
+        <v>3553</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>11</v>

--- a/Engine_Map.xlsx
+++ b/Engine_Map.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Engine_Info'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Functions'!$A$1:$K$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Function_Map'!$A$1:$S$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Function_Map'!$A$1:$S$284</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sections'!$A$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Records'!$A$1:$C$10</definedName>
   </definedNames>
@@ -531,7 +531,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>3785 lines, 158 functions and classes, 65 sections</t>
+          <t>3782 lines, 158 functions and classes, 65 sections</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>F-0067</t>
+          <t>F-0068</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2144,7 +2144,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>F-0045</t>
+          <t>F-0046</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2336,7 +2336,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>F-0047</t>
+          <t>F-0048</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2387,7 +2387,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>F-0046</t>
+          <t>F-0047</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2434,7 +2434,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>F-0050</t>
+          <t>F-0051</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>F-0048</t>
+          <t>F-0049</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2505,20 +2505,20 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>859-869</t>
+          <t>859-866</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Install Docling into its own folder - never into the runtime's packages - from the index(es) of widget 06, or</t>
+          <t>Install Docling from PyPI into its own folder - never into the runtime's packages. Returns what pip said when</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>docling_folder; index_arguments; install</t>
+          <t>docling_folder; install</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -2536,7 +2536,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>F-0049</t>
+          <t>F-0050</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>871-893</t>
+          <t>868-890</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>895-919</t>
+          <t>892-916</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
@@ -2638,7 +2638,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>F-0051</t>
+          <t>F-0052</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>921-931</t>
+          <t>918-928</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
@@ -2685,7 +2685,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>F-0069</t>
+          <t>F-0070</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>933-938</t>
+          <t>930-935</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
@@ -2732,7 +2732,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>F-0070</t>
+          <t>F-0071</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>942-961</t>
+          <t>939-958</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>963-964</t>
+          <t>960-961</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
@@ -2826,7 +2826,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>F-0071</t>
+          <t>F-0072</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>966-1009</t>
+          <t>963-1006</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1012-1014</t>
+          <t>1009-1011</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1016-1030</t>
+          <t>1013-1027</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1033-1035</t>
+          <t>1030-1032</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>1037-1039</t>
+          <t>1034-1036</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>1047-1048</t>
+          <t>1044-1045</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>1053-1056</t>
+          <t>1050-1053</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>1058-1079</t>
+          <t>1055-1076</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>1081-1093</t>
+          <t>1078-1090</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>1095-1115</t>
+          <t>1092-1112</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>1117-1122</t>
+          <t>1114-1119</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>1124-1133</t>
+          <t>1121-1130</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>1136-1140</t>
+          <t>1133-1137</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>1148-1154</t>
+          <t>1145-1151</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
@@ -3504,7 +3504,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>F-0059</t>
+          <t>F-0060</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>1164-1179</t>
+          <t>1161-1176</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
@@ -3551,7 +3551,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>F-0060</t>
+          <t>F-0061</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1181-1184</t>
+          <t>1178-1181</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1186-1195</t>
+          <t>1183-1192</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
@@ -3649,7 +3649,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>F-0062</t>
+          <t>F-0063</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>1197-1223</t>
+          <t>1194-1220</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1225-1248</t>
+          <t>1222-1245</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>1250-1254</t>
+          <t>1247-1251</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
@@ -3802,7 +3802,7 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>F-0061</t>
+          <t>F-0062</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1261-1344</t>
+          <t>1258-1341</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>1347-1349</t>
+          <t>1344-1346</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>1351-1355</t>
+          <t>1348-1352</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>1357-1362</t>
+          <t>1354-1359</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>1364-1369</t>
+          <t>1361-1366</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>1371-1377</t>
+          <t>1368-1374</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>1379-1403</t>
+          <t>1376-1400</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
@@ -4143,7 +4143,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>F-0066</t>
+          <t>F-0067</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1405-1426</t>
+          <t>1402-1423</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>1428-1453</t>
+          <t>1425-1450</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
@@ -4245,7 +4245,7 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>1465-1468</t>
+          <t>1462-1465</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
@@ -4343,7 +4343,7 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>F-0065</t>
+          <t>F-0066</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1471-1479</t>
+          <t>1468-1476</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1481-1496</t>
+          <t>1478-1493</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>1498-1532</t>
+          <t>1495-1529</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>1534-1552</t>
+          <t>1531-1549</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>1555-1567</t>
+          <t>1552-1564</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>1569-1606</t>
+          <t>1566-1603</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
@@ -4641,7 +4641,7 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>F-0068</t>
+          <t>F-0069</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>1608-1631</t>
+          <t>1605-1628</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>1633-1652</t>
+          <t>1630-1649</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
@@ -4743,7 +4743,7 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>F-0054</t>
+          <t>F-0055</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>1657-1667</t>
+          <t>1654-1664</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>1669-1691</t>
+          <t>1666-1688</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>1693-1746</t>
+          <t>1690-1743</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>1749-1755</t>
+          <t>1746-1752</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>1757-1773</t>
+          <t>1754-1770</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
@@ -4994,7 +4994,7 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>F-0044</t>
+          <t>F-0045</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>1775-1804</t>
+          <t>1772-1801</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>1806-1811</t>
+          <t>1803-1808</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>1814-1844</t>
+          <t>1811-1841</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>1849-1854</t>
+          <t>1846-1851</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>1856-1858</t>
+          <t>1853-1855</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
@@ -5241,7 +5241,7 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>F-0056</t>
+          <t>F-0057</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>1861-1895</t>
+          <t>1858-1892</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>1897-1918</t>
+          <t>1894-1915</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
@@ -5339,7 +5339,7 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>F-0057</t>
+          <t>F-0058</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>1920-1939</t>
+          <t>1917-1936</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>1941-1958</t>
+          <t>1938-1955</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>1961-2036</t>
+          <t>1958-2033</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
@@ -5488,7 +5488,7 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>F-0064</t>
+          <t>F-0065</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>2075-2100</t>
+          <t>2072-2097</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
@@ -5539,7 +5539,7 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>F-0063</t>
+          <t>F-0064</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>2102-2124</t>
+          <t>2099-2121</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>2126-2483</t>
+          <t>2123-2480</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>2486-2491</t>
+          <t>2483-2488</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>2493-2508</t>
+          <t>2490-2505</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
@@ -5739,7 +5739,7 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>F-0043</t>
+          <t>F-0044</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>2511-2539</t>
+          <t>2508-2536</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>2582-2583</t>
+          <t>2579-2580</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>2603-2612</t>
+          <t>2600-2609</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>2620-2626</t>
+          <t>2617-2623</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>2628-2633</t>
+          <t>2625-2630</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>2635-2652</t>
+          <t>2632-2649</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>2654-2661</t>
+          <t>2651-2658</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>2663-2689</t>
+          <t>2660-2686</t>
         </is>
       </c>
       <c r="F111" s="3" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>2691-2711</t>
+          <t>2688-2708</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>2715-2747</t>
+          <t>2712-2744</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>2754-2764</t>
+          <t>2751-2761</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>2767-2873</t>
+          <t>2764-2870</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>2875-2877</t>
+          <t>2872-2874</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>2881-2887</t>
+          <t>2878-2884</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>2898-2917</t>
+          <t>2895-2914</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>2919-2924</t>
+          <t>2916-2921</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>2927-2946</t>
+          <t>2924-2943</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>2948-2970</t>
+          <t>2945-2967</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>2972-2981</t>
+          <t>2969-2978</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>2983-2990</t>
+          <t>2980-2987</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>2992-2995</t>
+          <t>2989-2992</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
@@ -6762,7 +6762,7 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>F-0058</t>
+          <t>F-0059</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>3001-3006</t>
+          <t>2998-3003</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
@@ -6813,7 +6813,7 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>F-0053</t>
+          <t>F-0054</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>3008-3018</t>
+          <t>3005-3015</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>3020-3049</t>
+          <t>3017-3046</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>3051-3059</t>
+          <t>3048-3056</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>3068-3086</t>
+          <t>3065-3083</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>3089-3092</t>
+          <t>3086-3089</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>3094-3117</t>
+          <t>3091-3114</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
@@ -7107,7 +7107,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>F-0072</t>
+          <t>F-0073</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>3127-3250</t>
+          <t>3124-3247</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>3252-3257</t>
+          <t>3249-3254</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>3260-3263</t>
+          <t>3257-3260</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>3266-3269</t>
+          <t>3263-3266</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>3272-3278</t>
+          <t>3269-3275</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>3280-3289</t>
+          <t>3277-3286</t>
         </is>
       </c>
       <c r="F137" s="3" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>3345-3347</t>
+          <t>3342-3344</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>3349-3394</t>
+          <t>3346-3391</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>3396-3412</t>
+          <t>3393-3409</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
@@ -7550,7 +7550,7 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>F-0055</t>
+          <t>F-0056</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>3415-3418</t>
+          <t>3412-3415</t>
         </is>
       </c>
       <c r="F141" s="3" t="n">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>3421-3428</t>
+          <t>3418-3425</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>3430-3451</t>
+          <t>3427-3448</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>3454-3471</t>
+          <t>3451-3468</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>3473-3514</t>
+          <t>3470-3511</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>3516-3532</t>
+          <t>3513-3529</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>3534-3537</t>
+          <t>3531-3534</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>3539-3541</t>
+          <t>3536-3538</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
@@ -7942,12 +7942,12 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>F-0083</t>
+          <t>F-0043</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>databricks_user</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -7962,30 +7962,26 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>3566-3575</t>
+          <t>3562-3576</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>The endpoint, token or user id, read from the widgets at the moment chat() calls: a token pasted</t>
-        </is>
-      </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>LiveValues</t>
-        </is>
-      </c>
+          <t>Who runs the notebook, as Databricks knows them: the notebook context's user name; on a cluster that keeps</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr"/>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>LiveValues; setup; verify; verify_evidence_pack</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>Cell 1 sets up; Cell 4 verifies the pack; chat() reads the widgets</t>
+          <t>Cell 1 sets up</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr"/>
@@ -7993,12 +7989,12 @@
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>F-0095</t>
+          <t>F-0083</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>notebook_folder</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -8013,26 +8009,30 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>3577-3582</t>
+          <t>3578-3587</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>(no description)</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="inlineStr"/>
+          <t>The endpoint and token, read from the widgets at the moment chat() calls - a token pasted into widget 02</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>LiveValues</t>
+        </is>
+      </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>LiveValues; setup; verify; verify_evidence_pack</t>
         </is>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>Cell 1 sets up</t>
+          <t>Cell 1 sets up; Cell 4 verifies the pack; chat() reads the widgets</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr"/>
@@ -8040,43 +8040,43 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>F-0133</t>
+          <t>F-0095</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
+          <t>notebook_folder</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>the notebook: four cells, each one call</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>3589-3594</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>(no description)</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr"/>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
           <t>setup</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>the notebook: four cells, each one call</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>3584-3640</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>Cell 1: the widgets, the packages the engine needs (installed only if one is missing), flowR, and</t>
-        </is>
-      </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>docling_folder; docling_install; docling_ready; flowr_ready; install; live; notebook_folder; pip_said; review</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr"/>
       <c r="J151" s="3" t="inlineStr">
         <is>
           <t>Cell 1 sets up</t>
@@ -8087,12 +8087,12 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>F-0073</t>
+          <t>F-0133</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>index_arguments</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -8107,23 +8107,23 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>3642-3644</t>
+          <t>3596-3649</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>pip's arguments for the index(es) of widget 06: the first URL is the index, any further one an extra index.</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr"/>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>docling_install; install</t>
-        </is>
-      </c>
+          <t>Cell 1: the widgets, the packages the engine needs (installed only if one is missing), flowR, and</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>databricks_user; docling_folder; docling_install; docling_ready; flowr_ready; install; live; notebook_folder; pip_said; review</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr"/>
       <c r="J152" s="3" t="inlineStr">
         <is>
           <t>Cell 1 sets up</t>
@@ -8154,11 +8154,11 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>3646-3657</t>
+          <t>3652-3661</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -8201,20 +8201,20 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>3659-3707</t>
+          <t>3663-3705</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>Install what the engine needs - from a staged folder of wheels when there is one, else from the index named in</t>
+          <t>Install what the engine needs from PyPI, the runtime's own packages pinned as they are, and restart Python</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>index_arguments; pip_said</t>
+          <t>pip_said</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -8252,11 +8252,11 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>3709-3712</t>
+          <t>3707-3708</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -8303,11 +8303,11 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>3714-3734</t>
+          <t>3710-3731</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>3736-3749</t>
+          <t>3733-3746</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>3751-3772</t>
+          <t>3748-3769</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>3774-3784</t>
+          <t>3771-3781</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -8515,7 +8515,7 @@
     <hyperlink ref="A35" location="'Function_Map'!A27"/>
     <hyperlink ref="A36" location="'Function_Map'!A24"/>
     <hyperlink ref="A37" location="'Function_Map'!A25"/>
-    <hyperlink ref="A38" location="'Function_Map'!A249"/>
+    <hyperlink ref="A38" location="'Function_Map'!A250"/>
     <hyperlink ref="A39" location="'Function_Map'!A23"/>
     <hyperlink ref="A40" location="'Function_Map'!A16"/>
     <hyperlink ref="A41" location="'Function_Map'!A32"/>
@@ -8590,7 +8590,7 @@
     <hyperlink ref="A110" location="'Function_Map'!A93"/>
     <hyperlink ref="A111" location="'Function_Map'!A94"/>
     <hyperlink ref="A112" location="'Function_Map'!A90"/>
-    <hyperlink ref="A113" location="'Function_Map'!A259"/>
+    <hyperlink ref="A113" location="'Function_Map'!A258"/>
     <hyperlink ref="A114" location="'Function_Map'!A104"/>
     <hyperlink ref="A115" location="'Function_Map'!A100"/>
     <hyperlink ref="A116" location="'Function_Map'!A105"/>
@@ -8621,22 +8621,22 @@
     <hyperlink ref="A141" location="'Function_Map'!A5"/>
     <hyperlink ref="A142" location="'Function_Map'!A143"/>
     <hyperlink ref="A143" location="'Function_Map'!A111"/>
-    <hyperlink ref="A144" location="'Function_Map'!A275"/>
-    <hyperlink ref="A145" location="'Function_Map'!A271"/>
+    <hyperlink ref="A144" location="'Function_Map'!A274"/>
+    <hyperlink ref="A145" location="'Function_Map'!A270"/>
     <hyperlink ref="A146" location="'Function_Map'!A12"/>
     <hyperlink ref="A147" location="'Function_Map'!A11"/>
     <hyperlink ref="A148" location="'Function_Map'!A233"/>
-    <hyperlink ref="A149" location="'Function_Map'!A258"/>
-    <hyperlink ref="A150" location="'Function_Map'!A261"/>
-    <hyperlink ref="A151" location="'Function_Map'!A247"/>
-    <hyperlink ref="A152" location="'Function_Map'!A251"/>
-    <hyperlink ref="A153" location="'Function_Map'!A254"/>
+    <hyperlink ref="A149" location="'Function_Map'!A248"/>
+    <hyperlink ref="A150" location="'Function_Map'!A257"/>
+    <hyperlink ref="A151" location="'Function_Map'!A260"/>
+    <hyperlink ref="A152" location="'Function_Map'!A247"/>
+    <hyperlink ref="A153" location="'Function_Map'!A253"/>
     <hyperlink ref="A154" location="'Function_Map'!A252"/>
     <hyperlink ref="A155" location="'Function_Map'!A87"/>
-    <hyperlink ref="A156" location="'Function_Map'!A264"/>
+    <hyperlink ref="A156" location="'Function_Map'!A263"/>
     <hyperlink ref="A157" location="'Function_Map'!A89"/>
     <hyperlink ref="A158" location="'Function_Map'!A86"/>
-    <hyperlink ref="A159" location="'Function_Map'!A267"/>
+    <hyperlink ref="A159" location="'Function_Map'!A266"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8648,7 +8648,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S285"/>
+  <dimension ref="A1:S284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="7" customWidth="1" min="1" max="10"/>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>3020-3049</t>
+          <t>3017-3046</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>F-0053</t>
+          <t>F-0054</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>3008-3018</t>
+          <t>3005-3015</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>F-0055</t>
+          <t>F-0056</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>3415-3418</t>
+          <t>3412-3415</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>F-0058</t>
+          <t>F-0059</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>3001-3006</t>
+          <t>2998-3003</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>3051-3059</t>
+          <t>3048-3056</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>3534-3537</t>
+          <t>3531-3534</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>3516-3532</t>
+          <t>3513-3529</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>1037-1039</t>
+          <t>1034-1036</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>895-919</t>
+          <t>892-916</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>F-0049</t>
+          <t>F-0050</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>871-893</t>
+          <t>868-890</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>F-0046</t>
+          <t>F-0047</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>F-0050</t>
+          <t>F-0051</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>F-0046</t>
+          <t>F-0047</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>F-0047</t>
+          <t>F-0048</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>963-964</t>
+          <t>960-961</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>1016-1030</t>
+          <t>1013-1027</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>1012-1014</t>
+          <t>1009-1011</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>F-0045</t>
+          <t>F-0046</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>F-0051</t>
+          <t>F-0052</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>921-931</t>
+          <t>918-928</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>F-0069</t>
+          <t>F-0070</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>933-938</t>
+          <t>930-935</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>F-0070</t>
+          <t>F-0071</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>942-961</t>
+          <t>939-958</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>F-0071</t>
+          <t>F-0072</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>966-1009</t>
+          <t>963-1006</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>F-0070</t>
+          <t>F-0071</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>942-961</t>
+          <t>939-958</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>963-964</t>
+          <t>960-961</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>1033-1035</t>
+          <t>1030-1032</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>895-919</t>
+          <t>892-916</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>1961-2036</t>
+          <t>1958-2033</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>1814-1844</t>
+          <t>1811-1841</t>
         </is>
       </c>
       <c r="P56" s="3" t="n">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>1357-1362</t>
+          <t>1354-1359</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>1428-1453</t>
+          <t>1425-1450</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>1364-1369</t>
+          <t>1361-1366</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>1357-1362</t>
+          <t>1354-1359</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>1351-1355</t>
+          <t>1348-1352</t>
         </is>
       </c>
       <c r="P61" s="3" t="n">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>F-0045</t>
+          <t>F-0046</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>F-0056</t>
+          <t>F-0057</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>1861-1895</t>
+          <t>1858-1892</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>F-0044</t>
+          <t>F-0045</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>1775-1804</t>
+          <t>1772-1801</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>1047-1048</t>
+          <t>1044-1045</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>1757-1773</t>
+          <t>1754-1770</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P67" s="3" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>1749-1755</t>
+          <t>1746-1752</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>1693-1746</t>
+          <t>1690-1743</t>
         </is>
       </c>
       <c r="P69" s="3" t="n">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>1669-1691</t>
+          <t>1666-1688</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>1806-1811</t>
+          <t>1803-1808</t>
         </is>
       </c>
       <c r="P72" s="3" t="n">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>1757-1773</t>
+          <t>1754-1770</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>F-0045</t>
+          <t>F-0046</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P75" s="3" t="n">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>F-0054</t>
+          <t>F-0055</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>1657-1667</t>
+          <t>1654-1664</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>1047-1048</t>
+          <t>1044-1045</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>F-0045</t>
+          <t>F-0046</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>F-0068</t>
+          <t>F-0069</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>1608-1631</t>
+          <t>1605-1628</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>1555-1567</t>
+          <t>1552-1564</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>1849-1854</t>
+          <t>1846-1851</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>1856-1858</t>
+          <t>1853-1855</t>
         </is>
       </c>
       <c r="P85" s="3" t="n">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>3751-3772</t>
+          <t>3748-3769</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
@@ -14364,11 +14364,11 @@
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>3709-3712</t>
+          <t>3707-3708</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>2603-2612</t>
+          <t>2600-2609</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>3736-3749</t>
+          <t>3733-3746</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>2691-2711</t>
+          <t>2688-2708</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>2620-2626</t>
+          <t>2617-2623</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>963-964</t>
+          <t>960-961</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>2654-2661</t>
+          <t>2651-2658</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>2663-2689</t>
+          <t>2660-2686</t>
         </is>
       </c>
       <c r="P94" s="3" t="n">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>2635-2652</t>
+          <t>2632-2649</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>2628-2633</t>
+          <t>2625-2630</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>2635-2652</t>
+          <t>2632-2649</t>
         </is>
       </c>
       <c r="P98" s="3" t="n">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>2881-2887</t>
+          <t>2878-2884</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>2767-2873</t>
+          <t>2764-2870</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>2754-2764</t>
+          <t>2751-2761</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>2875-2877</t>
+          <t>2872-2874</t>
         </is>
       </c>
       <c r="P105" s="3" t="n">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>2927-2946</t>
+          <t>2924-2943</t>
         </is>
       </c>
       <c r="P108" s="3" t="n">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>2898-2917</t>
+          <t>2895-2914</t>
         </is>
       </c>
       <c r="P109" s="3" t="n">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>2881-2887</t>
+          <t>2878-2884</t>
         </is>
       </c>
       <c r="P110" s="3" t="n">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>3430-3451</t>
+          <t>3427-3448</t>
         </is>
       </c>
       <c r="P111" s="3" t="n">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>3396-3412</t>
+          <t>3393-3409</t>
         </is>
       </c>
       <c r="P112" s="3" t="n">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>3280-3289</t>
+          <t>3277-3286</t>
         </is>
       </c>
       <c r="P114" s="3" t="n">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>2582-2583</t>
+          <t>2579-2580</t>
         </is>
       </c>
       <c r="P115" s="3" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>3751-3772</t>
+          <t>3748-3769</t>
         </is>
       </c>
       <c r="P116" s="3" t="n">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>3751-3772</t>
+          <t>3748-3769</t>
         </is>
       </c>
       <c r="P117" s="3" t="n">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>3345-3347</t>
+          <t>3342-3344</t>
         </is>
       </c>
       <c r="P118" s="3" t="n">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>963-964</t>
+          <t>960-961</t>
         </is>
       </c>
       <c r="P119" s="3" t="n">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
-          <t>3089-3092</t>
+          <t>3086-3089</t>
         </is>
       </c>
       <c r="P120" s="3" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>3272-3278</t>
+          <t>3269-3275</t>
         </is>
       </c>
       <c r="P121" s="3" t="n">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>F-0072</t>
+          <t>F-0073</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>3127-3250</t>
+          <t>3124-3247</t>
         </is>
       </c>
       <c r="P122" s="3" t="n">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>3252-3257</t>
+          <t>3249-3254</t>
         </is>
       </c>
       <c r="P123" s="3" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>F-0043</t>
+          <t>F-0044</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>2511-2539</t>
+          <t>2508-2536</t>
         </is>
       </c>
       <c r="P124" s="3" t="n">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>F-0054</t>
+          <t>F-0055</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>1657-1667</t>
+          <t>1654-1664</t>
         </is>
       </c>
       <c r="P125" s="3" t="n">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>3260-3263</t>
+          <t>3257-3260</t>
         </is>
       </c>
       <c r="P126" s="3" t="n">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>3266-3269</t>
+          <t>3263-3266</t>
         </is>
       </c>
       <c r="P127" s="3" t="n">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>3094-3117</t>
+          <t>3091-3114</t>
         </is>
       </c>
       <c r="P128" s="3" t="n">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>3089-3092</t>
+          <t>3086-3089</t>
         </is>
       </c>
       <c r="P130" s="3" t="n">
@@ -17921,7 +17921,7 @@
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>3349-3394</t>
+          <t>3346-3391</t>
         </is>
       </c>
       <c r="P132" s="3" t="n">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>3068-3086</t>
+          <t>3065-3083</t>
         </is>
       </c>
       <c r="P133" s="3" t="n">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>F-0067</t>
+          <t>F-0068</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>2992-2995</t>
+          <t>2989-2992</t>
         </is>
       </c>
       <c r="P135" s="3" t="n">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>2754-2764</t>
+          <t>2751-2761</t>
         </is>
       </c>
       <c r="P139" s="3" t="n">
@@ -18587,7 +18587,7 @@
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>F-0055</t>
+          <t>F-0056</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>3415-3418</t>
+          <t>3412-3415</t>
         </is>
       </c>
       <c r="P140" s="3" t="n">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>963-964</t>
+          <t>960-961</t>
         </is>
       </c>
       <c r="P141" s="3" t="n">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>2992-2995</t>
+          <t>2989-2992</t>
         </is>
       </c>
       <c r="P142" s="3" t="n">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>3421-3428</t>
+          <t>3418-3425</t>
         </is>
       </c>
       <c r="P143" s="3" t="n">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>2919-2924</t>
+          <t>2916-2921</t>
         </is>
       </c>
       <c r="P144" s="3" t="n">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>2948-2970</t>
+          <t>2945-2967</t>
         </is>
       </c>
       <c r="P145" s="3" t="n">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>3430-3451</t>
+          <t>3427-3448</t>
         </is>
       </c>
       <c r="P152" s="3" t="n">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="O153" s="3" t="inlineStr">
         <is>
-          <t>2983-2990</t>
+          <t>2980-2987</t>
         </is>
       </c>
       <c r="P153" s="3" t="n">
@@ -19667,7 +19667,7 @@
       </c>
       <c r="O154" s="3" t="inlineStr">
         <is>
-          <t>2972-2981</t>
+          <t>2969-2978</t>
         </is>
       </c>
       <c r="P154" s="3" t="n">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="O155" s="3" t="inlineStr">
         <is>
-          <t>3751-3772</t>
+          <t>3748-3769</t>
         </is>
       </c>
       <c r="P155" s="3" t="n">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="O156" s="3" t="inlineStr">
         <is>
-          <t>1498-1532</t>
+          <t>1495-1529</t>
         </is>
       </c>
       <c r="P156" s="3" t="n">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="M157" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P157" s="3" t="n">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="O158" s="3" t="inlineStr">
         <is>
-          <t>1250-1254</t>
+          <t>1247-1251</t>
         </is>
       </c>
       <c r="P158" s="3" t="n">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="O159" s="3" t="inlineStr">
         <is>
-          <t>1225-1248</t>
+          <t>1222-1245</t>
         </is>
       </c>
       <c r="P159" s="3" t="n">
@@ -20095,7 +20095,7 @@
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>F-0059</t>
+          <t>F-0060</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="O160" s="3" t="inlineStr">
         <is>
-          <t>1164-1179</t>
+          <t>1161-1176</t>
         </is>
       </c>
       <c r="P160" s="3" t="n">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="M161" s="5" t="inlineStr">
         <is>
-          <t>F-0060</t>
+          <t>F-0061</t>
         </is>
       </c>
       <c r="N161" s="3" t="inlineStr">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="O161" s="3" t="inlineStr">
         <is>
-          <t>1181-1184</t>
+          <t>1178-1181</t>
         </is>
       </c>
       <c r="P161" s="3" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>F-0064</t>
+          <t>F-0065</t>
         </is>
       </c>
       <c r="N162" s="3" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="O162" s="3" t="inlineStr">
         <is>
-          <t>2075-2100</t>
+          <t>2072-2097</t>
         </is>
       </c>
       <c r="P162" s="3" t="n">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="M163" s="5" t="inlineStr">
         <is>
-          <t>F-0055</t>
+          <t>F-0056</t>
         </is>
       </c>
       <c r="N163" s="3" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="O163" s="3" t="inlineStr">
         <is>
-          <t>3415-3418</t>
+          <t>3412-3415</t>
         </is>
       </c>
       <c r="P163" s="3" t="n">
@@ -20407,7 +20407,7 @@
       </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>F-0063</t>
+          <t>F-0064</t>
         </is>
       </c>
       <c r="N164" s="3" t="inlineStr">
@@ -20417,7 +20417,7 @@
       </c>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>2102-2124</t>
+          <t>2099-2121</t>
         </is>
       </c>
       <c r="P164" s="3" t="n">
@@ -20492,7 +20492,7 @@
       </c>
       <c r="M165" s="5" t="inlineStr">
         <is>
-          <t>F-0059</t>
+          <t>F-0060</t>
         </is>
       </c>
       <c r="N165" s="3" t="inlineStr">
@@ -20502,7 +20502,7 @@
       </c>
       <c r="O165" s="3" t="inlineStr">
         <is>
-          <t>1164-1179</t>
+          <t>1161-1176</t>
         </is>
       </c>
       <c r="P165" s="3" t="n">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="O166" s="3" t="inlineStr">
         <is>
-          <t>3751-3772</t>
+          <t>3748-3769</t>
         </is>
       </c>
       <c r="P166" s="3" t="n">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="O167" s="3" t="inlineStr">
         <is>
-          <t>1186-1195</t>
+          <t>1183-1192</t>
         </is>
       </c>
       <c r="P167" s="3" t="n">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
-          <t>F-0061</t>
+          <t>F-0062</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="O168" s="3" t="inlineStr">
         <is>
-          <t>1261-1344</t>
+          <t>1258-1341</t>
         </is>
       </c>
       <c r="P168" s="3" t="n">
@@ -20830,7 +20830,7 @@
       </c>
       <c r="O169" s="3" t="inlineStr">
         <is>
-          <t>1148-1154</t>
+          <t>1145-1151</t>
         </is>
       </c>
       <c r="P169" s="3" t="n">
@@ -20911,7 +20911,7 @@
       </c>
       <c r="O170" s="3" t="inlineStr">
         <is>
-          <t>1347-1349</t>
+          <t>1344-1346</t>
         </is>
       </c>
       <c r="P170" s="3" t="n">
@@ -21000,7 +21000,7 @@
       </c>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>1148-1154</t>
+          <t>1145-1151</t>
         </is>
       </c>
       <c r="P171" s="3" t="n">
@@ -21069,7 +21069,7 @@
       </c>
       <c r="O172" s="3" t="inlineStr">
         <is>
-          <t>1569-1606</t>
+          <t>1566-1603</t>
         </is>
       </c>
       <c r="P172" s="3" t="n">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="O173" s="3" t="inlineStr">
         <is>
-          <t>1364-1369</t>
+          <t>1361-1366</t>
         </is>
       </c>
       <c r="P173" s="3" t="n">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N174" s="3" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="O174" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P174" s="3" t="n">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>1534-1552</t>
+          <t>1531-1549</t>
         </is>
       </c>
       <c r="P175" s="3" t="n">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="O176" s="3" t="inlineStr">
         <is>
-          <t>1481-1496</t>
+          <t>1478-1493</t>
         </is>
       </c>
       <c r="P176" s="3" t="n">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="O177" s="3" t="inlineStr">
         <is>
-          <t>1364-1369</t>
+          <t>1361-1366</t>
         </is>
       </c>
       <c r="P177" s="3" t="n">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="O178" s="3" t="inlineStr">
         <is>
-          <t>1357-1362</t>
+          <t>1354-1359</t>
         </is>
       </c>
       <c r="P178" s="3" t="n">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="O179" s="3" t="inlineStr">
         <is>
-          <t>1465-1468</t>
+          <t>1462-1465</t>
         </is>
       </c>
       <c r="P179" s="3" t="n">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="O180" s="3" t="inlineStr">
         <is>
-          <t>1428-1453</t>
+          <t>1425-1450</t>
         </is>
       </c>
       <c r="P180" s="3" t="n">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P181" s="3" t="n">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="M182" s="5" t="inlineStr">
         <is>
-          <t>F-0065</t>
+          <t>F-0066</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="O182" s="3" t="inlineStr">
         <is>
-          <t>1471-1479</t>
+          <t>1468-1476</t>
         </is>
       </c>
       <c r="P182" s="3" t="n">
@@ -21872,7 +21872,7 @@
       </c>
       <c r="O183" s="3" t="inlineStr">
         <is>
-          <t>1465-1468</t>
+          <t>1462-1465</t>
         </is>
       </c>
       <c r="P183" s="3" t="n">
@@ -21943,7 +21943,7 @@
       </c>
       <c r="M184" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N184" s="3" t="inlineStr">
@@ -21953,7 +21953,7 @@
       </c>
       <c r="O184" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P184" s="3" t="n">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="O185" s="3" t="inlineStr">
         <is>
-          <t>1136-1140</t>
+          <t>1133-1137</t>
         </is>
       </c>
       <c r="P185" s="3" t="n">
@@ -22103,7 +22103,7 @@
       </c>
       <c r="O186" s="3" t="inlineStr">
         <is>
-          <t>1379-1403</t>
+          <t>1376-1400</t>
         </is>
       </c>
       <c r="P186" s="3" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="M187" s="5" t="inlineStr">
         <is>
-          <t>F-0066</t>
+          <t>F-0067</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -22172,7 +22172,7 @@
       </c>
       <c r="O187" s="3" t="inlineStr">
         <is>
-          <t>1405-1426</t>
+          <t>1402-1423</t>
         </is>
       </c>
       <c r="P187" s="3" t="n">
@@ -22249,7 +22249,7 @@
       </c>
       <c r="O188" s="3" t="inlineStr">
         <is>
-          <t>1357-1362</t>
+          <t>1354-1359</t>
         </is>
       </c>
       <c r="P188" s="3" t="n">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="O189" s="3" t="inlineStr">
         <is>
-          <t>1371-1377</t>
+          <t>1368-1374</t>
         </is>
       </c>
       <c r="P189" s="3" t="n">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="O192" s="3" t="inlineStr">
         <is>
-          <t>1351-1355</t>
+          <t>1348-1352</t>
         </is>
       </c>
       <c r="P192" s="3" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="O193" s="3" t="inlineStr">
         <is>
-          <t>1186-1195</t>
+          <t>1183-1192</t>
         </is>
       </c>
       <c r="P193" s="3" t="n">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="O194" s="3" t="inlineStr">
         <is>
-          <t>1633-1652</t>
+          <t>1630-1649</t>
         </is>
       </c>
       <c r="P194" s="3" t="n">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="M195" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="O195" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P195" s="3" t="n">
@@ -22845,7 +22845,7 @@
       </c>
       <c r="O196" s="3" t="inlineStr">
         <is>
-          <t>1498-1532</t>
+          <t>1495-1529</t>
         </is>
       </c>
       <c r="P196" s="3" t="n">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="M197" s="5" t="inlineStr">
         <is>
-          <t>F-0057</t>
+          <t>F-0058</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="O197" s="3" t="inlineStr">
         <is>
-          <t>1920-1939</t>
+          <t>1917-1936</t>
         </is>
       </c>
       <c r="P197" s="3" t="n">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="M206" s="5" t="inlineStr">
         <is>
-          <t>F-0055</t>
+          <t>F-0056</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
@@ -23507,7 +23507,7 @@
       </c>
       <c r="O206" s="3" t="inlineStr">
         <is>
-          <t>3415-3418</t>
+          <t>3412-3415</t>
         </is>
       </c>
       <c r="P206" s="3" t="n">
@@ -23765,7 +23765,7 @@
       </c>
       <c r="M210" s="5" t="inlineStr">
         <is>
-          <t>F-0052</t>
+          <t>F-0053</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="O210" s="3" t="inlineStr">
         <is>
-          <t>1457-1463</t>
+          <t>1454-1460</t>
         </is>
       </c>
       <c r="P210" s="3" t="n">
@@ -23830,7 +23830,7 @@
       </c>
       <c r="M211" s="5" t="inlineStr">
         <is>
-          <t>F-0055</t>
+          <t>F-0056</t>
         </is>
       </c>
       <c r="N211" s="3" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="O211" s="3" t="inlineStr">
         <is>
-          <t>3415-3418</t>
+          <t>3412-3415</t>
         </is>
       </c>
       <c r="P211" s="3" t="n">
@@ -23956,7 +23956,7 @@
       </c>
       <c r="M213" s="5" t="inlineStr">
         <is>
-          <t>F-0062</t>
+          <t>F-0063</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="O213" s="3" t="inlineStr">
         <is>
-          <t>1197-1223</t>
+          <t>1194-1220</t>
         </is>
       </c>
       <c r="P213" s="3" t="n">
@@ -24021,7 +24021,7 @@
       </c>
       <c r="M214" s="5" t="inlineStr">
         <is>
-          <t>F-0045</t>
+          <t>F-0046</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -24086,7 +24086,7 @@
       </c>
       <c r="M215" s="5" t="inlineStr">
         <is>
-          <t>F-0059</t>
+          <t>F-0060</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="O215" s="3" t="inlineStr">
         <is>
-          <t>1164-1179</t>
+          <t>1161-1176</t>
         </is>
       </c>
       <c r="P215" s="3" t="n">
@@ -24151,7 +24151,7 @@
       </c>
       <c r="M216" s="5" t="inlineStr">
         <is>
-          <t>F-0060</t>
+          <t>F-0061</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="O216" s="3" t="inlineStr">
         <is>
-          <t>1181-1184</t>
+          <t>1178-1181</t>
         </is>
       </c>
       <c r="P216" s="3" t="n">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="M217" s="5" t="inlineStr">
         <is>
-          <t>F-0064</t>
+          <t>F-0065</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="O217" s="3" t="inlineStr">
         <is>
-          <t>2075-2100</t>
+          <t>2072-2097</t>
         </is>
       </c>
       <c r="P217" s="3" t="n">
@@ -24295,7 +24295,7 @@
       </c>
       <c r="O218" s="3" t="inlineStr">
         <is>
-          <t>1250-1254</t>
+          <t>1247-1251</t>
         </is>
       </c>
       <c r="P218" s="3" t="n">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="O219" s="3" t="inlineStr">
         <is>
-          <t>1186-1195</t>
+          <t>1183-1192</t>
         </is>
       </c>
       <c r="P219" s="3" t="n">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="O220" s="3" t="inlineStr">
         <is>
-          <t>1053-1056</t>
+          <t>1050-1053</t>
         </is>
       </c>
       <c r="P220" s="3" t="n">
@@ -24486,7 +24486,7 @@
       </c>
       <c r="O221" s="3" t="inlineStr">
         <is>
-          <t>1856-1858</t>
+          <t>1853-1855</t>
         </is>
       </c>
       <c r="P221" s="3" t="n">
@@ -24547,7 +24547,7 @@
       </c>
       <c r="O222" s="3" t="inlineStr">
         <is>
-          <t>1897-1918</t>
+          <t>1894-1915</t>
         </is>
       </c>
       <c r="P222" s="3" t="n">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="O223" s="3" t="inlineStr">
         <is>
-          <t>1081-1093</t>
+          <t>1078-1090</t>
         </is>
       </c>
       <c r="P223" s="3" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="O224" s="3" t="inlineStr">
         <is>
-          <t>1941-1958</t>
+          <t>1938-1955</t>
         </is>
       </c>
       <c r="P224" s="3" t="n">
@@ -24718,7 +24718,7 @@
       </c>
       <c r="O225" s="3" t="inlineStr">
         <is>
-          <t>1124-1133</t>
+          <t>1121-1130</t>
         </is>
       </c>
       <c r="P225" s="3" t="n">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="O228" s="3" t="inlineStr">
         <is>
-          <t>1117-1122</t>
+          <t>1114-1119</t>
         </is>
       </c>
       <c r="P228" s="3" t="n">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="O231" s="3" t="inlineStr">
         <is>
-          <t>1095-1115</t>
+          <t>1092-1112</t>
         </is>
       </c>
       <c r="P231" s="3" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="O232" s="3" t="inlineStr">
         <is>
-          <t>1058-1079</t>
+          <t>1055-1076</t>
         </is>
       </c>
       <c r="P232" s="3" t="n">
@@ -25186,7 +25186,7 @@
       </c>
       <c r="O233" s="3" t="inlineStr">
         <is>
-          <t>3539-3541</t>
+          <t>3536-3538</t>
         </is>
       </c>
       <c r="P233" s="3" t="n">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="O234" s="3" t="inlineStr">
         <is>
-          <t>2493-2508</t>
+          <t>2490-2505</t>
         </is>
       </c>
       <c r="P234" s="3" t="n">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="O235" s="3" t="inlineStr">
         <is>
-          <t>2126-2483</t>
+          <t>2123-2480</t>
         </is>
       </c>
       <c r="P235" s="3" t="n">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="O236" s="3" t="inlineStr">
         <is>
-          <t>1148-1154</t>
+          <t>1145-1151</t>
         </is>
       </c>
       <c r="P236" s="3" t="n">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="O237" s="3" t="inlineStr">
         <is>
-          <t>1357-1362</t>
+          <t>1354-1359</t>
         </is>
       </c>
       <c r="P237" s="3" t="n">
@@ -25489,7 +25489,7 @@
       </c>
       <c r="M238" s="5" t="inlineStr">
         <is>
-          <t>F-0063</t>
+          <t>F-0064</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
@@ -25499,7 +25499,7 @@
       </c>
       <c r="O238" s="3" t="inlineStr">
         <is>
-          <t>2102-2124</t>
+          <t>2099-2121</t>
         </is>
       </c>
       <c r="P238" s="3" t="n">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="M239" s="5" t="inlineStr">
         <is>
-          <t>F-0064</t>
+          <t>F-0065</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="O239" s="3" t="inlineStr">
         <is>
-          <t>2075-2100</t>
+          <t>2072-2097</t>
         </is>
       </c>
       <c r="P239" s="3" t="n">
@@ -25637,7 +25637,7 @@
       </c>
       <c r="O240" s="3" t="inlineStr">
         <is>
-          <t>1250-1254</t>
+          <t>1247-1251</t>
         </is>
       </c>
       <c r="P240" s="3" t="n">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="O241" s="3" t="inlineStr">
         <is>
-          <t>1225-1248</t>
+          <t>1222-1245</t>
         </is>
       </c>
       <c r="P241" s="3" t="n">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="O242" s="3" t="inlineStr">
         <is>
-          <t>2486-2491</t>
+          <t>2483-2488</t>
         </is>
       </c>
       <c r="P242" s="3" t="n">
@@ -25883,7 +25883,7 @@
       </c>
       <c r="M244" s="5" t="inlineStr">
         <is>
-          <t>F-0064</t>
+          <t>F-0065</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O244" s="3" t="inlineStr">
         <is>
-          <t>2075-2100</t>
+          <t>2072-2097</t>
         </is>
       </c>
       <c r="P244" s="3" t="n">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="O245" s="3" t="inlineStr">
         <is>
-          <t>3396-3412</t>
+          <t>3393-3409</t>
         </is>
       </c>
       <c r="P245" s="3" t="n">
@@ -26007,7 +26007,7 @@
       </c>
       <c r="O246" s="3" t="inlineStr">
         <is>
-          <t>2927-2946</t>
+          <t>2924-2943</t>
         </is>
       </c>
       <c r="P246" s="3" t="n">
@@ -26064,11 +26064,11 @@
       </c>
       <c r="O247" s="3" t="inlineStr">
         <is>
-          <t>3584-3640</t>
+          <t>3596-3649</t>
         </is>
       </c>
       <c r="P247" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="Q247" s="3" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
       </c>
       <c r="R247" s="3" t="inlineStr">
         <is>
-          <t>docling_folder; docling_install; docling_ready; flowr_ready; install; live; notebook_folder; pip_said; review</t>
+          <t>databricks_user; docling_folder; docling_install; docling_ready; flowr_ready; install; live; notebook_folder; pip_said; review</t>
         </is>
       </c>
       <c r="S247" s="3" t="inlineStr"/>
@@ -26106,42 +26106,34 @@
       </c>
       <c r="L248" s="6" t="inlineStr">
         <is>
-          <t>docling_folder</t>
+          <t>databricks_user</t>
         </is>
       </c>
       <c r="M248" s="5" t="inlineStr">
         <is>
-          <t>F-0047</t>
+          <t>F-0043</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>the methodology and the documentation, read by Docling</t>
+          <t>the notebook: four cells, each one call</t>
         </is>
       </c>
       <c r="O248" s="3" t="inlineStr">
         <is>
-          <t>832-836</t>
+          <t>3562-3576</t>
         </is>
       </c>
       <c r="P248" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q248" s="3" t="inlineStr">
         <is>
-          <t>Docling's own folder: on the machine's local disk, and this system user's own - a shared cluster runs each</t>
-        </is>
-      </c>
-      <c r="R248" s="3" t="inlineStr">
-        <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="S248" s="3" t="inlineStr">
-        <is>
-          <t>shown in full at 02.02.01.04.02.02</t>
-        </is>
-      </c>
+          <t>Who runs the notebook, as Databricks knows them: the notebook context's user name; on a cluster that keeps</t>
+        </is>
+      </c>
+      <c r="R248" s="3" t="inlineStr"/>
+      <c r="S248" s="3" t="inlineStr"/>
     </row>
     <row r="249" outlineLevel="1">
       <c r="A249" s="3" t="inlineStr">
@@ -26167,7 +26159,7 @@
       </c>
       <c r="L249" s="6" t="inlineStr">
         <is>
-          <t>docling_install</t>
+          <t>docling_folder</t>
         </is>
       </c>
       <c r="M249" s="5" t="inlineStr">
@@ -26182,25 +26174,29 @@
       </c>
       <c r="O249" s="3" t="inlineStr">
         <is>
-          <t>859-869</t>
+          <t>832-836</t>
         </is>
       </c>
       <c r="P249" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q249" s="3" t="inlineStr">
         <is>
-          <t>Install Docling into its own folder - never into the runtime's packages - from the index(es) of widget 06, or</t>
+          <t>Docling's own folder: on the machine's local disk, and this system user's own - a shared cluster runs each</t>
         </is>
       </c>
       <c r="R249" s="3" t="inlineStr">
         <is>
-          <t>docling_folder; index_arguments; install</t>
-        </is>
-      </c>
-      <c r="S249" s="3" t="inlineStr"/>
-    </row>
-    <row r="250" outlineLevel="2">
+          <t>local</t>
+        </is>
+      </c>
+      <c r="S249" s="3" t="inlineStr">
+        <is>
+          <t>shown in full at 02.02.01.04.02.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" outlineLevel="1">
       <c r="A250" s="3" t="inlineStr">
         <is>
           <t>08</t>
@@ -26208,14 +26204,10 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="C250" s="3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr"/>
       <c r="D250" s="3" t="inlineStr"/>
       <c r="E250" s="3" t="inlineStr"/>
       <c r="F250" s="3" t="inlineStr"/>
@@ -26224,16 +26216,16 @@
       <c r="I250" s="3" t="inlineStr"/>
       <c r="J250" s="3" t="inlineStr"/>
       <c r="K250" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L250" s="7" t="inlineStr">
-        <is>
-          <t>docling_folder</t>
+        <v>1</v>
+      </c>
+      <c r="L250" s="6" t="inlineStr">
+        <is>
+          <t>docling_install</t>
         </is>
       </c>
       <c r="M250" s="5" t="inlineStr">
         <is>
-          <t>F-0047</t>
+          <t>F-0049</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
@@ -26243,27 +26235,23 @@
       </c>
       <c r="O250" s="3" t="inlineStr">
         <is>
-          <t>832-836</t>
+          <t>859-866</t>
         </is>
       </c>
       <c r="P250" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q250" s="3" t="inlineStr">
         <is>
-          <t>Docling's own folder: on the machine's local disk, and this system user's own - a shared cluster runs each</t>
+          <t>Install Docling from PyPI into its own folder - never into the runtime's packages. Returns what pip said when</t>
         </is>
       </c>
       <c r="R250" s="3" t="inlineStr">
         <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="S250" s="3" t="inlineStr">
-        <is>
-          <t>shown in full at 02.02.01.04.02.02</t>
-        </is>
-      </c>
+          <t>docling_folder; install</t>
+        </is>
+      </c>
+      <c r="S250" s="3" t="inlineStr"/>
     </row>
     <row r="251" outlineLevel="2">
       <c r="A251" s="3" t="inlineStr">
@@ -26273,12 +26261,12 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr"/>
@@ -26293,34 +26281,42 @@
       </c>
       <c r="L251" s="7" t="inlineStr">
         <is>
-          <t>index_arguments</t>
+          <t>docling_folder</t>
         </is>
       </c>
       <c r="M251" s="5" t="inlineStr">
         <is>
-          <t>F-0073</t>
+          <t>F-0048</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>the notebook: four cells, each one call</t>
+          <t>the methodology and the documentation, read by Docling</t>
         </is>
       </c>
       <c r="O251" s="3" t="inlineStr">
         <is>
-          <t>3642-3644</t>
+          <t>832-836</t>
         </is>
       </c>
       <c r="P251" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q251" s="3" t="inlineStr">
         <is>
-          <t>pip's arguments for the index(es) of widget 06: the first URL is the index, any further one an extra index.</t>
-        </is>
-      </c>
-      <c r="R251" s="3" t="inlineStr"/>
-      <c r="S251" s="3" t="inlineStr"/>
+          <t>Docling's own folder: on the machine's local disk, and this system user's own - a shared cluster runs each</t>
+        </is>
+      </c>
+      <c r="R251" s="3" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="S251" s="3" t="inlineStr">
+        <is>
+          <t>shown in full at 02.02.01.04.02.02</t>
+        </is>
+      </c>
     </row>
     <row r="252" outlineLevel="2">
       <c r="A252" s="3" t="inlineStr">
@@ -26330,12 +26326,12 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
@@ -26365,20 +26361,20 @@
       </c>
       <c r="O252" s="3" t="inlineStr">
         <is>
-          <t>3659-3707</t>
+          <t>3663-3705</t>
         </is>
       </c>
       <c r="P252" s="3" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Q252" s="3" t="inlineStr">
         <is>
-          <t>Install what the engine needs - from a staged folder of wheels when there is one, else from the index named in</t>
+          <t>Install what the engine needs from PyPI, the runtime's own packages pinned as they are, and restart Python</t>
         </is>
       </c>
       <c r="R252" s="3" t="inlineStr">
         <is>
-          <t>index_arguments; pip_said</t>
+          <t>pip_said</t>
         </is>
       </c>
       <c r="S252" s="3" t="inlineStr"/>
@@ -26391,12 +26387,12 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -26415,12 +26411,12 @@
       </c>
       <c r="L253" s="8" t="inlineStr">
         <is>
-          <t>index_arguments</t>
+          <t>pip_said</t>
         </is>
       </c>
       <c r="M253" s="5" t="inlineStr">
         <is>
-          <t>F-0073</t>
+          <t>F-0108</t>
         </is>
       </c>
       <c r="N253" s="3" t="inlineStr">
@@ -26430,25 +26426,21 @@
       </c>
       <c r="O253" s="3" t="inlineStr">
         <is>
-          <t>3642-3644</t>
+          <t>3652-3661</t>
         </is>
       </c>
       <c r="P253" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q253" s="3" t="inlineStr">
         <is>
-          <t>pip's arguments for the index(es) of widget 06: the first URL is the index, any further one an extra index.</t>
+          <t>What pip said, without any credentials of an index URL, and what its most common failure means.</t>
         </is>
       </c>
       <c r="R253" s="3" t="inlineStr"/>
-      <c r="S253" s="3" t="inlineStr">
-        <is>
-          <t>shown in full at 08.02.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" outlineLevel="3">
+      <c r="S253" s="3" t="inlineStr"/>
+    </row>
+    <row r="254" outlineLevel="1">
       <c r="A254" s="3" t="inlineStr">
         <is>
           <t>08</t>
@@ -26456,19 +26448,11 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="C254" s="3" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D254" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr"/>
+      <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="3" t="inlineStr"/>
       <c r="F254" s="3" t="inlineStr"/>
       <c r="G254" s="3" t="inlineStr"/>
@@ -26476,26 +26460,26 @@
       <c r="I254" s="3" t="inlineStr"/>
       <c r="J254" s="3" t="inlineStr"/>
       <c r="K254" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L254" s="8" t="inlineStr">
-        <is>
-          <t>pip_said</t>
+        <v>1</v>
+      </c>
+      <c r="L254" s="6" t="inlineStr">
+        <is>
+          <t>docling_ready</t>
         </is>
       </c>
       <c r="M254" s="5" t="inlineStr">
         <is>
-          <t>F-0108</t>
+          <t>F-0051</t>
         </is>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>the notebook: four cells, each one call</t>
+          <t>the methodology and the documentation, read by Docling</t>
         </is>
       </c>
       <c r="O254" s="3" t="inlineStr">
         <is>
-          <t>3646-3657</t>
+          <t>846-857</t>
         </is>
       </c>
       <c r="P254" s="3" t="n">
@@ -26503,11 +26487,19 @@
       </c>
       <c r="Q254" s="3" t="inlineStr">
         <is>
-          <t>What pip said, without any credentials of an index URL, and what its most common failure means.</t>
-        </is>
-      </c>
-      <c r="R254" s="3" t="inlineStr"/>
-      <c r="S254" s="3" t="inlineStr"/>
+          <t>Where Docling runs from: its own folder, or "" when the runtime itself carries it; None when it is nowhere yet.</t>
+        </is>
+      </c>
+      <c r="R254" s="3" t="inlineStr">
+        <is>
+          <t>docling_environment; docling_folder</t>
+        </is>
+      </c>
+      <c r="S254" s="3" t="inlineStr">
+        <is>
+          <t>shown in full at 02.02.01.04.02</t>
+        </is>
+      </c>
     </row>
     <row r="255" outlineLevel="1">
       <c r="A255" s="3" t="inlineStr">
@@ -26517,7 +26509,7 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr"/>
@@ -26533,40 +26525,40 @@
       </c>
       <c r="L255" s="6" t="inlineStr">
         <is>
-          <t>docling_ready</t>
+          <t>flowr_ready</t>
         </is>
       </c>
       <c r="M255" s="5" t="inlineStr">
         <is>
-          <t>F-0050</t>
+          <t>F-0065</t>
         </is>
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>the methodology and the documentation, read by Docling</t>
+          <t>flowR: the program the data flow is read with</t>
         </is>
       </c>
       <c r="O255" s="3" t="inlineStr">
         <is>
-          <t>846-857</t>
+          <t>2072-2097</t>
         </is>
       </c>
       <c r="P255" s="3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Q255" s="3" t="inlineStr">
         <is>
-          <t>Where Docling runs from: its own folder, or "" when the runtime itself carries it; None when it is nowhere yet.</t>
+          <t>flowR's folder, fetched once from source - a staged archive, such as one in a Volume - or from the</t>
         </is>
       </c>
       <c r="R255" s="3" t="inlineStr">
         <is>
-          <t>docling_environment; docling_folder</t>
+          <t>file_sha256; flowr_read; review</t>
         </is>
       </c>
       <c r="S255" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.02.01.04.02</t>
+          <t>shown in full at 02.04.07.08.02.01.03</t>
         </is>
       </c>
     </row>
@@ -26578,7 +26570,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr"/>
@@ -26594,40 +26586,40 @@
       </c>
       <c r="L256" s="6" t="inlineStr">
         <is>
-          <t>flowr_ready</t>
+          <t>install</t>
         </is>
       </c>
       <c r="M256" s="5" t="inlineStr">
         <is>
-          <t>F-0064</t>
+          <t>F-0075</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>flowR: the program the data flow is read with</t>
+          <t>the notebook: four cells, each one call</t>
         </is>
       </c>
       <c r="O256" s="3" t="inlineStr">
         <is>
-          <t>2075-2100</t>
+          <t>3663-3705</t>
         </is>
       </c>
       <c r="P256" s="3" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="Q256" s="3" t="inlineStr">
         <is>
-          <t>flowR's folder, fetched once from source - a staged archive, such as one in a Volume - or from the</t>
+          <t>Install what the engine needs from PyPI, the runtime's own packages pinned as they are, and restart Python</t>
         </is>
       </c>
       <c r="R256" s="3" t="inlineStr">
         <is>
-          <t>file_sha256; flowr_read; review</t>
+          <t>pip_said</t>
         </is>
       </c>
       <c r="S256" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.04.07.08.02.01.03</t>
+          <t>shown in full at 08.03.02</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26631,7 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr"/>
@@ -26655,12 +26647,12 @@
       </c>
       <c r="L257" s="6" t="inlineStr">
         <is>
-          <t>install</t>
+          <t>live</t>
         </is>
       </c>
       <c r="M257" s="5" t="inlineStr">
         <is>
-          <t>F-0075</t>
+          <t>F-0083</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -26670,29 +26662,25 @@
       </c>
       <c r="O257" s="3" t="inlineStr">
         <is>
-          <t>3659-3707</t>
+          <t>3578-3587</t>
         </is>
       </c>
       <c r="P257" s="3" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="Q257" s="3" t="inlineStr">
         <is>
-          <t>Install what the engine needs - from a staged folder of wheels when there is one, else from the index named in</t>
+          <t>The endpoint and token, read from the widgets at the moment chat() calls - a token pasted into widget 02</t>
         </is>
       </c>
       <c r="R257" s="3" t="inlineStr">
         <is>
-          <t>index_arguments; pip_said</t>
-        </is>
-      </c>
-      <c r="S257" s="3" t="inlineStr">
-        <is>
-          <t>shown in full at 08.02.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" outlineLevel="1">
+          <t>LiveValues</t>
+        </is>
+      </c>
+      <c r="S257" s="3" t="inlineStr"/>
+    </row>
+    <row r="258" outlineLevel="2">
       <c r="A258" s="3" t="inlineStr">
         <is>
           <t>08</t>
@@ -26700,10 +26688,14 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="C258" s="3" t="inlineStr"/>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr"/>
       <c r="F258" s="3" t="inlineStr"/>
@@ -26712,44 +26704,44 @@
       <c r="I258" s="3" t="inlineStr"/>
       <c r="J258" s="3" t="inlineStr"/>
       <c r="K258" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L258" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L258" s="7" t="inlineStr">
+        <is>
+          <t>LiveValues</t>
+        </is>
+      </c>
+      <c r="M258" s="5" t="inlineStr">
+        <is>
+          <t>F-0007</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
+          <t>live values (the token)</t>
+        </is>
+      </c>
+      <c r="O258" s="3" t="inlineStr">
+        <is>
+          <t>2712-2744</t>
+        </is>
+      </c>
+      <c r="P258" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q258" s="3" t="inlineStr">
+        <is>
+          <t>The three values chat() reads when it is CALLED: endpoint, token, user id. They live</t>
+        </is>
+      </c>
+      <c r="R258" s="3" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="M258" s="5" t="inlineStr">
-        <is>
-          <t>F-0083</t>
-        </is>
-      </c>
-      <c r="N258" s="3" t="inlineStr">
-        <is>
-          <t>the notebook: four cells, each one call</t>
-        </is>
-      </c>
-      <c r="O258" s="3" t="inlineStr">
-        <is>
-          <t>3566-3575</t>
-        </is>
-      </c>
-      <c r="P258" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q258" s="3" t="inlineStr">
-        <is>
-          <t>The endpoint, token or user id, read from the widgets at the moment chat() calls: a token pasted</t>
-        </is>
-      </c>
-      <c r="R258" s="3" t="inlineStr">
-        <is>
-          <t>LiveValues</t>
-        </is>
-      </c>
       <c r="S258" s="3" t="inlineStr"/>
     </row>
-    <row r="259" outlineLevel="2">
+    <row r="259" outlineLevel="3">
       <c r="A259" s="3" t="inlineStr">
         <is>
           <t>08</t>
@@ -26757,7 +26749,7 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
@@ -26765,7 +26757,11 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D259" s="3" t="inlineStr"/>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="E259" s="3" t="inlineStr"/>
       <c r="F259" s="3" t="inlineStr"/>
       <c r="G259" s="3" t="inlineStr"/>
@@ -26773,44 +26769,48 @@
       <c r="I259" s="3" t="inlineStr"/>
       <c r="J259" s="3" t="inlineStr"/>
       <c r="K259" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L259" s="7" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L259" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="M259" s="5" t="inlineStr">
+        <is>
+          <t>F-0083</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
+          <t>the notebook: four cells, each one call</t>
+        </is>
+      </c>
+      <c r="O259" s="3" t="inlineStr">
+        <is>
+          <t>3578-3587</t>
+        </is>
+      </c>
+      <c r="P259" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q259" s="3" t="inlineStr">
+        <is>
+          <t>The endpoint and token, read from the widgets at the moment chat() calls - a token pasted into widget 02</t>
+        </is>
+      </c>
+      <c r="R259" s="3" t="inlineStr">
         <is>
           <t>LiveValues</t>
         </is>
       </c>
-      <c r="M259" s="5" t="inlineStr">
-        <is>
-          <t>F-0007</t>
-        </is>
-      </c>
-      <c r="N259" s="3" t="inlineStr">
-        <is>
-          <t>live values (the token)</t>
-        </is>
-      </c>
-      <c r="O259" s="3" t="inlineStr">
-        <is>
-          <t>2715-2747</t>
-        </is>
-      </c>
-      <c r="P259" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q259" s="3" t="inlineStr">
-        <is>
-          <t>The three values chat() reads when it is CALLED: endpoint, token, user id. They live</t>
-        </is>
-      </c>
-      <c r="R259" s="3" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="S259" s="3" t="inlineStr"/>
-    </row>
-    <row r="260" outlineLevel="3">
+      <c r="S259" s="3" t="inlineStr">
+        <is>
+          <t>calls itself; the descent stops here</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" outlineLevel="1">
       <c r="A260" s="3" t="inlineStr">
         <is>
           <t>08</t>
@@ -26818,19 +26818,11 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="C260" s="3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D260" s="3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr"/>
+      <c r="D260" s="3" t="inlineStr"/>
       <c r="E260" s="3" t="inlineStr"/>
       <c r="F260" s="3" t="inlineStr"/>
       <c r="G260" s="3" t="inlineStr"/>
@@ -26838,16 +26830,16 @@
       <c r="I260" s="3" t="inlineStr"/>
       <c r="J260" s="3" t="inlineStr"/>
       <c r="K260" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L260" s="8" t="inlineStr">
-        <is>
-          <t>live</t>
+        <v>1</v>
+      </c>
+      <c r="L260" s="6" t="inlineStr">
+        <is>
+          <t>notebook_folder</t>
         </is>
       </c>
       <c r="M260" s="5" t="inlineStr">
         <is>
-          <t>F-0083</t>
+          <t>F-0095</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
@@ -26857,27 +26849,19 @@
       </c>
       <c r="O260" s="3" t="inlineStr">
         <is>
-          <t>3566-3575</t>
+          <t>3589-3594</t>
         </is>
       </c>
       <c r="P260" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q260" s="3" t="inlineStr">
         <is>
-          <t>The endpoint, token or user id, read from the widgets at the moment chat() calls: a token pasted</t>
-        </is>
-      </c>
-      <c r="R260" s="3" t="inlineStr">
-        <is>
-          <t>LiveValues</t>
-        </is>
-      </c>
-      <c r="S260" s="3" t="inlineStr">
-        <is>
-          <t>calls itself; the descent stops here</t>
-        </is>
-      </c>
+          <t>(no description)</t>
+        </is>
+      </c>
+      <c r="R260" s="3" t="inlineStr"/>
+      <c r="S260" s="3" t="inlineStr"/>
     </row>
     <row r="261" outlineLevel="1">
       <c r="A261" s="3" t="inlineStr">
@@ -26887,7 +26871,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr"/>
@@ -26903,12 +26887,12 @@
       </c>
       <c r="L261" s="6" t="inlineStr">
         <is>
-          <t>notebook_folder</t>
+          <t>pip_said</t>
         </is>
       </c>
       <c r="M261" s="5" t="inlineStr">
         <is>
-          <t>F-0095</t>
+          <t>F-0108</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
@@ -26918,19 +26902,23 @@
       </c>
       <c r="O261" s="3" t="inlineStr">
         <is>
-          <t>3577-3582</t>
+          <t>3652-3661</t>
         </is>
       </c>
       <c r="P261" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q261" s="3" t="inlineStr">
         <is>
-          <t>(no description)</t>
+          <t>What pip said, without any credentials of an index URL, and what its most common failure means.</t>
         </is>
       </c>
       <c r="R261" s="3" t="inlineStr"/>
-      <c r="S261" s="3" t="inlineStr"/>
+      <c r="S261" s="3" t="inlineStr">
+        <is>
+          <t>shown in full at 08.03.02.01</t>
+        </is>
+      </c>
     </row>
     <row r="262" outlineLevel="1">
       <c r="A262" s="3" t="inlineStr">
@@ -26940,7 +26928,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr"/>
@@ -26956,12 +26944,12 @@
       </c>
       <c r="L262" s="6" t="inlineStr">
         <is>
-          <t>pip_said</t>
+          <t>review</t>
         </is>
       </c>
       <c r="M262" s="5" t="inlineStr">
         <is>
-          <t>F-0108</t>
+          <t>F-0124</t>
         </is>
       </c>
       <c r="N262" s="3" t="inlineStr">
@@ -26971,35 +26959,35 @@
       </c>
       <c r="O262" s="3" t="inlineStr">
         <is>
-          <t>3646-3657</t>
+          <t>3748-3769</t>
         </is>
       </c>
       <c r="P262" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q262" s="3" t="inlineStr">
         <is>
-          <t>What pip said, without any credentials of an index URL, and what its most common failure means.</t>
-        </is>
-      </c>
-      <c r="R262" s="3" t="inlineStr"/>
+          <t>Cell 3: read the inputs and map how the model computes what it returns, in this cell; then say</t>
+        </is>
+      </c>
+      <c r="R262" s="3" t="inlineStr">
+        <is>
+          <t>notebook_settings; open_current; open_store; run_pipeline</t>
+        </is>
+      </c>
       <c r="S262" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 08.02.03.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" outlineLevel="1">
+          <t>shown in full at 02.04.07.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="inlineStr">
-        <is>
           <t>09</t>
         </is>
       </c>
+      <c r="B263" s="3" t="inlineStr"/>
       <c r="C263" s="3" t="inlineStr"/>
       <c r="D263" s="3" t="inlineStr"/>
       <c r="E263" s="3" t="inlineStr"/>
@@ -27009,16 +26997,16 @@
       <c r="I263" s="3" t="inlineStr"/>
       <c r="J263" s="3" t="inlineStr"/>
       <c r="K263" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L263" s="6" t="inlineStr">
-        <is>
-          <t>review</t>
+        <v>0</v>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t>check_chat</t>
         </is>
       </c>
       <c r="M263" s="5" t="inlineStr">
         <is>
-          <t>F-0124</t>
+          <t>F-0031</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
@@ -27028,7 +27016,7 @@
       </c>
       <c r="O263" s="3" t="inlineStr">
         <is>
-          <t>3751-3772</t>
+          <t>3710-3731</t>
         </is>
       </c>
       <c r="P263" s="3" t="n">
@@ -27036,27 +27024,27 @@
       </c>
       <c r="Q263" s="3" t="inlineStr">
         <is>
-          <t>Cell 3: read the inputs and map how the model computes what it returns, in this cell; then say</t>
+          <t>Cell 2 checks chat() - Cell 2: ask the organisation's chat() one question and, once it answers, make the project's three</t>
         </is>
       </c>
       <c r="R263" s="3" t="inlineStr">
         <is>
-          <t>notebook_settings; open_current; open_store; run_pipeline</t>
-        </is>
-      </c>
-      <c r="S263" s="3" t="inlineStr">
-        <is>
-          <t>shown in full at 02.04.07.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
+          <t>setup_project</t>
+        </is>
+      </c>
+      <c r="S263" s="3" t="inlineStr"/>
+    </row>
+    <row r="264" outlineLevel="1">
       <c r="A264" s="3" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B264" s="3" t="inlineStr"/>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="C264" s="3" t="inlineStr"/>
       <c r="D264" s="3" t="inlineStr"/>
       <c r="E264" s="3" t="inlineStr"/>
@@ -27066,54 +27054,54 @@
       <c r="I264" s="3" t="inlineStr"/>
       <c r="J264" s="3" t="inlineStr"/>
       <c r="K264" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L264" s="3" t="inlineStr">
-        <is>
-          <t>check_chat</t>
+        <v>1</v>
+      </c>
+      <c r="L264" s="6" t="inlineStr">
+        <is>
+          <t>setup_project</t>
         </is>
       </c>
       <c r="M264" s="5" t="inlineStr">
         <is>
-          <t>F-0031</t>
+          <t>F-0134</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
-          <t>the notebook: four cells, each one call</t>
+          <t>paths and project setup</t>
         </is>
       </c>
       <c r="O264" s="3" t="inlineStr">
         <is>
-          <t>3714-3734</t>
+          <t>2632-2649</t>
         </is>
       </c>
       <c r="P264" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q264" s="3" t="inlineStr">
         <is>
-          <t>Cell 2 checks chat() - Cell 2: ask the organisation's chat() one question and, once it answers, make the project's three</t>
+          <t>Create the project skeleton and say what is still missing. Inputs are never touched.</t>
         </is>
       </c>
       <c r="R264" s="3" t="inlineStr">
         <is>
-          <t>setup_project</t>
-        </is>
-      </c>
-      <c r="S264" s="3" t="inlineStr"/>
-    </row>
-    <row r="265" outlineLevel="1">
+          <t>check_model_id</t>
+        </is>
+      </c>
+      <c r="S264" s="3" t="inlineStr">
+        <is>
+          <t>shown in full at 02.04.07.07.02.01.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr"/>
       <c r="C265" s="3" t="inlineStr"/>
       <c r="D265" s="3" t="inlineStr"/>
       <c r="E265" s="3" t="inlineStr"/>
@@ -27123,51 +27111,51 @@
       <c r="I265" s="3" t="inlineStr"/>
       <c r="J265" s="3" t="inlineStr"/>
       <c r="K265" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L265" s="6" t="inlineStr">
-        <is>
-          <t>setup_project</t>
+        <v>0</v>
+      </c>
+      <c r="L265" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
       <c r="M265" s="5" t="inlineStr">
         <is>
-          <t>F-0134</t>
+          <t>F-0124</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>paths and project setup</t>
+          <t>the notebook: four cells, each one call</t>
         </is>
       </c>
       <c r="O265" s="3" t="inlineStr">
         <is>
-          <t>2635-2652</t>
+          <t>3748-3769</t>
         </is>
       </c>
       <c r="P265" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q265" s="3" t="inlineStr">
         <is>
-          <t>Create the project skeleton and say what is still missing. Inputs are never touched.</t>
+          <t>Cell 3 runs the review - Cell 3: read the inputs and map how the model computes what it returns, in this cell; then say</t>
         </is>
       </c>
       <c r="R265" s="3" t="inlineStr">
         <is>
-          <t>check_model_id</t>
+          <t>notebook_settings; open_current; open_store; run_pipeline</t>
         </is>
       </c>
       <c r="S265" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.04.07.07.02.01.05</t>
+          <t>shown in full at 02.04.07.07</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr"/>
@@ -27184,12 +27172,12 @@
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="M266" s="5" t="inlineStr">
         <is>
-          <t>F-0124</t>
+          <t>F-0153</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
@@ -27199,35 +27187,35 @@
       </c>
       <c r="O266" s="3" t="inlineStr">
         <is>
-          <t>3751-3772</t>
+          <t>3771-3781</t>
         </is>
       </c>
       <c r="P266" s="3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="Q266" s="3" t="inlineStr">
         <is>
-          <t>Cell 3 runs the review - Cell 3: read the inputs and map how the model computes what it returns, in this cell; then say</t>
+          <t>Cell 4 verifies the pack - Cell 4: check the run folder against its own record.</t>
         </is>
       </c>
       <c r="R266" s="3" t="inlineStr">
         <is>
-          <t>notebook_settings; open_current; open_store; run_pipeline</t>
-        </is>
-      </c>
-      <c r="S266" s="3" t="inlineStr">
-        <is>
-          <t>shown in full at 02.04.07.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
+          <t>LiveValues; live; notebook_settings; verify_evidence_pack</t>
+        </is>
+      </c>
+      <c r="S266" s="3" t="inlineStr"/>
+    </row>
+    <row r="267" outlineLevel="1">
       <c r="A267" s="3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B267" s="3" t="inlineStr"/>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="C267" s="3" t="inlineStr"/>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr"/>
@@ -27237,42 +27225,46 @@
       <c r="I267" s="3" t="inlineStr"/>
       <c r="J267" s="3" t="inlineStr"/>
       <c r="K267" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L267" s="3" t="inlineStr">
-        <is>
-          <t>verify</t>
+        <v>1</v>
+      </c>
+      <c r="L267" s="6" t="inlineStr">
+        <is>
+          <t>LiveValues</t>
         </is>
       </c>
       <c r="M267" s="5" t="inlineStr">
         <is>
-          <t>F-0153</t>
+          <t>F-0007</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>the notebook: four cells, each one call</t>
+          <t>live values (the token)</t>
         </is>
       </c>
       <c r="O267" s="3" t="inlineStr">
         <is>
-          <t>3774-3784</t>
+          <t>2712-2744</t>
         </is>
       </c>
       <c r="P267" s="3" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="Q267" s="3" t="inlineStr">
         <is>
-          <t>Cell 4 verifies the pack - Cell 4: check the run folder against its own record.</t>
+          <t>The three values chat() reads when it is CALLED: endpoint, token, user id. They live</t>
         </is>
       </c>
       <c r="R267" s="3" t="inlineStr">
         <is>
-          <t>LiveValues; live; notebook_settings; verify_evidence_pack</t>
-        </is>
-      </c>
-      <c r="S267" s="3" t="inlineStr"/>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S267" s="3" t="inlineStr">
+        <is>
+          <t>shown in full at 08.07.01</t>
+        </is>
+      </c>
     </row>
     <row r="268" outlineLevel="1">
       <c r="A268" s="3" t="inlineStr">
@@ -27282,7 +27274,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr"/>
@@ -27298,40 +27290,40 @@
       </c>
       <c r="L268" s="6" t="inlineStr">
         <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="M268" s="5" t="inlineStr">
+        <is>
+          <t>F-0083</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
+          <t>the notebook: four cells, each one call</t>
+        </is>
+      </c>
+      <c r="O268" s="3" t="inlineStr">
+        <is>
+          <t>3578-3587</t>
+        </is>
+      </c>
+      <c r="P268" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q268" s="3" t="inlineStr">
+        <is>
+          <t>The endpoint and token, read from the widgets at the moment chat() calls - a token pasted into widget 02</t>
+        </is>
+      </c>
+      <c r="R268" s="3" t="inlineStr">
+        <is>
           <t>LiveValues</t>
         </is>
       </c>
-      <c r="M268" s="5" t="inlineStr">
-        <is>
-          <t>F-0007</t>
-        </is>
-      </c>
-      <c r="N268" s="3" t="inlineStr">
-        <is>
-          <t>live values (the token)</t>
-        </is>
-      </c>
-      <c r="O268" s="3" t="inlineStr">
-        <is>
-          <t>2715-2747</t>
-        </is>
-      </c>
-      <c r="P268" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q268" s="3" t="inlineStr">
-        <is>
-          <t>The three values chat() reads when it is CALLED: endpoint, token, user id. They live</t>
-        </is>
-      </c>
-      <c r="R268" s="3" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
       <c r="S268" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 08.06.01</t>
+          <t>shown in full at 08.07</t>
         </is>
       </c>
     </row>
@@ -27343,7 +27335,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr"/>
@@ -27359,12 +27351,12 @@
       </c>
       <c r="L269" s="6" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>notebook_settings</t>
         </is>
       </c>
       <c r="M269" s="5" t="inlineStr">
         <is>
-          <t>F-0083</t>
+          <t>F-0096</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
@@ -27374,25 +27366,25 @@
       </c>
       <c r="O269" s="3" t="inlineStr">
         <is>
-          <t>3566-3575</t>
+          <t>3707-3708</t>
         </is>
       </c>
       <c r="P269" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q269" s="3" t="inlineStr">
         <is>
-          <t>The endpoint, token or user id, read from the widgets at the moment chat() calls: a token pasted</t>
+          <t>(no description)</t>
         </is>
       </c>
       <c r="R269" s="3" t="inlineStr">
         <is>
-          <t>LiveValues</t>
+          <t>make_settings</t>
         </is>
       </c>
       <c r="S269" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 08.06</t>
+          <t>shown in full at 02.04.07.07.01</t>
         </is>
       </c>
     </row>
@@ -27404,7 +27396,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr"/>
@@ -27420,44 +27412,40 @@
       </c>
       <c r="L270" s="6" t="inlineStr">
         <is>
-          <t>notebook_settings</t>
+          <t>verify_evidence_pack</t>
         </is>
       </c>
       <c r="M270" s="5" t="inlineStr">
         <is>
-          <t>F-0096</t>
+          <t>F-0154</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
-          <t>the notebook: four cells, each one call</t>
+          <t>determinations</t>
         </is>
       </c>
       <c r="O270" s="3" t="inlineStr">
         <is>
-          <t>3709-3712</t>
+          <t>3470-3511</t>
         </is>
       </c>
       <c r="P270" s="3" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="Q270" s="3" t="inlineStr">
         <is>
-          <t>(no description)</t>
+          <t>Works from a run folder and the Inputs folder alone. Returns rows (what was checked,</t>
         </is>
       </c>
       <c r="R270" s="3" t="inlineStr">
         <is>
-          <t>make_settings</t>
-        </is>
-      </c>
-      <c r="S270" s="3" t="inlineStr">
-        <is>
-          <t>shown in full at 02.04.07.07.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" outlineLevel="1">
+          <t>AuditStore; StepContext; content_hash; contents_of; engine_file_hashes; file_sha256; list_input_files; live; read_documentation; read_methodology; read_package; run_identity; to_plain</t>
+        </is>
+      </c>
+      <c r="S270" s="3" t="inlineStr"/>
+    </row>
+    <row r="271" outlineLevel="2">
       <c r="A271" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -27468,7 +27456,11 @@
           <t>04</t>
         </is>
       </c>
-      <c r="C271" s="3" t="inlineStr"/>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr"/>
       <c r="F271" s="3" t="inlineStr"/>
@@ -27477,42 +27469,46 @@
       <c r="I271" s="3" t="inlineStr"/>
       <c r="J271" s="3" t="inlineStr"/>
       <c r="K271" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L271" s="6" t="inlineStr">
-        <is>
-          <t>verify_evidence_pack</t>
+        <v>2</v>
+      </c>
+      <c r="L271" s="7" t="inlineStr">
+        <is>
+          <t>AuditStore</t>
         </is>
       </c>
       <c r="M271" s="5" t="inlineStr">
         <is>
-          <t>F-0154</t>
+          <t>F-0001</t>
         </is>
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>determinations</t>
+          <t>the audit store</t>
         </is>
       </c>
       <c r="O271" s="3" t="inlineStr">
         <is>
-          <t>3473-3514</t>
+          <t>2764-2870</t>
         </is>
       </c>
       <c r="P271" s="3" t="n">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="Q271" s="3" t="inlineStr">
         <is>
-          <t>Works from a run folder and the Inputs folder alone. Returns rows (what was checked,</t>
+          <t>The record of a run, as one workbook a person can open: _audit/Audit_Log.xlsx.</t>
         </is>
       </c>
       <c r="R271" s="3" t="inlineStr">
         <is>
-          <t>AuditStore; StepContext; content_hash; contents_of; engine_file_hashes; file_sha256; list_input_files; live; read_documentation; read_methodology; read_package; run_identity; to_plain</t>
-        </is>
-      </c>
-      <c r="S271" s="3" t="inlineStr"/>
+          <t>account; canonical_json; copy_whole; parts_of; to_plain</t>
+        </is>
+      </c>
+      <c r="S271" s="3" t="inlineStr">
+        <is>
+          <t>shown in full at 02.04.07.07.03.01</t>
+        </is>
+      </c>
     </row>
     <row r="272" outlineLevel="2">
       <c r="A272" s="3" t="inlineStr">
@@ -27527,7 +27523,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
@@ -27542,40 +27538,40 @@
       </c>
       <c r="L272" s="7" t="inlineStr">
         <is>
-          <t>AuditStore</t>
+          <t>StepContext</t>
         </is>
       </c>
       <c r="M272" s="5" t="inlineStr">
         <is>
-          <t>F-0001</t>
+          <t>F-0015</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>the audit store</t>
+          <t>data contracts (plan 2.3)</t>
         </is>
       </c>
       <c r="O272" s="3" t="inlineStr">
         <is>
-          <t>2767-2873</t>
+          <t>130-133</t>
         </is>
       </c>
       <c r="P272" s="3" t="n">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="Q272" s="3" t="inlineStr">
         <is>
-          <t>The record of a run, as one workbook a person can open: _audit/Audit_Log.xlsx.</t>
+          <t>What every step function receives. It never contains the access token.</t>
         </is>
       </c>
       <c r="R272" s="3" t="inlineStr">
         <is>
-          <t>account; canonical_json; copy_whole; parts_of; to_plain</t>
+          <t>Provenance</t>
         </is>
       </c>
       <c r="S272" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.04.07.07.03.01</t>
+          <t>shown in full at 02.04.07.07.04.04.02</t>
         </is>
       </c>
     </row>
@@ -27592,7 +27588,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
@@ -27607,22 +27603,22 @@
       </c>
       <c r="L273" s="7" t="inlineStr">
         <is>
-          <t>StepContext</t>
+          <t>content_hash</t>
         </is>
       </c>
       <c r="M273" s="5" t="inlineStr">
         <is>
-          <t>F-0015</t>
+          <t>F-0037</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>data contracts (plan 2.3)</t>
+          <t>canonical JSON and hashes</t>
         </is>
       </c>
       <c r="O273" s="3" t="inlineStr">
         <is>
-          <t>130-133</t>
+          <t>172-175</t>
         </is>
       </c>
       <c r="P273" s="3" t="n">
@@ -27630,17 +27626,17 @@
       </c>
       <c r="Q273" s="3" t="inlineStr">
         <is>
-          <t>What every step function receives. It never contains the access token.</t>
+          <t>The hash that makes a citation re-verifiable. It ignores white-space and</t>
         </is>
       </c>
       <c r="R273" s="3" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>normalise_text; sha256_text</t>
         </is>
       </c>
       <c r="S273" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.04.07.07.04.04.02</t>
+          <t>shown in full at 02.02.01.01.01</t>
         </is>
       </c>
     </row>
@@ -27657,7 +27653,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
@@ -27672,42 +27668,34 @@
       </c>
       <c r="L274" s="7" t="inlineStr">
         <is>
-          <t>content_hash</t>
+          <t>contents_of</t>
         </is>
       </c>
       <c r="M274" s="5" t="inlineStr">
         <is>
-          <t>F-0037</t>
+          <t>F-0038</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>canonical JSON and hashes</t>
+          <t>determinations</t>
         </is>
       </c>
       <c r="O274" s="3" t="inlineStr">
         <is>
-          <t>172-175</t>
+          <t>3451-3468</t>
         </is>
       </c>
       <c r="P274" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Q274" s="3" t="inlineStr">
         <is>
-          <t>The hash that makes a citation re-verifiable. It ignores white-space and</t>
-        </is>
-      </c>
-      <c r="R274" s="3" t="inlineStr">
-        <is>
-          <t>normalise_text; sha256_text</t>
-        </is>
-      </c>
-      <c r="S274" s="3" t="inlineStr">
-        <is>
-          <t>shown in full at 02.02.01.01.01</t>
-        </is>
-      </c>
+          <t>Every byte string a file holds, looking INSIDE the compressed ones: the call log is gzip,</t>
+        </is>
+      </c>
+      <c r="R274" s="3" t="inlineStr"/>
+      <c r="S274" s="3" t="inlineStr"/>
     </row>
     <row r="275" outlineLevel="2">
       <c r="A275" s="3" t="inlineStr">
@@ -27722,7 +27710,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
@@ -27737,34 +27725,42 @@
       </c>
       <c r="L275" s="7" t="inlineStr">
         <is>
-          <t>contents_of</t>
+          <t>engine_file_hashes</t>
         </is>
       </c>
       <c r="M275" s="5" t="inlineStr">
         <is>
-          <t>F-0038</t>
+          <t>F-0054</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>determinations</t>
+          <t>step 01: prepare-run</t>
         </is>
       </c>
       <c r="O275" s="3" t="inlineStr">
         <is>
-          <t>3454-3471</t>
+          <t>3005-3015</t>
         </is>
       </c>
       <c r="P275" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q275" s="3" t="inlineStr">
         <is>
-          <t>Every byte string a file holds, looking INSIDE the compressed ones: the call log is gzip,</t>
-        </is>
-      </c>
-      <c r="R275" s="3" t="inlineStr"/>
-      <c r="S275" s="3" t="inlineStr"/>
+          <t>SHA-256 of every file that makes up the engine (its code, which now holds its prompts and</t>
+        </is>
+      </c>
+      <c r="R275" s="3" t="inlineStr">
+        <is>
+          <t>file_sha256</t>
+        </is>
+      </c>
+      <c r="S275" s="3" t="inlineStr">
+        <is>
+          <t>shown in full at 01.02</t>
+        </is>
+      </c>
     </row>
     <row r="276" outlineLevel="2">
       <c r="A276" s="3" t="inlineStr">
@@ -27779,7 +27775,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr"/>
@@ -27794,40 +27790,40 @@
       </c>
       <c r="L276" s="7" t="inlineStr">
         <is>
-          <t>engine_file_hashes</t>
+          <t>file_sha256</t>
         </is>
       </c>
       <c r="M276" s="5" t="inlineStr">
         <is>
-          <t>F-0053</t>
+          <t>F-0056</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>step 01: prepare-run</t>
+          <t>rebuilding the outputs</t>
         </is>
       </c>
       <c r="O276" s="3" t="inlineStr">
         <is>
-          <t>3008-3018</t>
+          <t>3412-3415</t>
         </is>
       </c>
       <c r="P276" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q276" s="3" t="inlineStr">
         <is>
-          <t>SHA-256 of every file that makes up the engine (its code, which now holds its prompts and</t>
+          <t>SHA-256 of a file's bytes.</t>
         </is>
       </c>
       <c r="R276" s="3" t="inlineStr">
         <is>
-          <t>file_sha256</t>
+          <t>sha256_bytes</t>
         </is>
       </c>
       <c r="S276" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 01.02</t>
+          <t>shown in full at 01.02.01</t>
         </is>
       </c>
     </row>
@@ -27844,7 +27840,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
@@ -27859,40 +27855,40 @@
       </c>
       <c r="L277" s="7" t="inlineStr">
         <is>
-          <t>file_sha256</t>
+          <t>list_input_files</t>
         </is>
       </c>
       <c r="M277" s="5" t="inlineStr">
         <is>
-          <t>F-0055</t>
+          <t>F-0082</t>
         </is>
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
-          <t>rebuilding the outputs</t>
+          <t>the three Inputs folders of a project</t>
         </is>
       </c>
       <c r="O277" s="3" t="inlineStr">
         <is>
-          <t>3415-3418</t>
+          <t>623-634</t>
         </is>
       </c>
       <c r="P277" s="3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q277" s="3" t="inlineStr">
         <is>
-          <t>SHA-256 of a file's bytes.</t>
+          <t>The input files of a project, by corner, walking into folders; the folder each corner is</t>
         </is>
       </c>
       <c r="R277" s="3" t="inlineStr">
         <is>
-          <t>sha256_bytes</t>
+          <t>input_files</t>
         </is>
       </c>
       <c r="S277" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 01.02.01</t>
+          <t>shown in full at 02.04.07.07.04.04.04</t>
         </is>
       </c>
     </row>
@@ -27909,7 +27905,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>08</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr"/>
@@ -27924,40 +27920,40 @@
       </c>
       <c r="L278" s="7" t="inlineStr">
         <is>
-          <t>list_input_files</t>
+          <t>live</t>
         </is>
       </c>
       <c r="M278" s="5" t="inlineStr">
         <is>
-          <t>F-0082</t>
+          <t>F-0083</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>the three Inputs folders of a project</t>
+          <t>the notebook: four cells, each one call</t>
         </is>
       </c>
       <c r="O278" s="3" t="inlineStr">
         <is>
-          <t>623-634</t>
+          <t>3578-3587</t>
         </is>
       </c>
       <c r="P278" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q278" s="3" t="inlineStr">
         <is>
-          <t>The input files of a project, by corner, walking into folders; the folder each corner is</t>
+          <t>The endpoint and token, read from the widgets at the moment chat() calls - a token pasted into widget 02</t>
         </is>
       </c>
       <c r="R278" s="3" t="inlineStr">
         <is>
-          <t>input_files</t>
+          <t>LiveValues</t>
         </is>
       </c>
       <c r="S278" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.04.07.07.04.04.04</t>
+          <t>shown in full at 08.07</t>
         </is>
       </c>
     </row>
@@ -27974,7 +27970,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
@@ -27989,40 +27985,40 @@
       </c>
       <c r="L279" s="7" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>read_documentation</t>
         </is>
       </c>
       <c r="M279" s="5" t="inlineStr">
         <is>
-          <t>F-0083</t>
+          <t>F-0117</t>
         </is>
       </c>
       <c r="N279" s="3" t="inlineStr">
         <is>
-          <t>the notebook: four cells, each one call</t>
+          <t>the methodology and the documentation, read by Docling</t>
         </is>
       </c>
       <c r="O279" s="3" t="inlineStr">
         <is>
-          <t>3566-3575</t>
+          <t>1034-1036</t>
         </is>
       </c>
       <c r="P279" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q279" s="3" t="inlineStr">
         <is>
-          <t>The endpoint, token or user id, read from the widgets at the moment chat() calls: a token pasted</t>
+          <t>Step 03, read-documentation: the model documentation into chunks D-0001, D-0002, ...</t>
         </is>
       </c>
       <c r="R279" s="3" t="inlineStr">
         <is>
-          <t>LiveValues</t>
+          <t>read_corner</t>
         </is>
       </c>
       <c r="S279" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 08.06</t>
+          <t>shown in full at 02.02</t>
         </is>
       </c>
     </row>
@@ -28039,7 +28035,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr"/>
@@ -28054,12 +28050,12 @@
       </c>
       <c r="L280" s="7" t="inlineStr">
         <is>
-          <t>read_documentation</t>
+          <t>read_methodology</t>
         </is>
       </c>
       <c r="M280" s="5" t="inlineStr">
         <is>
-          <t>F-0117</t>
+          <t>F-0119</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
@@ -28069,7 +28065,7 @@
       </c>
       <c r="O280" s="3" t="inlineStr">
         <is>
-          <t>1037-1039</t>
+          <t>1030-1032</t>
         </is>
       </c>
       <c r="P280" s="3" t="n">
@@ -28077,7 +28073,7 @@
       </c>
       <c r="Q280" s="3" t="inlineStr">
         <is>
-          <t>Step 03, read-documentation: the model documentation into chunks D-0001, D-0002, ...</t>
+          <t>Step 02, read-methodology: the canonical methodology into chunks C-0001, C-0002, ...</t>
         </is>
       </c>
       <c r="R280" s="3" t="inlineStr">
@@ -28087,7 +28083,7 @@
       </c>
       <c r="S280" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.02</t>
+          <t>shown in full at 02.03</t>
         </is>
       </c>
     </row>
@@ -28104,7 +28100,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
@@ -28119,40 +28115,40 @@
       </c>
       <c r="L281" s="7" t="inlineStr">
         <is>
-          <t>read_methodology</t>
+          <t>read_package</t>
         </is>
       </c>
       <c r="M281" s="5" t="inlineStr">
         <is>
-          <t>F-0119</t>
+          <t>F-0120</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
         <is>
-          <t>the methodology and the documentation, read by Docling</t>
+          <t>step 04: read-package</t>
         </is>
       </c>
       <c r="O281" s="3" t="inlineStr">
         <is>
-          <t>1033-1035</t>
+          <t>1958-2033</t>
         </is>
       </c>
       <c r="P281" s="3" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="Q281" s="3" t="inlineStr">
         <is>
-          <t>Step 02, read-methodology: the canonical methodology into chunks C-0001, C-0002, ...</t>
+          <t>Step 04, read-package. Files are taken in a fixed order (DESCRIPTION, NAMESPACE, R/,</t>
         </is>
       </c>
       <c r="R281" s="3" t="inlineStr">
         <is>
-          <t>read_corner</t>
+          <t>StepResult; account; account_lines; account_of_package; data_reads; decode_text; file_units; finalise_units; flowr_package; is_archive; is_parsed_r_file; link_documentation_units; loose_package; package_rows; read_description; reason_for; sha256_bytes; strip_top_folder; swhid_content; to_plain; unpack_package</t>
         </is>
       </c>
       <c r="S281" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.03</t>
+          <t>shown in full at 02.04</t>
         </is>
       </c>
     </row>
@@ -28169,7 +28165,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
@@ -28184,40 +28180,36 @@
       </c>
       <c r="L282" s="7" t="inlineStr">
         <is>
-          <t>read_package</t>
+          <t>run_identity</t>
         </is>
       </c>
       <c r="M282" s="5" t="inlineStr">
         <is>
-          <t>F-0120</t>
+          <t>F-0129</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
         <is>
-          <t>step 04: read-package</t>
+          <t>Output.xlsx</t>
         </is>
       </c>
       <c r="O282" s="3" t="inlineStr">
         <is>
-          <t>1961-2036</t>
+          <t>3086-3089</t>
         </is>
       </c>
       <c r="P282" s="3" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="Q282" s="3" t="inlineStr">
         <is>
-          <t>Step 04, read-package. Files are taken in a fixed order (DESCRIPTION, NAMESPACE, R/,</t>
-        </is>
-      </c>
-      <c r="R282" s="3" t="inlineStr">
-        <is>
-          <t>StepResult; account; account_lines; account_of_package; data_reads; decode_text; file_units; finalise_units; flowr_package; is_archive; is_parsed_r_file; link_documentation_units; loose_package; package_rows; read_description; reason_for; sha256_bytes; strip_top_folder; swhid_content; to_plain; unpack_package</t>
-        </is>
-      </c>
+          <t>What ties a workbook to its run: also written into the workbook's properties.</t>
+        </is>
+      </c>
+      <c r="R282" s="3" t="inlineStr"/>
       <c r="S282" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.04</t>
+          <t>shown in full at 02.04.07.07.04.03.01.05</t>
         </is>
       </c>
     </row>
@@ -28234,7 +28226,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr"/>
@@ -28249,55 +28241,47 @@
       </c>
       <c r="L283" s="7" t="inlineStr">
         <is>
-          <t>run_identity</t>
+          <t>to_plain</t>
         </is>
       </c>
       <c r="M283" s="5" t="inlineStr">
         <is>
-          <t>F-0129</t>
+          <t>F-0144</t>
         </is>
       </c>
       <c r="N283" s="3" t="inlineStr">
         <is>
-          <t>Output.xlsx</t>
+          <t>canonical JSON and hashes</t>
         </is>
       </c>
       <c r="O283" s="3" t="inlineStr">
         <is>
-          <t>3089-3092</t>
+          <t>142-152</t>
         </is>
       </c>
       <c r="P283" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q283" s="3" t="inlineStr">
         <is>
-          <t>What ties a workbook to its run: also written into the workbook's properties.</t>
+          <t>Turn dataclasses, tuples and Decimals into plain JSON-ready values.</t>
         </is>
       </c>
       <c r="R283" s="3" t="inlineStr"/>
       <c r="S283" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.04.07.07.04.03.01.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" outlineLevel="2">
+          <t>shown in full at 02.01.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B284" s="3" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C284" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr"/>
+      <c r="C284" s="3" t="inlineStr"/>
       <c r="D284" s="3" t="inlineStr"/>
       <c r="E284" s="3" t="inlineStr"/>
       <c r="F284" s="3" t="inlineStr"/>
@@ -28306,102 +28290,49 @@
       <c r="I284" s="3" t="inlineStr"/>
       <c r="J284" s="3" t="inlineStr"/>
       <c r="K284" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L284" s="7" t="inlineStr">
-        <is>
-          <t>to_plain</t>
+        <v>0</v>
+      </c>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
       <c r="M284" s="5" t="inlineStr">
         <is>
-          <t>F-0144</t>
+          <t>F-0083</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
-          <t>canonical JSON and hashes</t>
+          <t>the notebook: four cells, each one call</t>
         </is>
       </c>
       <c r="O284" s="3" t="inlineStr">
         <is>
-          <t>142-152</t>
+          <t>3578-3587</t>
         </is>
       </c>
       <c r="P284" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q284" s="3" t="inlineStr">
         <is>
-          <t>Turn dataclasses, tuples and Decimals into plain JSON-ready values.</t>
-        </is>
-      </c>
-      <c r="R284" s="3" t="inlineStr"/>
+          <t>chat() reads the widgets - The endpoint and token, read from the widgets at the moment chat() calls - a token pasted into widget 02</t>
+        </is>
+      </c>
+      <c r="R284" s="3" t="inlineStr">
+        <is>
+          <t>LiveValues</t>
+        </is>
+      </c>
       <c r="S284" s="3" t="inlineStr">
         <is>
-          <t>shown in full at 02.01.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="inlineStr"/>
-      <c r="C285" s="3" t="inlineStr"/>
-      <c r="D285" s="3" t="inlineStr"/>
-      <c r="E285" s="3" t="inlineStr"/>
-      <c r="F285" s="3" t="inlineStr"/>
-      <c r="G285" s="3" t="inlineStr"/>
-      <c r="H285" s="3" t="inlineStr"/>
-      <c r="I285" s="3" t="inlineStr"/>
-      <c r="J285" s="3" t="inlineStr"/>
-      <c r="K285" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L285" s="3" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="M285" s="5" t="inlineStr">
-        <is>
-          <t>F-0083</t>
-        </is>
-      </c>
-      <c r="N285" s="3" t="inlineStr">
-        <is>
-          <t>the notebook: four cells, each one call</t>
-        </is>
-      </c>
-      <c r="O285" s="3" t="inlineStr">
-        <is>
-          <t>3566-3575</t>
-        </is>
-      </c>
-      <c r="P285" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q285" s="3" t="inlineStr">
-        <is>
-          <t>chat() reads the widgets - The endpoint, token or user id, read from the widgets at the moment chat() calls: a token pasted</t>
-        </is>
-      </c>
-      <c r="R285" s="3" t="inlineStr">
-        <is>
-          <t>LiveValues</t>
-        </is>
-      </c>
-      <c r="S285" s="3" t="inlineStr">
-        <is>
-          <t>shown in full at 08.06</t>
+          <t>shown in full at 08.07</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S285"/>
+  <autoFilter ref="A1:S284"/>
   <hyperlinks>
     <hyperlink ref="M2" location="'Functions'!A127"/>
     <hyperlink ref="M3" location="'Functions'!A11"/>
@@ -28648,45 +28579,44 @@
     <hyperlink ref="M244" location="'Functions'!A99"/>
     <hyperlink ref="M245" location="'Functions'!A140"/>
     <hyperlink ref="M246" location="'Functions'!A120"/>
-    <hyperlink ref="M247" location="'Functions'!A151"/>
-    <hyperlink ref="M248" location="'Functions'!A35"/>
-    <hyperlink ref="M249" location="'Functions'!A38"/>
-    <hyperlink ref="M250" location="'Functions'!A35"/>
-    <hyperlink ref="M251" location="'Functions'!A152"/>
+    <hyperlink ref="M247" location="'Functions'!A152"/>
+    <hyperlink ref="M248" location="'Functions'!A149"/>
+    <hyperlink ref="M249" location="'Functions'!A35"/>
+    <hyperlink ref="M250" location="'Functions'!A38"/>
+    <hyperlink ref="M251" location="'Functions'!A35"/>
     <hyperlink ref="M252" location="'Functions'!A154"/>
-    <hyperlink ref="M253" location="'Functions'!A152"/>
-    <hyperlink ref="M254" location="'Functions'!A153"/>
-    <hyperlink ref="M255" location="'Functions'!A37"/>
-    <hyperlink ref="M256" location="'Functions'!A99"/>
-    <hyperlink ref="M257" location="'Functions'!A154"/>
-    <hyperlink ref="M258" location="'Functions'!A149"/>
-    <hyperlink ref="M259" location="'Functions'!A113"/>
-    <hyperlink ref="M260" location="'Functions'!A149"/>
-    <hyperlink ref="M261" location="'Functions'!A150"/>
-    <hyperlink ref="M262" location="'Functions'!A153"/>
-    <hyperlink ref="M263" location="'Functions'!A158"/>
-    <hyperlink ref="M264" location="'Functions'!A156"/>
-    <hyperlink ref="M265" location="'Functions'!A109"/>
-    <hyperlink ref="M266" location="'Functions'!A158"/>
-    <hyperlink ref="M267" location="'Functions'!A159"/>
-    <hyperlink ref="M268" location="'Functions'!A113"/>
-    <hyperlink ref="M269" location="'Functions'!A149"/>
-    <hyperlink ref="M270" location="'Functions'!A155"/>
-    <hyperlink ref="M271" location="'Functions'!A145"/>
-    <hyperlink ref="M272" location="'Functions'!A115"/>
-    <hyperlink ref="M273" location="'Functions'!A10"/>
-    <hyperlink ref="M274" location="'Functions'!A18"/>
-    <hyperlink ref="M275" location="'Functions'!A144"/>
-    <hyperlink ref="M276" location="'Functions'!A126"/>
-    <hyperlink ref="M277" location="'Functions'!A141"/>
-    <hyperlink ref="M278" location="'Functions'!A34"/>
-    <hyperlink ref="M279" location="'Functions'!A149"/>
-    <hyperlink ref="M280" location="'Functions'!A49"/>
-    <hyperlink ref="M281" location="'Functions'!A48"/>
-    <hyperlink ref="M282" location="'Functions'!A98"/>
-    <hyperlink ref="M283" location="'Functions'!A130"/>
-    <hyperlink ref="M284" location="'Functions'!A12"/>
-    <hyperlink ref="M285" location="'Functions'!A149"/>
+    <hyperlink ref="M253" location="'Functions'!A153"/>
+    <hyperlink ref="M254" location="'Functions'!A37"/>
+    <hyperlink ref="M255" location="'Functions'!A99"/>
+    <hyperlink ref="M256" location="'Functions'!A154"/>
+    <hyperlink ref="M257" location="'Functions'!A150"/>
+    <hyperlink ref="M258" location="'Functions'!A113"/>
+    <hyperlink ref="M259" location="'Functions'!A150"/>
+    <hyperlink ref="M260" location="'Functions'!A151"/>
+    <hyperlink ref="M261" location="'Functions'!A153"/>
+    <hyperlink ref="M262" location="'Functions'!A158"/>
+    <hyperlink ref="M263" location="'Functions'!A156"/>
+    <hyperlink ref="M264" location="'Functions'!A109"/>
+    <hyperlink ref="M265" location="'Functions'!A158"/>
+    <hyperlink ref="M266" location="'Functions'!A159"/>
+    <hyperlink ref="M267" location="'Functions'!A113"/>
+    <hyperlink ref="M268" location="'Functions'!A150"/>
+    <hyperlink ref="M269" location="'Functions'!A155"/>
+    <hyperlink ref="M270" location="'Functions'!A145"/>
+    <hyperlink ref="M271" location="'Functions'!A115"/>
+    <hyperlink ref="M272" location="'Functions'!A10"/>
+    <hyperlink ref="M273" location="'Functions'!A18"/>
+    <hyperlink ref="M274" location="'Functions'!A144"/>
+    <hyperlink ref="M275" location="'Functions'!A126"/>
+    <hyperlink ref="M276" location="'Functions'!A141"/>
+    <hyperlink ref="M277" location="'Functions'!A34"/>
+    <hyperlink ref="M278" location="'Functions'!A150"/>
+    <hyperlink ref="M279" location="'Functions'!A49"/>
+    <hyperlink ref="M280" location="'Functions'!A48"/>
+    <hyperlink ref="M281" location="'Functions'!A98"/>
+    <hyperlink ref="M282" location="'Functions'!A130"/>
+    <hyperlink ref="M283" location="'Functions'!A12"/>
+    <hyperlink ref="M284" location="'Functions'!A150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29308,7 +29238,7 @@
         <v>780</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>15</v>
@@ -29326,7 +29256,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>7</v>
@@ -29347,7 +29277,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>92</v>
@@ -29368,7 +29298,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>4</v>
@@ -29385,7 +29315,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>13</v>
@@ -29406,7 +29336,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>297</v>
@@ -29427,7 +29357,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>98</v>
@@ -29448,7 +29378,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>100</v>
@@ -29469,7 +29399,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>159</v>
@@ -29490,7 +29420,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>33</v>
@@ -29511,7 +29441,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>1846</v>
+        <v>1843</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>192</v>
@@ -29532,7 +29462,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>23</v>
@@ -29549,7 +29479,7 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>484</v>
@@ -29570,7 +29500,7 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>2</v>
@@ -29587,7 +29517,7 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>2547</v>
+        <v>2544</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>6</v>
@@ -29604,7 +29534,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>8</v>
@@ -29621,7 +29551,7 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>3</v>
@@ -29638,7 +29568,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>2564</v>
+        <v>2561</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>9</v>
@@ -29655,7 +29585,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>2573</v>
+        <v>2570</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>4</v>
@@ -29672,7 +29602,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>2577</v>
+        <v>2574</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>4</v>
@@ -29689,7 +29619,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>2581</v>
+        <v>2578</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>5</v>
@@ -29710,7 +29640,7 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>4</v>
@@ -29727,7 +29657,7 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>2590</v>
+        <v>2587</v>
       </c>
       <c r="C55" s="3" t="n">
         <v>24</v>
@@ -29748,7 +29678,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>2614</v>
+        <v>2611</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>99</v>
@@ -29769,7 +29699,7 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>2713</v>
+        <v>2710</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>36</v>
@@ -29790,7 +29720,7 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>2749</v>
+        <v>2746</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>140</v>
@@ -29811,7 +29741,7 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>2889</v>
+        <v>2886</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>8</v>
@@ -29828,7 +29758,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>2897</v>
+        <v>2894</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>100</v>
@@ -29849,7 +29779,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>64</v>
@@ -29870,7 +29800,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>3061</v>
+        <v>3058</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>230</v>
@@ -29891,7 +29821,7 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>3291</v>
+        <v>3288</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>123</v>
@@ -29912,7 +29842,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>3414</v>
+        <v>3411</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>39</v>
@@ -29933,7 +29863,7 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>3453</v>
+        <v>3450</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>100</v>
@@ -29954,7 +29884,7 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>3553</v>
+        <v>3550</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>233</v>
@@ -29964,7 +29894,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>check_chat; index_arguments; install; live; notebook_folder; notebook_settings; open_current; pip_said; review; setup; verify</t>
+          <t>check_chat; databricks_user; install; live; notebook_folder; notebook_settings; open_current; pip_said; review; setup; verify</t>
         </is>
       </c>
     </row>

--- a/Engine_Map.xlsx
+++ b/Engine_Map.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>3782 lines, 158 functions and classes, 65 sections</t>
+          <t>3819 lines, 158 functions and classes, 65 sections</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>832-836</t>
+          <t>869-873</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>838-844</t>
+          <t>875-881</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>846-857</t>
+          <t>883-894</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>859-866</t>
+          <t>896-903</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>868-890</t>
+          <t>905-927</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>892-916</t>
+          <t>929-953</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>918-928</t>
+          <t>955-965</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>930-935</t>
+          <t>967-972</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>939-958</t>
+          <t>976-995</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>960-961</t>
+          <t>997-998</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>963-1006</t>
+          <t>1000-1043</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1009-1011</t>
+          <t>1046-1048</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1013-1027</t>
+          <t>1050-1064</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1030-1032</t>
+          <t>1067-1069</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>1034-1036</t>
+          <t>1071-1073</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>1044-1045</t>
+          <t>1081-1082</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>1050-1053</t>
+          <t>1087-1090</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>1055-1076</t>
+          <t>1092-1113</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>1078-1090</t>
+          <t>1115-1127</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>1092-1112</t>
+          <t>1129-1149</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>1114-1119</t>
+          <t>1151-1156</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>1121-1130</t>
+          <t>1158-1167</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>1133-1137</t>
+          <t>1170-1174</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>1145-1151</t>
+          <t>1182-1188</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>1161-1176</t>
+          <t>1198-1213</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1178-1181</t>
+          <t>1215-1218</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1183-1192</t>
+          <t>1220-1229</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>1194-1220</t>
+          <t>1231-1257</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1222-1245</t>
+          <t>1259-1282</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>1247-1251</t>
+          <t>1284-1288</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1258-1341</t>
+          <t>1295-1378</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>1344-1346</t>
+          <t>1381-1383</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>1348-1352</t>
+          <t>1385-1389</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1391-1396</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>1361-1366</t>
+          <t>1398-1403</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>1368-1374</t>
+          <t>1405-1411</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>1376-1400</t>
+          <t>1413-1437</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1402-1423</t>
+          <t>1439-1460</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>1425-1450</t>
+          <t>1462-1487</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>1462-1465</t>
+          <t>1499-1502</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1468-1476</t>
+          <t>1505-1513</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1478-1493</t>
+          <t>1515-1530</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>1495-1529</t>
+          <t>1532-1566</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>1531-1549</t>
+          <t>1568-1586</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>1552-1564</t>
+          <t>1589-1601</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>1566-1603</t>
+          <t>1603-1640</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>1605-1628</t>
+          <t>1642-1665</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>1630-1649</t>
+          <t>1667-1686</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>1654-1664</t>
+          <t>1691-1701</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>1666-1688</t>
+          <t>1703-1725</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>1690-1743</t>
+          <t>1727-1780</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>1746-1752</t>
+          <t>1783-1789</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>1754-1770</t>
+          <t>1791-1807</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>1772-1801</t>
+          <t>1809-1838</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>1803-1808</t>
+          <t>1840-1845</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>1811-1841</t>
+          <t>1848-1878</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>1846-1851</t>
+          <t>1883-1888</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>1853-1855</t>
+          <t>1890-1892</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>1858-1892</t>
+          <t>1895-1929</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>1894-1915</t>
+          <t>1931-1952</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>1917-1936</t>
+          <t>1954-1973</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>1938-1955</t>
+          <t>1975-1992</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>1958-2033</t>
+          <t>1995-2070</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>2072-2097</t>
+          <t>2109-2134</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>2099-2121</t>
+          <t>2136-2158</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>2123-2480</t>
+          <t>2160-2517</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>2483-2488</t>
+          <t>2520-2525</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>2490-2505</t>
+          <t>2527-2542</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>2508-2536</t>
+          <t>2545-2573</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>2579-2580</t>
+          <t>2616-2617</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>2600-2609</t>
+          <t>2637-2646</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>2617-2623</t>
+          <t>2654-2660</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>2625-2630</t>
+          <t>2662-2667</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>2632-2649</t>
+          <t>2669-2686</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>2651-2658</t>
+          <t>2688-2695</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>2660-2686</t>
+          <t>2697-2723</t>
         </is>
       </c>
       <c r="F111" s="3" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>2688-2708</t>
+          <t>2725-2745</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>2712-2744</t>
+          <t>2749-2781</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>2751-2761</t>
+          <t>2788-2798</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>2764-2870</t>
+          <t>2801-2907</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>2872-2874</t>
+          <t>2909-2911</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>2878-2884</t>
+          <t>2915-2921</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>2895-2914</t>
+          <t>2932-2951</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>2916-2921</t>
+          <t>2953-2958</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>2924-2943</t>
+          <t>2961-2980</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>2945-2967</t>
+          <t>2982-3004</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>2969-2978</t>
+          <t>3006-3015</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>2980-2987</t>
+          <t>3017-3024</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>2989-2992</t>
+          <t>3026-3029</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>2998-3003</t>
+          <t>3035-3040</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>3005-3015</t>
+          <t>3042-3052</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>3017-3046</t>
+          <t>3054-3083</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>3048-3056</t>
+          <t>3085-3093</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>3065-3083</t>
+          <t>3102-3120</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>3086-3089</t>
+          <t>3123-3126</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>3091-3114</t>
+          <t>3128-3151</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>3124-3247</t>
+          <t>3161-3284</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>3249-3254</t>
+          <t>3286-3291</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>3257-3260</t>
+          <t>3294-3297</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>3263-3266</t>
+          <t>3300-3303</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>3269-3275</t>
+          <t>3306-3312</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>3277-3286</t>
+          <t>3314-3323</t>
         </is>
       </c>
       <c r="F137" s="3" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>3342-3344</t>
+          <t>3379-3381</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>3346-3391</t>
+          <t>3383-3428</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>3393-3409</t>
+          <t>3430-3446</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>3412-3415</t>
+          <t>3449-3452</t>
         </is>
       </c>
       <c r="F141" s="3" t="n">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>3418-3425</t>
+          <t>3455-3462</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>3427-3448</t>
+          <t>3464-3485</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>3451-3468</t>
+          <t>3488-3505</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>3470-3511</t>
+          <t>3507-3548</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>3513-3529</t>
+          <t>3550-3566</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>3531-3534</t>
+          <t>3568-3571</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>3536-3538</t>
+          <t>3573-3575</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>3562-3576</t>
+          <t>3599-3613</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>3578-3587</t>
+          <t>3615-3624</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>3589-3594</t>
+          <t>3626-3631</t>
         </is>
       </c>
       <c r="F151" s="3" t="n">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>3596-3649</t>
+          <t>3633-3686</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>3652-3661</t>
+          <t>3689-3698</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>3663-3705</t>
+          <t>3700-3742</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>3707-3708</t>
+          <t>3744-3745</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>3710-3731</t>
+          <t>3747-3768</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>3733-3746</t>
+          <t>3770-3783</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>3748-3769</t>
+          <t>3785-3806</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>3771-3781</t>
+          <t>3808-3818</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>3017-3046</t>
+          <t>3054-3083</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>3005-3015</t>
+          <t>3042-3052</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>3412-3415</t>
+          <t>3449-3452</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>2998-3003</t>
+          <t>3035-3040</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>3048-3056</t>
+          <t>3085-3093</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>3531-3534</t>
+          <t>3568-3571</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>3513-3529</t>
+          <t>3550-3566</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>1034-1036</t>
+          <t>1071-1073</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>892-916</t>
+          <t>929-953</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>868-890</t>
+          <t>905-927</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>838-844</t>
+          <t>875-881</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>846-857</t>
+          <t>883-894</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>838-844</t>
+          <t>875-881</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>832-836</t>
+          <t>869-873</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>960-961</t>
+          <t>997-998</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>1013-1027</t>
+          <t>1050-1064</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>1009-1011</t>
+          <t>1046-1048</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>918-928</t>
+          <t>955-965</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>930-935</t>
+          <t>967-972</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>939-958</t>
+          <t>976-995</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>963-1006</t>
+          <t>1000-1043</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>939-958</t>
+          <t>976-995</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>960-961</t>
+          <t>997-998</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>1030-1032</t>
+          <t>1067-1069</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>892-916</t>
+          <t>929-953</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>1958-2033</t>
+          <t>1995-2070</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>1811-1841</t>
+          <t>1848-1878</t>
         </is>
       </c>
       <c r="P56" s="3" t="n">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1391-1396</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>1425-1450</t>
+          <t>1462-1487</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>1361-1366</t>
+          <t>1398-1403</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1391-1396</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>1348-1352</t>
+          <t>1385-1389</t>
         </is>
       </c>
       <c r="P61" s="3" t="n">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>1858-1892</t>
+          <t>1895-1929</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>1772-1801</t>
+          <t>1809-1838</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>1044-1045</t>
+          <t>1081-1082</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>1754-1770</t>
+          <t>1791-1807</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P67" s="3" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>1746-1752</t>
+          <t>1783-1789</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>1690-1743</t>
+          <t>1727-1780</t>
         </is>
       </c>
       <c r="P69" s="3" t="n">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>1666-1688</t>
+          <t>1703-1725</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>1803-1808</t>
+          <t>1840-1845</t>
         </is>
       </c>
       <c r="P72" s="3" t="n">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>1754-1770</t>
+          <t>1791-1807</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P75" s="3" t="n">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>1654-1664</t>
+          <t>1691-1701</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>1044-1045</t>
+          <t>1081-1082</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>1605-1628</t>
+          <t>1642-1665</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>1552-1564</t>
+          <t>1589-1601</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>1846-1851</t>
+          <t>1883-1888</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>1853-1855</t>
+          <t>1890-1892</t>
         </is>
       </c>
       <c r="P85" s="3" t="n">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>3748-3769</t>
+          <t>3785-3806</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>3707-3708</t>
+          <t>3744-3745</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>2600-2609</t>
+          <t>2637-2646</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>3733-3746</t>
+          <t>3770-3783</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>2688-2708</t>
+          <t>2725-2745</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>2617-2623</t>
+          <t>2654-2660</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>960-961</t>
+          <t>997-998</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>2651-2658</t>
+          <t>2688-2695</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>2660-2686</t>
+          <t>2697-2723</t>
         </is>
       </c>
       <c r="P94" s="3" t="n">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>2632-2649</t>
+          <t>2669-2686</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>2625-2630</t>
+          <t>2662-2667</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>2632-2649</t>
+          <t>2669-2686</t>
         </is>
       </c>
       <c r="P98" s="3" t="n">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>2878-2884</t>
+          <t>2915-2921</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>2764-2870</t>
+          <t>2801-2907</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>2751-2761</t>
+          <t>2788-2798</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>2872-2874</t>
+          <t>2909-2911</t>
         </is>
       </c>
       <c r="P105" s="3" t="n">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>2924-2943</t>
+          <t>2961-2980</t>
         </is>
       </c>
       <c r="P108" s="3" t="n">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>2895-2914</t>
+          <t>2932-2951</t>
         </is>
       </c>
       <c r="P109" s="3" t="n">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>2878-2884</t>
+          <t>2915-2921</t>
         </is>
       </c>
       <c r="P110" s="3" t="n">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>3427-3448</t>
+          <t>3464-3485</t>
         </is>
       </c>
       <c r="P111" s="3" t="n">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>3393-3409</t>
+          <t>3430-3446</t>
         </is>
       </c>
       <c r="P112" s="3" t="n">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>3277-3286</t>
+          <t>3314-3323</t>
         </is>
       </c>
       <c r="P114" s="3" t="n">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>2579-2580</t>
+          <t>2616-2617</t>
         </is>
       </c>
       <c r="P115" s="3" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>3748-3769</t>
+          <t>3785-3806</t>
         </is>
       </c>
       <c r="P116" s="3" t="n">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>3748-3769</t>
+          <t>3785-3806</t>
         </is>
       </c>
       <c r="P117" s="3" t="n">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>3342-3344</t>
+          <t>3379-3381</t>
         </is>
       </c>
       <c r="P118" s="3" t="n">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>960-961</t>
+          <t>997-998</t>
         </is>
       </c>
       <c r="P119" s="3" t="n">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
-          <t>3086-3089</t>
+          <t>3123-3126</t>
         </is>
       </c>
       <c r="P120" s="3" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>3269-3275</t>
+          <t>3306-3312</t>
         </is>
       </c>
       <c r="P121" s="3" t="n">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>3124-3247</t>
+          <t>3161-3284</t>
         </is>
       </c>
       <c r="P122" s="3" t="n">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>3249-3254</t>
+          <t>3286-3291</t>
         </is>
       </c>
       <c r="P123" s="3" t="n">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>2508-2536</t>
+          <t>2545-2573</t>
         </is>
       </c>
       <c r="P124" s="3" t="n">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>1654-1664</t>
+          <t>1691-1701</t>
         </is>
       </c>
       <c r="P125" s="3" t="n">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>3257-3260</t>
+          <t>3294-3297</t>
         </is>
       </c>
       <c r="P126" s="3" t="n">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>3263-3266</t>
+          <t>3300-3303</t>
         </is>
       </c>
       <c r="P127" s="3" t="n">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>3091-3114</t>
+          <t>3128-3151</t>
         </is>
       </c>
       <c r="P128" s="3" t="n">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>3086-3089</t>
+          <t>3123-3126</t>
         </is>
       </c>
       <c r="P130" s="3" t="n">
@@ -17921,7 +17921,7 @@
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>3346-3391</t>
+          <t>3383-3428</t>
         </is>
       </c>
       <c r="P132" s="3" t="n">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>3065-3083</t>
+          <t>3102-3120</t>
         </is>
       </c>
       <c r="P133" s="3" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>2989-2992</t>
+          <t>3026-3029</t>
         </is>
       </c>
       <c r="P135" s="3" t="n">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>2751-2761</t>
+          <t>2788-2798</t>
         </is>
       </c>
       <c r="P139" s="3" t="n">
@@ -18597,7 +18597,7 @@
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>3412-3415</t>
+          <t>3449-3452</t>
         </is>
       </c>
       <c r="P140" s="3" t="n">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>960-961</t>
+          <t>997-998</t>
         </is>
       </c>
       <c r="P141" s="3" t="n">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>2989-2992</t>
+          <t>3026-3029</t>
         </is>
       </c>
       <c r="P142" s="3" t="n">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>3418-3425</t>
+          <t>3455-3462</t>
         </is>
       </c>
       <c r="P143" s="3" t="n">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>2916-2921</t>
+          <t>2953-2958</t>
         </is>
       </c>
       <c r="P144" s="3" t="n">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>2945-2967</t>
+          <t>2982-3004</t>
         </is>
       </c>
       <c r="P145" s="3" t="n">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>3427-3448</t>
+          <t>3464-3485</t>
         </is>
       </c>
       <c r="P152" s="3" t="n">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="O153" s="3" t="inlineStr">
         <is>
-          <t>2980-2987</t>
+          <t>3017-3024</t>
         </is>
       </c>
       <c r="P153" s="3" t="n">
@@ -19667,7 +19667,7 @@
       </c>
       <c r="O154" s="3" t="inlineStr">
         <is>
-          <t>2969-2978</t>
+          <t>3006-3015</t>
         </is>
       </c>
       <c r="P154" s="3" t="n">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="O155" s="3" t="inlineStr">
         <is>
-          <t>3748-3769</t>
+          <t>3785-3806</t>
         </is>
       </c>
       <c r="P155" s="3" t="n">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="O156" s="3" t="inlineStr">
         <is>
-          <t>1495-1529</t>
+          <t>1532-1566</t>
         </is>
       </c>
       <c r="P156" s="3" t="n">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P157" s="3" t="n">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="O158" s="3" t="inlineStr">
         <is>
-          <t>1247-1251</t>
+          <t>1284-1288</t>
         </is>
       </c>
       <c r="P158" s="3" t="n">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="O159" s="3" t="inlineStr">
         <is>
-          <t>1222-1245</t>
+          <t>1259-1282</t>
         </is>
       </c>
       <c r="P159" s="3" t="n">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="O160" s="3" t="inlineStr">
         <is>
-          <t>1161-1176</t>
+          <t>1198-1213</t>
         </is>
       </c>
       <c r="P160" s="3" t="n">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="O161" s="3" t="inlineStr">
         <is>
-          <t>1178-1181</t>
+          <t>1215-1218</t>
         </is>
       </c>
       <c r="P161" s="3" t="n">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="O162" s="3" t="inlineStr">
         <is>
-          <t>2072-2097</t>
+          <t>2109-2134</t>
         </is>
       </c>
       <c r="P162" s="3" t="n">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="O163" s="3" t="inlineStr">
         <is>
-          <t>3412-3415</t>
+          <t>3449-3452</t>
         </is>
       </c>
       <c r="P163" s="3" t="n">
@@ -20417,7 +20417,7 @@
       </c>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>2099-2121</t>
+          <t>2136-2158</t>
         </is>
       </c>
       <c r="P164" s="3" t="n">
@@ -20502,7 +20502,7 @@
       </c>
       <c r="O165" s="3" t="inlineStr">
         <is>
-          <t>1161-1176</t>
+          <t>1198-1213</t>
         </is>
       </c>
       <c r="P165" s="3" t="n">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="O166" s="3" t="inlineStr">
         <is>
-          <t>3748-3769</t>
+          <t>3785-3806</t>
         </is>
       </c>
       <c r="P166" s="3" t="n">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="O167" s="3" t="inlineStr">
         <is>
-          <t>1183-1192</t>
+          <t>1220-1229</t>
         </is>
       </c>
       <c r="P167" s="3" t="n">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="O168" s="3" t="inlineStr">
         <is>
-          <t>1258-1341</t>
+          <t>1295-1378</t>
         </is>
       </c>
       <c r="P168" s="3" t="n">
@@ -20830,7 +20830,7 @@
       </c>
       <c r="O169" s="3" t="inlineStr">
         <is>
-          <t>1145-1151</t>
+          <t>1182-1188</t>
         </is>
       </c>
       <c r="P169" s="3" t="n">
@@ -20911,7 +20911,7 @@
       </c>
       <c r="O170" s="3" t="inlineStr">
         <is>
-          <t>1344-1346</t>
+          <t>1381-1383</t>
         </is>
       </c>
       <c r="P170" s="3" t="n">
@@ -21000,7 +21000,7 @@
       </c>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>1145-1151</t>
+          <t>1182-1188</t>
         </is>
       </c>
       <c r="P171" s="3" t="n">
@@ -21069,7 +21069,7 @@
       </c>
       <c r="O172" s="3" t="inlineStr">
         <is>
-          <t>1566-1603</t>
+          <t>1603-1640</t>
         </is>
       </c>
       <c r="P172" s="3" t="n">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="O173" s="3" t="inlineStr">
         <is>
-          <t>1361-1366</t>
+          <t>1398-1403</t>
         </is>
       </c>
       <c r="P173" s="3" t="n">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="O174" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P174" s="3" t="n">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>1531-1549</t>
+          <t>1568-1586</t>
         </is>
       </c>
       <c r="P175" s="3" t="n">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="O176" s="3" t="inlineStr">
         <is>
-          <t>1478-1493</t>
+          <t>1515-1530</t>
         </is>
       </c>
       <c r="P176" s="3" t="n">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="O177" s="3" t="inlineStr">
         <is>
-          <t>1361-1366</t>
+          <t>1398-1403</t>
         </is>
       </c>
       <c r="P177" s="3" t="n">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="O178" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1391-1396</t>
         </is>
       </c>
       <c r="P178" s="3" t="n">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="O179" s="3" t="inlineStr">
         <is>
-          <t>1462-1465</t>
+          <t>1499-1502</t>
         </is>
       </c>
       <c r="P179" s="3" t="n">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="O180" s="3" t="inlineStr">
         <is>
-          <t>1425-1450</t>
+          <t>1462-1487</t>
         </is>
       </c>
       <c r="P180" s="3" t="n">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P181" s="3" t="n">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="O182" s="3" t="inlineStr">
         <is>
-          <t>1468-1476</t>
+          <t>1505-1513</t>
         </is>
       </c>
       <c r="P182" s="3" t="n">
@@ -21872,7 +21872,7 @@
       </c>
       <c r="O183" s="3" t="inlineStr">
         <is>
-          <t>1462-1465</t>
+          <t>1499-1502</t>
         </is>
       </c>
       <c r="P183" s="3" t="n">
@@ -21953,7 +21953,7 @@
       </c>
       <c r="O184" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P184" s="3" t="n">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="O185" s="3" t="inlineStr">
         <is>
-          <t>1133-1137</t>
+          <t>1170-1174</t>
         </is>
       </c>
       <c r="P185" s="3" t="n">
@@ -22103,7 +22103,7 @@
       </c>
       <c r="O186" s="3" t="inlineStr">
         <is>
-          <t>1376-1400</t>
+          <t>1413-1437</t>
         </is>
       </c>
       <c r="P186" s="3" t="n">
@@ -22172,7 +22172,7 @@
       </c>
       <c r="O187" s="3" t="inlineStr">
         <is>
-          <t>1402-1423</t>
+          <t>1439-1460</t>
         </is>
       </c>
       <c r="P187" s="3" t="n">
@@ -22249,7 +22249,7 @@
       </c>
       <c r="O188" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1391-1396</t>
         </is>
       </c>
       <c r="P188" s="3" t="n">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="O189" s="3" t="inlineStr">
         <is>
-          <t>1368-1374</t>
+          <t>1405-1411</t>
         </is>
       </c>
       <c r="P189" s="3" t="n">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="O192" s="3" t="inlineStr">
         <is>
-          <t>1348-1352</t>
+          <t>1385-1389</t>
         </is>
       </c>
       <c r="P192" s="3" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="O193" s="3" t="inlineStr">
         <is>
-          <t>1183-1192</t>
+          <t>1220-1229</t>
         </is>
       </c>
       <c r="P193" s="3" t="n">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="O194" s="3" t="inlineStr">
         <is>
-          <t>1630-1649</t>
+          <t>1667-1686</t>
         </is>
       </c>
       <c r="P194" s="3" t="n">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="O195" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P195" s="3" t="n">
@@ -22845,7 +22845,7 @@
       </c>
       <c r="O196" s="3" t="inlineStr">
         <is>
-          <t>1495-1529</t>
+          <t>1532-1566</t>
         </is>
       </c>
       <c r="P196" s="3" t="n">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="O197" s="3" t="inlineStr">
         <is>
-          <t>1917-1936</t>
+          <t>1954-1973</t>
         </is>
       </c>
       <c r="P197" s="3" t="n">
@@ -23507,7 +23507,7 @@
       </c>
       <c r="O206" s="3" t="inlineStr">
         <is>
-          <t>3412-3415</t>
+          <t>3449-3452</t>
         </is>
       </c>
       <c r="P206" s="3" t="n">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="O210" s="3" t="inlineStr">
         <is>
-          <t>1454-1460</t>
+          <t>1491-1497</t>
         </is>
       </c>
       <c r="P210" s="3" t="n">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="O211" s="3" t="inlineStr">
         <is>
-          <t>3412-3415</t>
+          <t>3449-3452</t>
         </is>
       </c>
       <c r="P211" s="3" t="n">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="O213" s="3" t="inlineStr">
         <is>
-          <t>1194-1220</t>
+          <t>1231-1257</t>
         </is>
       </c>
       <c r="P213" s="3" t="n">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="O215" s="3" t="inlineStr">
         <is>
-          <t>1161-1176</t>
+          <t>1198-1213</t>
         </is>
       </c>
       <c r="P215" s="3" t="n">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="O216" s="3" t="inlineStr">
         <is>
-          <t>1178-1181</t>
+          <t>1215-1218</t>
         </is>
       </c>
       <c r="P216" s="3" t="n">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="O217" s="3" t="inlineStr">
         <is>
-          <t>2072-2097</t>
+          <t>2109-2134</t>
         </is>
       </c>
       <c r="P217" s="3" t="n">
@@ -24295,7 +24295,7 @@
       </c>
       <c r="O218" s="3" t="inlineStr">
         <is>
-          <t>1247-1251</t>
+          <t>1284-1288</t>
         </is>
       </c>
       <c r="P218" s="3" t="n">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="O219" s="3" t="inlineStr">
         <is>
-          <t>1183-1192</t>
+          <t>1220-1229</t>
         </is>
       </c>
       <c r="P219" s="3" t="n">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="O220" s="3" t="inlineStr">
         <is>
-          <t>1050-1053</t>
+          <t>1087-1090</t>
         </is>
       </c>
       <c r="P220" s="3" t="n">
@@ -24486,7 +24486,7 @@
       </c>
       <c r="O221" s="3" t="inlineStr">
         <is>
-          <t>1853-1855</t>
+          <t>1890-1892</t>
         </is>
       </c>
       <c r="P221" s="3" t="n">
@@ -24547,7 +24547,7 @@
       </c>
       <c r="O222" s="3" t="inlineStr">
         <is>
-          <t>1894-1915</t>
+          <t>1931-1952</t>
         </is>
       </c>
       <c r="P222" s="3" t="n">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="O223" s="3" t="inlineStr">
         <is>
-          <t>1078-1090</t>
+          <t>1115-1127</t>
         </is>
       </c>
       <c r="P223" s="3" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="O224" s="3" t="inlineStr">
         <is>
-          <t>1938-1955</t>
+          <t>1975-1992</t>
         </is>
       </c>
       <c r="P224" s="3" t="n">
@@ -24718,7 +24718,7 @@
       </c>
       <c r="O225" s="3" t="inlineStr">
         <is>
-          <t>1121-1130</t>
+          <t>1158-1167</t>
         </is>
       </c>
       <c r="P225" s="3" t="n">
@@ -24893,7 +24893,7 @@
       </c>
       <c r="O228" s="3" t="inlineStr">
         <is>
-          <t>1114-1119</t>
+          <t>1151-1156</t>
         </is>
       </c>
       <c r="P228" s="3" t="n">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="O231" s="3" t="inlineStr">
         <is>
-          <t>1092-1112</t>
+          <t>1129-1149</t>
         </is>
       </c>
       <c r="P231" s="3" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="O232" s="3" t="inlineStr">
         <is>
-          <t>1055-1076</t>
+          <t>1092-1113</t>
         </is>
       </c>
       <c r="P232" s="3" t="n">
@@ -25186,7 +25186,7 @@
       </c>
       <c r="O233" s="3" t="inlineStr">
         <is>
-          <t>3536-3538</t>
+          <t>3573-3575</t>
         </is>
       </c>
       <c r="P233" s="3" t="n">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="O234" s="3" t="inlineStr">
         <is>
-          <t>2490-2505</t>
+          <t>2527-2542</t>
         </is>
       </c>
       <c r="P234" s="3" t="n">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="O235" s="3" t="inlineStr">
         <is>
-          <t>2123-2480</t>
+          <t>2160-2517</t>
         </is>
       </c>
       <c r="P235" s="3" t="n">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="O236" s="3" t="inlineStr">
         <is>
-          <t>1145-1151</t>
+          <t>1182-1188</t>
         </is>
       </c>
       <c r="P236" s="3" t="n">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="O237" s="3" t="inlineStr">
         <is>
-          <t>1354-1359</t>
+          <t>1391-1396</t>
         </is>
       </c>
       <c r="P237" s="3" t="n">
@@ -25499,7 +25499,7 @@
       </c>
       <c r="O238" s="3" t="inlineStr">
         <is>
-          <t>2099-2121</t>
+          <t>2136-2158</t>
         </is>
       </c>
       <c r="P238" s="3" t="n">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="O239" s="3" t="inlineStr">
         <is>
-          <t>2072-2097</t>
+          <t>2109-2134</t>
         </is>
       </c>
       <c r="P239" s="3" t="n">
@@ -25637,7 +25637,7 @@
       </c>
       <c r="O240" s="3" t="inlineStr">
         <is>
-          <t>1247-1251</t>
+          <t>1284-1288</t>
         </is>
       </c>
       <c r="P240" s="3" t="n">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="O241" s="3" t="inlineStr">
         <is>
-          <t>1222-1245</t>
+          <t>1259-1282</t>
         </is>
       </c>
       <c r="P241" s="3" t="n">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="O242" s="3" t="inlineStr">
         <is>
-          <t>2483-2488</t>
+          <t>2520-2525</t>
         </is>
       </c>
       <c r="P242" s="3" t="n">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O244" s="3" t="inlineStr">
         <is>
-          <t>2072-2097</t>
+          <t>2109-2134</t>
         </is>
       </c>
       <c r="P244" s="3" t="n">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="O245" s="3" t="inlineStr">
         <is>
-          <t>3393-3409</t>
+          <t>3430-3446</t>
         </is>
       </c>
       <c r="P245" s="3" t="n">
@@ -26007,7 +26007,7 @@
       </c>
       <c r="O246" s="3" t="inlineStr">
         <is>
-          <t>2924-2943</t>
+          <t>2961-2980</t>
         </is>
       </c>
       <c r="P246" s="3" t="n">
@@ -26064,7 +26064,7 @@
       </c>
       <c r="O247" s="3" t="inlineStr">
         <is>
-          <t>3596-3649</t>
+          <t>3633-3686</t>
         </is>
       </c>
       <c r="P247" s="3" t="n">
@@ -26121,7 +26121,7 @@
       </c>
       <c r="O248" s="3" t="inlineStr">
         <is>
-          <t>3562-3576</t>
+          <t>3599-3613</t>
         </is>
       </c>
       <c r="P248" s="3" t="n">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="O249" s="3" t="inlineStr">
         <is>
-          <t>832-836</t>
+          <t>869-873</t>
         </is>
       </c>
       <c r="P249" s="3" t="n">
@@ -26235,7 +26235,7 @@
       </c>
       <c r="O250" s="3" t="inlineStr">
         <is>
-          <t>859-866</t>
+          <t>896-903</t>
         </is>
       </c>
       <c r="P250" s="3" t="n">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="O251" s="3" t="inlineStr">
         <is>
-          <t>832-836</t>
+          <t>869-873</t>
         </is>
       </c>
       <c r="P251" s="3" t="n">
@@ -26361,7 +26361,7 @@
       </c>
       <c r="O252" s="3" t="inlineStr">
         <is>
-          <t>3663-3705</t>
+          <t>3700-3742</t>
         </is>
       </c>
       <c r="P252" s="3" t="n">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="O253" s="3" t="inlineStr">
         <is>
-          <t>3652-3661</t>
+          <t>3689-3698</t>
         </is>
       </c>
       <c r="P253" s="3" t="n">
@@ -26479,7 +26479,7 @@
       </c>
       <c r="O254" s="3" t="inlineStr">
         <is>
-          <t>846-857</t>
+          <t>883-894</t>
         </is>
       </c>
       <c r="P254" s="3" t="n">
@@ -26540,7 +26540,7 @@
       </c>
       <c r="O255" s="3" t="inlineStr">
         <is>
-          <t>2072-2097</t>
+          <t>2109-2134</t>
         </is>
       </c>
       <c r="P255" s="3" t="n">
@@ -26601,7 +26601,7 @@
       </c>
       <c r="O256" s="3" t="inlineStr">
         <is>
-          <t>3663-3705</t>
+          <t>3700-3742</t>
         </is>
       </c>
       <c r="P256" s="3" t="n">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="O257" s="3" t="inlineStr">
         <is>
-          <t>3578-3587</t>
+          <t>3615-3624</t>
         </is>
       </c>
       <c r="P257" s="3" t="n">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="O258" s="3" t="inlineStr">
         <is>
-          <t>2712-2744</t>
+          <t>2749-2781</t>
         </is>
       </c>
       <c r="P258" s="3" t="n">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="O259" s="3" t="inlineStr">
         <is>
-          <t>3578-3587</t>
+          <t>3615-3624</t>
         </is>
       </c>
       <c r="P259" s="3" t="n">
@@ -26849,7 +26849,7 @@
       </c>
       <c r="O260" s="3" t="inlineStr">
         <is>
-          <t>3589-3594</t>
+          <t>3626-3631</t>
         </is>
       </c>
       <c r="P260" s="3" t="n">
@@ -26902,7 +26902,7 @@
       </c>
       <c r="O261" s="3" t="inlineStr">
         <is>
-          <t>3652-3661</t>
+          <t>3689-3698</t>
         </is>
       </c>
       <c r="P261" s="3" t="n">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O262" s="3" t="inlineStr">
         <is>
-          <t>3748-3769</t>
+          <t>3785-3806</t>
         </is>
       </c>
       <c r="P262" s="3" t="n">
@@ -27016,7 +27016,7 @@
       </c>
       <c r="O263" s="3" t="inlineStr">
         <is>
-          <t>3710-3731</t>
+          <t>3747-3768</t>
         </is>
       </c>
       <c r="P263" s="3" t="n">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="O264" s="3" t="inlineStr">
         <is>
-          <t>2632-2649</t>
+          <t>2669-2686</t>
         </is>
       </c>
       <c r="P264" s="3" t="n">
@@ -27130,7 +27130,7 @@
       </c>
       <c r="O265" s="3" t="inlineStr">
         <is>
-          <t>3748-3769</t>
+          <t>3785-3806</t>
         </is>
       </c>
       <c r="P265" s="3" t="n">
@@ -27187,7 +27187,7 @@
       </c>
       <c r="O266" s="3" t="inlineStr">
         <is>
-          <t>3771-3781</t>
+          <t>3808-3818</t>
         </is>
       </c>
       <c r="P266" s="3" t="n">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="O267" s="3" t="inlineStr">
         <is>
-          <t>2712-2744</t>
+          <t>2749-2781</t>
         </is>
       </c>
       <c r="P267" s="3" t="n">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="O268" s="3" t="inlineStr">
         <is>
-          <t>3578-3587</t>
+          <t>3615-3624</t>
         </is>
       </c>
       <c r="P268" s="3" t="n">
@@ -27366,7 +27366,7 @@
       </c>
       <c r="O269" s="3" t="inlineStr">
         <is>
-          <t>3707-3708</t>
+          <t>3744-3745</t>
         </is>
       </c>
       <c r="P269" s="3" t="n">
@@ -27427,7 +27427,7 @@
       </c>
       <c r="O270" s="3" t="inlineStr">
         <is>
-          <t>3470-3511</t>
+          <t>3507-3548</t>
         </is>
       </c>
       <c r="P270" s="3" t="n">
@@ -27488,7 +27488,7 @@
       </c>
       <c r="O271" s="3" t="inlineStr">
         <is>
-          <t>2764-2870</t>
+          <t>2801-2907</t>
         </is>
       </c>
       <c r="P271" s="3" t="n">
@@ -27683,7 +27683,7 @@
       </c>
       <c r="O274" s="3" t="inlineStr">
         <is>
-          <t>3451-3468</t>
+          <t>3488-3505</t>
         </is>
       </c>
       <c r="P274" s="3" t="n">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="O275" s="3" t="inlineStr">
         <is>
-          <t>3005-3015</t>
+          <t>3042-3052</t>
         </is>
       </c>
       <c r="P275" s="3" t="n">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="O276" s="3" t="inlineStr">
         <is>
-          <t>3412-3415</t>
+          <t>3449-3452</t>
         </is>
       </c>
       <c r="P276" s="3" t="n">
@@ -27935,7 +27935,7 @@
       </c>
       <c r="O278" s="3" t="inlineStr">
         <is>
-          <t>3578-3587</t>
+          <t>3615-3624</t>
         </is>
       </c>
       <c r="P278" s="3" t="n">
@@ -28000,7 +28000,7 @@
       </c>
       <c r="O279" s="3" t="inlineStr">
         <is>
-          <t>1034-1036</t>
+          <t>1071-1073</t>
         </is>
       </c>
       <c r="P279" s="3" t="n">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="O280" s="3" t="inlineStr">
         <is>
-          <t>1030-1032</t>
+          <t>1067-1069</t>
         </is>
       </c>
       <c r="P280" s="3" t="n">
@@ -28130,7 +28130,7 @@
       </c>
       <c r="O281" s="3" t="inlineStr">
         <is>
-          <t>1958-2033</t>
+          <t>1995-2070</t>
         </is>
       </c>
       <c r="P281" s="3" t="n">
@@ -28195,7 +28195,7 @@
       </c>
       <c r="O282" s="3" t="inlineStr">
         <is>
-          <t>3086-3089</t>
+          <t>3123-3126</t>
         </is>
       </c>
       <c r="P282" s="3" t="n">
@@ -28309,7 +28309,7 @@
       </c>
       <c r="O284" s="3" t="inlineStr">
         <is>
-          <t>3578-3587</t>
+          <t>3615-3624</t>
         </is>
       </c>
       <c r="P284" s="3" t="n">
@@ -29238,7 +29238,7 @@
         <v>780</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>15</v>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>1040</v>
+        <v>1077</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>7</v>
@@ -29277,7 +29277,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>1047</v>
+        <v>1084</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>92</v>
@@ -29298,7 +29298,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1139</v>
+        <v>1176</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>4</v>
@@ -29315,7 +29315,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>1143</v>
+        <v>1180</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>13</v>
@@ -29336,7 +29336,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1156</v>
+        <v>1193</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>297</v>
@@ -29357,7 +29357,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>1453</v>
+        <v>1490</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>98</v>
@@ -29378,7 +29378,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>1551</v>
+        <v>1588</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>100</v>
@@ -29399,7 +29399,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>1651</v>
+        <v>1688</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>159</v>
@@ -29420,7 +29420,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>1810</v>
+        <v>1847</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>33</v>
@@ -29441,7 +29441,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>1843</v>
+        <v>1880</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>192</v>
@@ -29462,7 +29462,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>2035</v>
+        <v>2072</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>23</v>
@@ -29479,7 +29479,7 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>2058</v>
+        <v>2095</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>484</v>
@@ -29500,7 +29500,7 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>2542</v>
+        <v>2579</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>2</v>
@@ -29517,7 +29517,7 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>2544</v>
+        <v>2581</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>6</v>
@@ -29534,7 +29534,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2550</v>
+        <v>2587</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>8</v>
@@ -29551,7 +29551,7 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>2558</v>
+        <v>2595</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>3</v>
@@ -29568,7 +29568,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>2561</v>
+        <v>2598</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>9</v>
@@ -29585,7 +29585,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>2570</v>
+        <v>2607</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>4</v>
@@ -29602,7 +29602,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>2574</v>
+        <v>2611</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>4</v>
@@ -29619,7 +29619,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>2578</v>
+        <v>2615</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>5</v>
@@ -29640,7 +29640,7 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2583</v>
+        <v>2620</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>4</v>
@@ -29657,7 +29657,7 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>2587</v>
+        <v>2624</v>
       </c>
       <c r="C55" s="3" t="n">
         <v>24</v>
@@ -29678,7 +29678,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>2611</v>
+        <v>2648</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>99</v>
@@ -29699,7 +29699,7 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>2710</v>
+        <v>2747</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>36</v>
@@ -29720,7 +29720,7 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>2746</v>
+        <v>2783</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>140</v>
@@ -29741,7 +29741,7 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>2886</v>
+        <v>2923</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>8</v>
@@ -29758,7 +29758,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>2894</v>
+        <v>2931</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>100</v>
@@ -29779,7 +29779,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>2994</v>
+        <v>3031</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>64</v>
@@ -29800,7 +29800,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>3058</v>
+        <v>3095</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>230</v>
@@ -29821,7 +29821,7 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>3288</v>
+        <v>3325</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>123</v>
@@ -29842,7 +29842,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>3411</v>
+        <v>3448</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>39</v>
@@ -29863,7 +29863,7 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>3450</v>
+        <v>3487</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>100</v>
@@ -29884,7 +29884,7 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>3550</v>
+        <v>3587</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>233</v>

--- a/Engine_Map.xlsx
+++ b/Engine_Map.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>5663 lines, 239 functions and classes, 64 sections</t>
+          <t>5664 lines, 239 functions and classes, 64 sections</t>
         </is>
       </c>
     </row>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>The rows of Chunks_Canon and Chunks_Doc.</t>
+          <t>The rows of Chunks_Methodology and Chunks_Documentation.</t>
         </is>
       </c>
       <c r="H215" s="3" t="inlineStr"/>
@@ -11841,11 +11841,11 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>5363-5404</t>
+          <t>5363-5405</t>
         </is>
       </c>
       <c r="F226" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>5406-5422</t>
+          <t>5407-5423</t>
         </is>
       </c>
       <c r="F227" s="3" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>5424-5427</t>
+          <t>5425-5428</t>
         </is>
       </c>
       <c r="F228" s="3" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>5429-5431</t>
+          <t>5430-5432</t>
         </is>
       </c>
       <c r="F229" s="3" t="n">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>5455-5469</t>
+          <t>5456-5470</t>
         </is>
       </c>
       <c r="F230" s="3" t="n">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>5471-5480</t>
+          <t>5472-5481</t>
         </is>
       </c>
       <c r="F231" s="3" t="n">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>5482-5487</t>
+          <t>5483-5488</t>
         </is>
       </c>
       <c r="F232" s="3" t="n">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>5489-5531</t>
+          <t>5490-5532</t>
         </is>
       </c>
       <c r="F233" s="3" t="n">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>5533-5542</t>
+          <t>5534-5543</t>
         </is>
       </c>
       <c r="F234" s="3" t="n">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>5544-5586</t>
+          <t>5545-5587</t>
         </is>
       </c>
       <c r="F235" s="3" t="n">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>5588-5589</t>
+          <t>5589-5590</t>
         </is>
       </c>
       <c r="F236" s="3" t="n">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>5591-5612</t>
+          <t>5592-5613</t>
         </is>
       </c>
       <c r="F237" s="3" t="n">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>5614-5627</t>
+          <t>5615-5628</t>
         </is>
       </c>
       <c r="F238" s="3" t="n">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="F239" s="3" t="n">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>5652-5662</t>
+          <t>5653-5663</t>
         </is>
       </c>
       <c r="F240" s="3" t="n">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>5424-5427</t>
+          <t>5425-5428</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>5406-5422</t>
+          <t>5407-5423</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="P109" s="3" t="n">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>5588-5589</t>
+          <t>5589-5590</t>
         </is>
       </c>
       <c r="P110" s="3" t="n">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>5614-5627</t>
+          <t>5615-5628</t>
         </is>
       </c>
       <c r="P112" s="3" t="n">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="P138" s="3" t="n">
@@ -23252,7 +23252,7 @@
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="P139" s="3" t="n">
@@ -24045,7 +24045,7 @@
       </c>
       <c r="Q148" s="3" t="inlineStr">
         <is>
-          <t>The rows of Chunks_Canon and Chunks_Doc.</t>
+          <t>The rows of Chunks_Methodology and Chunks_Documentation.</t>
         </is>
       </c>
       <c r="R148" s="3" t="inlineStr"/>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="O176" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="P176" s="3" t="n">
@@ -39013,7 +39013,7 @@
       </c>
       <c r="O328" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="P328" s="3" t="n">
@@ -45138,7 +45138,7 @@
       </c>
       <c r="O413" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="P413" s="3" t="n">
@@ -45973,7 +45973,7 @@
       </c>
       <c r="O424" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="P424" s="3" t="n">
@@ -50373,7 +50373,7 @@
       </c>
       <c r="O488" s="3" t="inlineStr">
         <is>
-          <t>5429-5431</t>
+          <t>5430-5432</t>
         </is>
       </c>
       <c r="P488" s="3" t="n">
@@ -51316,7 +51316,7 @@
       </c>
       <c r="O503" s="3" t="inlineStr">
         <is>
-          <t>5489-5531</t>
+          <t>5490-5532</t>
         </is>
       </c>
       <c r="P503" s="3" t="n">
@@ -51373,7 +51373,7 @@
       </c>
       <c r="O504" s="3" t="inlineStr">
         <is>
-          <t>5455-5469</t>
+          <t>5456-5470</t>
         </is>
       </c>
       <c r="P504" s="3" t="n">
@@ -51487,7 +51487,7 @@
       </c>
       <c r="O506" s="3" t="inlineStr">
         <is>
-          <t>5544-5586</t>
+          <t>5545-5587</t>
         </is>
       </c>
       <c r="P506" s="3" t="n">
@@ -51548,7 +51548,7 @@
       </c>
       <c r="O507" s="3" t="inlineStr">
         <is>
-          <t>5533-5542</t>
+          <t>5534-5543</t>
         </is>
       </c>
       <c r="P507" s="3" t="n">
@@ -51601,7 +51601,7 @@
       </c>
       <c r="O508" s="3" t="inlineStr">
         <is>
-          <t>5471-5480</t>
+          <t>5472-5481</t>
         </is>
       </c>
       <c r="P508" s="3" t="n">
@@ -51727,7 +51727,7 @@
       </c>
       <c r="O510" s="3" t="inlineStr">
         <is>
-          <t>5471-5480</t>
+          <t>5472-5481</t>
         </is>
       </c>
       <c r="P510" s="3" t="n">
@@ -51788,7 +51788,7 @@
       </c>
       <c r="O511" s="3" t="inlineStr">
         <is>
-          <t>5482-5487</t>
+          <t>5483-5488</t>
         </is>
       </c>
       <c r="P511" s="3" t="n">
@@ -51841,7 +51841,7 @@
       </c>
       <c r="O512" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="P512" s="3" t="n">
@@ -51898,7 +51898,7 @@
       </c>
       <c r="O513" s="3" t="inlineStr">
         <is>
-          <t>5591-5612</t>
+          <t>5592-5613</t>
         </is>
       </c>
       <c r="P513" s="3" t="n">
@@ -52012,7 +52012,7 @@
       </c>
       <c r="O515" s="3" t="inlineStr">
         <is>
-          <t>5629-5650</t>
+          <t>5630-5651</t>
         </is>
       </c>
       <c r="P515" s="3" t="n">
@@ -52069,7 +52069,7 @@
       </c>
       <c r="O516" s="3" t="inlineStr">
         <is>
-          <t>5652-5662</t>
+          <t>5653-5663</t>
         </is>
       </c>
       <c r="P516" s="3" t="n">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="O518" s="3" t="inlineStr">
         <is>
-          <t>5471-5480</t>
+          <t>5472-5481</t>
         </is>
       </c>
       <c r="P518" s="3" t="n">
@@ -52248,7 +52248,7 @@
       </c>
       <c r="O519" s="3" t="inlineStr">
         <is>
-          <t>5588-5589</t>
+          <t>5589-5590</t>
         </is>
       </c>
       <c r="P519" s="3" t="n">
@@ -52309,11 +52309,11 @@
       </c>
       <c r="O520" s="3" t="inlineStr">
         <is>
-          <t>5363-5404</t>
+          <t>5363-5405</t>
         </is>
       </c>
       <c r="P520" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q520" s="3" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
       </c>
       <c r="O528" s="3" t="inlineStr">
         <is>
-          <t>5471-5480</t>
+          <t>5472-5481</t>
         </is>
       </c>
       <c r="P528" s="3" t="n">
@@ -53191,7 +53191,7 @@
       </c>
       <c r="O534" s="3" t="inlineStr">
         <is>
-          <t>5471-5480</t>
+          <t>5472-5481</t>
         </is>
       </c>
       <c r="P534" s="3" t="n">
@@ -55037,7 +55037,7 @@
         <v>5343</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>5</v>
@@ -55055,7 +55055,7 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>5443</v>
+        <v>5444</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>221</v>

--- a/Engine_Map.xlsx
+++ b/Engine_Map.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Engine_Info'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Functions'!$A$1:$K$239</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Function_Map'!$A$1:$S$533</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sections'!$A$1:$E$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sections'!$A$1:$E$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Records'!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>5647 lines, 238 functions and classes, 64 sections</t>
+          <t>5636 lines, 238 functions and classes, 63 sections</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>80-83</t>
+          <t>79-82</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>86-88</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>92-95</t>
+          <t>91-94</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>98-104</t>
+          <t>97-103</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>107-110</t>
+          <t>106-109</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>113-116</t>
+          <t>112-115</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>119-121</t>
+          <t>118-120</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>125-131</t>
+          <t>124-130</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>134-137</t>
+          <t>133-136</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Which run and step produced a record, at which version, and from which AI exchange if any.</t>
+          <t>Which run and step produced a record, and from which AI exchange if any.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>142-145</t>
+          <t>141-144</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>148-151</t>
+          <t>147-150</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>154-164</t>
+          <t>153-163</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>166-168</t>
+          <t>165-167</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>169-171</t>
+          <t>168-170</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>172-174</t>
+          <t>171-173</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>175-177</t>
+          <t>174-176</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>184-187</t>
+          <t>183-186</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>189-191</t>
+          <t>188-190</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>208-230</t>
+          <t>207-229</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>232-235</t>
+          <t>231-234</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>237-254</t>
+          <t>236-253</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>256-266</t>
+          <t>255-265</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>278-298</t>
+          <t>277-297</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>302-307</t>
+          <t>301-306</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>312-334</t>
+          <t>311-333</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>353-358</t>
+          <t>347-352</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>360-365</t>
+          <t>354-359</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>368-375</t>
+          <t>362-369</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>379-382</t>
+          <t>373-376</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>384-390</t>
+          <t>378-384</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>392-420</t>
+          <t>386-414</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>422-493</t>
+          <t>416-487</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>495-501</t>
+          <t>489-495</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>503-533</t>
+          <t>497-527</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>535-554</t>
+          <t>529-548</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>581-585</t>
+          <t>575-579</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>587-592</t>
+          <t>581-586</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>594-600</t>
+          <t>588-594</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>602-609</t>
+          <t>596-603</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>617-645</t>
+          <t>611-639</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>652-673</t>
+          <t>646-667</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>675-683</t>
+          <t>669-677</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>685-688</t>
+          <t>679-682</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>695-716</t>
+          <t>689-710</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>719-736</t>
+          <t>713-730</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>785-807</t>
+          <t>779-801</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>810-867</t>
+          <t>804-861</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>934-940</t>
+          <t>928-934</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>942-958</t>
+          <t>936-952</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>960-997</t>
+          <t>954-991</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>999-1007</t>
+          <t>993-1001</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>1012-1038</t>
+          <t>1006-1032</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>1051-1058</t>
+          <t>1045-1052</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1065-1129</t>
+          <t>1059-1123</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1131-1142</t>
+          <t>1125-1136</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>1144-1153</t>
+          <t>1138-1147</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1155-1158</t>
+          <t>1149-1152</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>1160-1165</t>
+          <t>1154-1159</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1167-1169</t>
+          <t>1161-1163</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>1171-1191</t>
+          <t>1165-1185</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>1193-1207</t>
+          <t>1187-1201</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>1211-1217</t>
+          <t>1205-1211</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>1219-1226</t>
+          <t>1213-1220</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>1228-1247</t>
+          <t>1222-1241</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>1250-1285</t>
+          <t>1244-1279</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1287-1302</t>
+          <t>1281-1296</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>1304-1314</t>
+          <t>1298-1308</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>1316-1333</t>
+          <t>1310-1327</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>1335-1356</t>
+          <t>1329-1350</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1358-1375</t>
+          <t>1352-1369</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1379-1390</t>
+          <t>1373-1384</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>1400-1411</t>
+          <t>1394-1405</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>1418-1419</t>
+          <t>1412-1413</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>1529-1531</t>
+          <t>1523-1525</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>1533-1552</t>
+          <t>1527-1546</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>1554-1680</t>
+          <t>1548-1674</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>1682-1692</t>
+          <t>1676-1686</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>1694-1704</t>
+          <t>1688-1698</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>1708-1722</t>
+          <t>1702-1716</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>1725-1731</t>
+          <t>1719-1725</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>1737-1790</t>
+          <t>1731-1784</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>1792-1802</t>
+          <t>1786-1796</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>1804-1807</t>
+          <t>1798-1801</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>1814-1826</t>
+          <t>1808-1820</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>1828-1871</t>
+          <t>1822-1865</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>1876-1917</t>
+          <t>1870-1911</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>1923-1997</t>
+          <t>1917-1991</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>1999-2011</t>
+          <t>1993-2005</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>2014-2036</t>
+          <t>2008-2030</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>2041-2055</t>
+          <t>2035-2049</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>2065-2068</t>
+          <t>2059-2062</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>2071-2096</t>
+          <t>2065-2090</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>2098-2170</t>
+          <t>2092-2164</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>2172-2195</t>
+          <t>2166-2189</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>2197-2228</t>
+          <t>2191-2222</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>2230-2252</t>
+          <t>2224-2246</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>2257-2284</t>
+          <t>2251-2278</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>2286-2296</t>
+          <t>2280-2290</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>2298-2309</t>
+          <t>2292-2303</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>2313-2338</t>
+          <t>2307-2332</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>2340-2363</t>
+          <t>2334-2357</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>2365-2378</t>
+          <t>2359-2372</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>2381-2401</t>
+          <t>2375-2395</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>2403-2409</t>
+          <t>2397-2403</t>
         </is>
       </c>
       <c r="F111" s="3" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>2412-2433</t>
+          <t>2406-2427</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>2435-2442</t>
+          <t>2429-2436</t>
         </is>
       </c>
       <c r="F113" s="3" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>2451-2454</t>
+          <t>2445-2448</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>2456-2477</t>
+          <t>2450-2471</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>2479-2487</t>
+          <t>2473-2481</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>2489-2503</t>
+          <t>2483-2497</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>2505-2517</t>
+          <t>2499-2511</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>2519-2523</t>
+          <t>2513-2517</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>2525-2547</t>
+          <t>2519-2541</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>2549-2621</t>
+          <t>2543-2615</t>
         </is>
       </c>
       <c r="F121" s="3" t="n">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>2628-2650</t>
+          <t>2622-2644</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>2652-2710</t>
+          <t>2646-2704</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>2712-2725</t>
+          <t>2706-2719</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>2736-2751</t>
+          <t>2730-2745</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>2753-2807</t>
+          <t>2747-2801</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>2809-2817</t>
+          <t>2803-2811</t>
         </is>
       </c>
       <c r="F127" s="3" t="n">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>2821-2846</t>
+          <t>2815-2840</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>2848-2878</t>
+          <t>2842-2872</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>2880-2962</t>
+          <t>2874-2956</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>2964-2966</t>
+          <t>2958-2960</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>2968-2970</t>
+          <t>2962-2964</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>2978-2979</t>
+          <t>2972-2973</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>2984-2987</t>
+          <t>2978-2981</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>2989-3010</t>
+          <t>2983-3004</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>3012-3024</t>
+          <t>3006-3018</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>3026-3046</t>
+          <t>3020-3040</t>
         </is>
       </c>
       <c r="F137" s="3" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>3048-3053</t>
+          <t>3042-3047</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>3055-3064</t>
+          <t>3049-3058</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>3067-3071</t>
+          <t>3061-3065</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>3079-3085</t>
+          <t>3073-3079</t>
         </is>
       </c>
       <c r="F141" s="3" t="n">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>3095-3110</t>
+          <t>3089-3104</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>3112-3115</t>
+          <t>3106-3109</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>3117-3126</t>
+          <t>3111-3120</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>3128-3154</t>
+          <t>3122-3148</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>3156-3179</t>
+          <t>3150-3173</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>3181-3185</t>
+          <t>3175-3179</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>3192-3275</t>
+          <t>3186-3269</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>3278-3280</t>
+          <t>3272-3274</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>3282-3286</t>
+          <t>3276-3280</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>3288-3293</t>
+          <t>3282-3287</t>
         </is>
       </c>
       <c r="F151" s="3" t="n">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>3295-3300</t>
+          <t>3289-3294</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>3302-3308</t>
+          <t>3296-3302</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>3310-3334</t>
+          <t>3304-3328</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>3336-3357</t>
+          <t>3330-3351</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>3359-3384</t>
+          <t>3353-3378</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>3396-3399</t>
+          <t>3390-3393</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>3402-3410</t>
+          <t>3396-3404</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>3412-3427</t>
+          <t>3406-3421</t>
         </is>
       </c>
       <c r="F160" s="3" t="n">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>3429-3463</t>
+          <t>3423-3457</t>
         </is>
       </c>
       <c r="F161" s="3" t="n">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>3465-3483</t>
+          <t>3459-3477</t>
         </is>
       </c>
       <c r="F162" s="3" t="n">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>3487-3524</t>
+          <t>3481-3518</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>3527-3546</t>
+          <t>3521-3540</t>
         </is>
       </c>
       <c r="F164" s="3" t="n">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>3551-3561</t>
+          <t>3545-3555</t>
         </is>
       </c>
       <c r="F165" s="3" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>3563-3585</t>
+          <t>3557-3579</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>3587-3640</t>
+          <t>3581-3634</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>3643-3649</t>
+          <t>3637-3643</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>3651-3667</t>
+          <t>3645-3661</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>3669-3698</t>
+          <t>3663-3692</t>
         </is>
       </c>
       <c r="F170" s="3" t="n">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>3700-3705</t>
+          <t>3694-3699</t>
         </is>
       </c>
       <c r="F171" s="3" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>3708-3738</t>
+          <t>3702-3732</t>
         </is>
       </c>
       <c r="F172" s="3" t="n">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>3743-3748</t>
+          <t>3737-3742</t>
         </is>
       </c>
       <c r="F173" s="3" t="n">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>3750-3752</t>
+          <t>3744-3746</t>
         </is>
       </c>
       <c r="F174" s="3" t="n">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>3755-3791</t>
+          <t>3749-3785</t>
         </is>
       </c>
       <c r="F175" s="3" t="n">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>3793-3802</t>
+          <t>3787-3796</t>
         </is>
       </c>
       <c r="F176" s="3" t="n">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>3804-3819</t>
+          <t>3798-3813</t>
         </is>
       </c>
       <c r="F177" s="3" t="n">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>3821-3841</t>
+          <t>3815-3835</t>
         </is>
       </c>
       <c r="F178" s="3" t="n">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>3844-3920</t>
+          <t>3838-3914</t>
         </is>
       </c>
       <c r="F179" s="3" t="n">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>3959-3984</t>
+          <t>3953-3978</t>
         </is>
       </c>
       <c r="F180" s="3" t="n">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>3986-4008</t>
+          <t>3980-4002</t>
         </is>
       </c>
       <c r="F181" s="3" t="n">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>4010-4367</t>
+          <t>4004-4361</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>4370-4375</t>
+          <t>4364-4369</t>
         </is>
       </c>
       <c r="F183" s="3" t="n">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>4377-4392</t>
+          <t>4371-4386</t>
         </is>
       </c>
       <c r="F184" s="3" t="n">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>4395-4423</t>
+          <t>4389-4417</t>
         </is>
       </c>
       <c r="F185" s="3" t="n">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>4466-4467</t>
+          <t>4460-4461</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>4487-4496</t>
+          <t>4481-4490</t>
         </is>
       </c>
       <c r="F187" s="3" t="n">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>4504-4510</t>
+          <t>4498-4504</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>4512-4517</t>
+          <t>4506-4511</t>
         </is>
       </c>
       <c r="F189" s="3" t="n">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>4519-4536</t>
+          <t>4513-4530</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>4538-4545</t>
+          <t>4532-4539</t>
         </is>
       </c>
       <c r="F191" s="3" t="n">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>4547-4573</t>
+          <t>4541-4567</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>4575-4595</t>
+          <t>4569-4589</t>
         </is>
       </c>
       <c r="F193" s="3" t="n">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>4599-4631</t>
+          <t>4593-4625</t>
         </is>
       </c>
       <c r="F194" s="3" t="n">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>4638-4648</t>
+          <t>4632-4642</t>
         </is>
       </c>
       <c r="F195" s="3" t="n">
@@ -10367,11 +10367,11 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>4651-4757</t>
+          <t>4645-4750</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>4759-4761</t>
+          <t>4752-4754</t>
         </is>
       </c>
       <c r="F197" s="3" t="n">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>4765-4771</t>
+          <t>4758-4764</t>
         </is>
       </c>
       <c r="F198" s="3" t="n">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>4789-4794</t>
+          <t>4780-4785</t>
         </is>
       </c>
       <c r="F199" s="3" t="n">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>4797-4814</t>
+          <t>4788-4805</t>
         </is>
       </c>
       <c r="F200" s="3" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>4816-4838</t>
+          <t>4807-4829</t>
         </is>
       </c>
       <c r="F201" s="3" t="n">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>4840-4849</t>
+          <t>4831-4840</t>
         </is>
       </c>
       <c r="F202" s="3" t="n">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>4851-4858</t>
+          <t>4842-4849</t>
         </is>
       </c>
       <c r="F203" s="3" t="n">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>4860-4863</t>
+          <t>4851-4854</t>
         </is>
       </c>
       <c r="F204" s="3" t="n">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>4869-4874</t>
+          <t>4860-4865</t>
         </is>
       </c>
       <c r="F205" s="3" t="n">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>4876-4885</t>
+          <t>4867-4876</t>
         </is>
       </c>
       <c r="F206" s="3" t="n">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>4887-4916</t>
+          <t>4878-4907</t>
         </is>
       </c>
       <c r="F207" s="3" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>4918-4926</t>
+          <t>4909-4917</t>
         </is>
       </c>
       <c r="F208" s="3" t="n">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>4935-4953</t>
+          <t>4926-4944</t>
         </is>
       </c>
       <c r="F209" s="3" t="n">
@@ -11057,11 +11057,11 @@
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>4956-4959</t>
+          <t>4947-4949</t>
         </is>
       </c>
       <c r="F210" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
@@ -11104,11 +11104,11 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>4961-4990</t>
+          <t>4951-4979</t>
         </is>
       </c>
       <c r="F211" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>5000-5123</t>
+          <t>4989-5112</t>
         </is>
       </c>
       <c r="F212" s="3" t="n">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>5125-5130</t>
+          <t>5114-5119</t>
         </is>
       </c>
       <c r="F213" s="3" t="n">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>5133-5136</t>
+          <t>5122-5125</t>
         </is>
       </c>
       <c r="F214" s="3" t="n">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>5139-5142</t>
+          <t>5128-5131</t>
         </is>
       </c>
       <c r="F215" s="3" t="n">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>5145-5151</t>
+          <t>5134-5140</t>
         </is>
       </c>
       <c r="F216" s="3" t="n">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>5153-5162</t>
+          <t>5142-5151</t>
         </is>
       </c>
       <c r="F217" s="3" t="n">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>5218-5220</t>
+          <t>5207-5209</t>
         </is>
       </c>
       <c r="F218" s="3" t="n">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>5222-5267</t>
+          <t>5211-5256</t>
         </is>
       </c>
       <c r="F219" s="3" t="n">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>5269-5285</t>
+          <t>5258-5274</t>
         </is>
       </c>
       <c r="F220" s="3" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>5288-5291</t>
+          <t>5277-5280</t>
         </is>
       </c>
       <c r="F221" s="3" t="n">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>5294-5301</t>
+          <t>5283-5290</t>
         </is>
       </c>
       <c r="F222" s="3" t="n">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>5303-5324</t>
+          <t>5292-5313</t>
         </is>
       </c>
       <c r="F223" s="3" t="n">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>5327-5344</t>
+          <t>5316-5333</t>
         </is>
       </c>
       <c r="F224" s="3" t="n">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>5346-5388</t>
+          <t>5335-5377</t>
         </is>
       </c>
       <c r="F225" s="3" t="n">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>5390-5406</t>
+          <t>5379-5395</t>
         </is>
       </c>
       <c r="F226" s="3" t="n">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>5408-5411</t>
+          <t>5397-5400</t>
         </is>
       </c>
       <c r="F227" s="3" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>5413-5415</t>
+          <t>5402-5404</t>
         </is>
       </c>
       <c r="F228" s="3" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>5439-5453</t>
+          <t>5428-5442</t>
         </is>
       </c>
       <c r="F229" s="3" t="n">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>5455-5464</t>
+          <t>5444-5453</t>
         </is>
       </c>
       <c r="F230" s="3" t="n">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>5466-5471</t>
+          <t>5455-5460</t>
         </is>
       </c>
       <c r="F231" s="3" t="n">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>5473-5515</t>
+          <t>5462-5504</t>
         </is>
       </c>
       <c r="F232" s="3" t="n">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>5517-5526</t>
+          <t>5506-5515</t>
         </is>
       </c>
       <c r="F233" s="3" t="n">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>5528-5570</t>
+          <t>5517-5559</t>
         </is>
       </c>
       <c r="F234" s="3" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>5572-5573</t>
+          <t>5561-5562</t>
         </is>
       </c>
       <c r="F235" s="3" t="n">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>5575-5596</t>
+          <t>5564-5585</t>
         </is>
       </c>
       <c r="F236" s="3" t="n">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>5598-5611</t>
+          <t>5587-5600</t>
         </is>
       </c>
       <c r="F237" s="3" t="n">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="F238" s="3" t="n">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>5636-5646</t>
+          <t>5625-5635</t>
         </is>
       </c>
       <c r="F239" s="3" t="n">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>4887-4916</t>
+          <t>4878-4907</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>148-151</t>
+          <t>147-150</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>4876-4885</t>
+          <t>4867-4876</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>5288-5291</t>
+          <t>5277-5280</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>169-171</t>
+          <t>168-170</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>4869-4874</t>
+          <t>4860-4865</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>169-171</t>
+          <t>168-170</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>175-177</t>
+          <t>174-176</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>4918-4926</t>
+          <t>4909-4917</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>5408-5411</t>
+          <t>5397-5400</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>5390-5406</t>
+          <t>5379-5395</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>148-151</t>
+          <t>147-150</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>154-164</t>
+          <t>153-163</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>2968-2970</t>
+          <t>2962-2964</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>2880-2962</t>
+          <t>2874-2956</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>148-151</t>
+          <t>147-150</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>2071-2096</t>
+          <t>2065-2090</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>353-358</t>
+          <t>347-352</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>594-600</t>
+          <t>588-594</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>587-592</t>
+          <t>581-586</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>581-585</t>
+          <t>575-579</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
@@ -14585,7 +14585,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>581-585</t>
+          <t>575-579</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>695-716</t>
+          <t>689-710</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>594-600</t>
+          <t>588-594</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>602-609</t>
+          <t>596-603</t>
         </is>
       </c>
       <c r="P31" s="3" t="n">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>581-585</t>
+          <t>575-579</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>785-807</t>
+          <t>779-801</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>2753-2807</t>
+          <t>2747-2801</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>98-104</t>
+          <t>97-103</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>92-95</t>
+          <t>91-94</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>86-88</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>184-187</t>
+          <t>183-186</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>172-174</t>
+          <t>171-173</t>
         </is>
       </c>
       <c r="P43" s="3" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2809-2817</t>
+          <t>2803-2811</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>184-187</t>
+          <t>183-186</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>2736-2751</t>
+          <t>2730-2745</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>503-533</t>
+          <t>497-527</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>495-501</t>
+          <t>489-495</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>1708-1722</t>
+          <t>1702-1716</t>
         </is>
       </c>
       <c r="P49" s="3" t="n">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>92-95</t>
+          <t>91-94</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>1418-1419</t>
+          <t>1412-1413</t>
         </is>
       </c>
       <c r="P51" s="3" t="n">
@@ -16281,7 +16281,7 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>312-334</t>
+          <t>311-333</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>1682-1692</t>
+          <t>1676-1686</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>1554-1680</t>
+          <t>1548-1674</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>302-307</t>
+          <t>301-306</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
@@ -16585,7 +16585,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>1418-1419</t>
+          <t>1412-1413</t>
         </is>
       </c>
       <c r="P56" s="3" t="n">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>1725-1731</t>
+          <t>1719-1725</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>602-609</t>
+          <t>596-603</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>278-298</t>
+          <t>277-297</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>581-585</t>
+          <t>575-579</t>
         </is>
       </c>
       <c r="P61" s="3" t="n">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>1418-1419</t>
+          <t>1412-1413</t>
         </is>
       </c>
       <c r="P62" s="3" t="n">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>1533-1552</t>
+          <t>1527-1546</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
@@ -17221,7 +17221,7 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>1418-1419</t>
+          <t>1412-1413</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>232-235</t>
+          <t>231-234</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>581-585</t>
+          <t>575-579</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>581-585</t>
+          <t>575-579</t>
         </is>
       </c>
       <c r="P67" s="3" t="n">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>189-191</t>
+          <t>188-190</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
@@ -17594,7 +17594,7 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>1529-1531</t>
+          <t>1523-1525</t>
         </is>
       </c>
       <c r="P69" s="3" t="n">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>2014-2036</t>
+          <t>2008-2030</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>719-736</t>
+          <t>713-730</t>
         </is>
       </c>
       <c r="P71" s="3" t="n">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>2065-2068</t>
+          <t>2059-2062</t>
         </is>
       </c>
       <c r="P72" s="3" t="n">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P73" s="3" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P75" s="3" t="n">
@@ -18057,7 +18057,7 @@
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>2848-2878</t>
+          <t>2842-2872</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
@@ -18126,7 +18126,7 @@
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>2821-2846</t>
+          <t>2815-2840</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>652-673</t>
+          <t>646-667</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
@@ -18495,7 +18495,7 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>617-645</t>
+          <t>611-639</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P83" s="3" t="n">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
@@ -18730,7 +18730,7 @@
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>353-358</t>
+          <t>347-352</t>
         </is>
       </c>
       <c r="P85" s="3" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>3282-3286</t>
+          <t>3276-3280</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>675-683</t>
+          <t>669-677</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
@@ -19111,7 +19111,7 @@
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>685-688</t>
+          <t>679-682</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>999-1007</t>
+          <t>993-1001</t>
         </is>
       </c>
       <c r="P94" s="3" t="n">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>1999-2011</t>
+          <t>1993-2005</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>1923-1997</t>
+          <t>1917-1991</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P98" s="3" t="n">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>1876-1917</t>
+          <t>1870-1911</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>353-358</t>
+          <t>347-352</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>1876-1917</t>
+          <t>1870-1911</t>
         </is>
       </c>
       <c r="P101" s="3" t="n">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="O102" s="3" t="inlineStr">
         <is>
-          <t>2519-2523</t>
+          <t>2513-2517</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>685-688</t>
+          <t>679-682</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
@@ -20169,7 +20169,7 @@
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>2549-2621</t>
+          <t>2543-2615</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
@@ -20242,7 +20242,7 @@
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>2505-2517</t>
+          <t>2499-2511</t>
         </is>
       </c>
       <c r="P105" s="3" t="n">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="O106" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P106" s="3" t="n">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P107" s="3" t="n">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>2257-2284</t>
+          <t>2251-2278</t>
         </is>
       </c>
       <c r="P108" s="3" t="n">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="P109" s="3" t="n">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>5572-5573</t>
+          <t>5561-5562</t>
         </is>
       </c>
       <c r="P110" s="3" t="n">
@@ -20732,7 +20732,7 @@
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>4487-4496</t>
+          <t>4481-4490</t>
         </is>
       </c>
       <c r="P111" s="3" t="n">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>5598-5611</t>
+          <t>5587-5600</t>
         </is>
       </c>
       <c r="P112" s="3" t="n">
@@ -20902,7 +20902,7 @@
       </c>
       <c r="O113" s="3" t="inlineStr">
         <is>
-          <t>4575-4595</t>
+          <t>4569-4589</t>
         </is>
       </c>
       <c r="P113" s="3" t="n">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>4504-4510</t>
+          <t>4498-4504</t>
         </is>
       </c>
       <c r="P114" s="3" t="n">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>4538-4545</t>
+          <t>4532-4539</t>
         </is>
       </c>
       <c r="P115" s="3" t="n">
@@ -21161,7 +21161,7 @@
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>4547-4573</t>
+          <t>4541-4567</t>
         </is>
       </c>
       <c r="P116" s="3" t="n">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>4519-4536</t>
+          <t>4513-4530</t>
         </is>
       </c>
       <c r="P117" s="3" t="n">
@@ -21335,7 +21335,7 @@
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>4512-4517</t>
+          <t>4506-4511</t>
         </is>
       </c>
       <c r="P118" s="3" t="n">
@@ -21420,7 +21420,7 @@
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>172-174</t>
+          <t>171-173</t>
         </is>
       </c>
       <c r="P119" s="3" t="n">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
-          <t>4519-4536</t>
+          <t>4513-4530</t>
         </is>
       </c>
       <c r="P120" s="3" t="n">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>4765-4771</t>
+          <t>4758-4764</t>
         </is>
       </c>
       <c r="P121" s="3" t="n">
@@ -21687,11 +21687,11 @@
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>4651-4757</t>
+          <t>4645-4750</t>
         </is>
       </c>
       <c r="P122" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q122" s="3" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P123" s="3" t="n">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>166-168</t>
+          <t>165-167</t>
         </is>
       </c>
       <c r="P124" s="3" t="n">
@@ -21958,7 +21958,7 @@
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>154-164</t>
+          <t>153-163</t>
         </is>
       </c>
       <c r="P125" s="3" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>4638-4648</t>
+          <t>4632-4642</t>
         </is>
       </c>
       <c r="P126" s="3" t="n">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>4759-4761</t>
+          <t>4752-4754</t>
         </is>
       </c>
       <c r="P127" s="3" t="n">
@@ -22217,7 +22217,7 @@
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>154-164</t>
+          <t>153-163</t>
         </is>
       </c>
       <c r="P128" s="3" t="n">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P129" s="3" t="n">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>4797-4814</t>
+          <t>4788-4805</t>
         </is>
       </c>
       <c r="P130" s="3" t="n">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>4765-4771</t>
+          <t>4758-4764</t>
         </is>
       </c>
       <c r="P131" s="3" t="n">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>5303-5324</t>
+          <t>5292-5313</t>
         </is>
       </c>
       <c r="P132" s="3" t="n">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>5269-5285</t>
+          <t>5258-5274</t>
         </is>
       </c>
       <c r="P133" s="3" t="n">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="O134" s="3" t="inlineStr">
         <is>
-          <t>166-168</t>
+          <t>165-167</t>
         </is>
       </c>
       <c r="P134" s="3" t="n">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>5153-5162</t>
+          <t>5142-5151</t>
         </is>
       </c>
       <c r="P135" s="3" t="n">
@@ -22937,7 +22937,7 @@
       </c>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>4466-4467</t>
+          <t>4460-4461</t>
         </is>
       </c>
       <c r="P136" s="3" t="n">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="P137" s="3" t="n">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="P138" s="3" t="n">
@@ -23212,7 +23212,7 @@
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>5218-5220</t>
+          <t>5207-5209</t>
         </is>
       </c>
       <c r="P139" s="3" t="n">
@@ -23297,11 +23297,11 @@
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>4956-4959</t>
+          <t>4947-4949</t>
         </is>
       </c>
       <c r="P140" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q140" s="3" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>5145-5151</t>
+          <t>5134-5140</t>
         </is>
       </c>
       <c r="P141" s="3" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>5000-5123</t>
+          <t>4989-5112</t>
         </is>
       </c>
       <c r="P142" s="3" t="n">
@@ -23560,7 +23560,7 @@
       </c>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>5125-5130</t>
+          <t>5114-5119</t>
         </is>
       </c>
       <c r="P143" s="3" t="n">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>4395-4423</t>
+          <t>4389-4417</t>
         </is>
       </c>
       <c r="P144" s="3" t="n">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>3551-3561</t>
+          <t>3545-3555</t>
         </is>
       </c>
       <c r="P145" s="3" t="n">
@@ -23819,7 +23819,7 @@
       </c>
       <c r="O146" s="3" t="inlineStr">
         <is>
-          <t>2978-2979</t>
+          <t>2972-2973</t>
         </is>
       </c>
       <c r="P146" s="3" t="n">
@@ -23904,7 +23904,7 @@
       </c>
       <c r="O147" s="3" t="inlineStr">
         <is>
-          <t>5133-5136</t>
+          <t>5122-5125</t>
         </is>
       </c>
       <c r="P147" s="3" t="n">
@@ -23989,7 +23989,7 @@
       </c>
       <c r="O148" s="3" t="inlineStr">
         <is>
-          <t>5139-5142</t>
+          <t>5128-5131</t>
         </is>
       </c>
       <c r="P148" s="3" t="n">
@@ -24074,11 +24074,11 @@
       </c>
       <c r="O149" s="3" t="inlineStr">
         <is>
-          <t>4961-4990</t>
+          <t>4951-4979</t>
         </is>
       </c>
       <c r="P149" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q149" s="3" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
       </c>
       <c r="O150" s="3" t="inlineStr">
         <is>
-          <t>166-168</t>
+          <t>165-167</t>
         </is>
       </c>
       <c r="P150" s="3" t="n">
@@ -24256,11 +24256,11 @@
       </c>
       <c r="O151" s="3" t="inlineStr">
         <is>
-          <t>4956-4959</t>
+          <t>4947-4949</t>
         </is>
       </c>
       <c r="P151" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q151" s="3" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>172-174</t>
+          <t>171-173</t>
         </is>
       </c>
       <c r="P152" s="3" t="n">
@@ -24434,7 +24434,7 @@
       </c>
       <c r="O153" s="3" t="inlineStr">
         <is>
-          <t>5222-5267</t>
+          <t>5211-5256</t>
         </is>
       </c>
       <c r="P153" s="3" t="n">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="O154" s="3" t="inlineStr">
         <is>
-          <t>4935-4953</t>
+          <t>4926-4944</t>
         </is>
       </c>
       <c r="P154" s="3" t="n">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="O155" s="3" t="inlineStr">
         <is>
-          <t>80-83</t>
+          <t>79-82</t>
         </is>
       </c>
       <c r="P155" s="3" t="n">
@@ -24697,7 +24697,7 @@
       </c>
       <c r="O156" s="3" t="inlineStr">
         <is>
-          <t>4860-4863</t>
+          <t>4851-4854</t>
         </is>
       </c>
       <c r="P156" s="3" t="n">
@@ -24782,7 +24782,7 @@
       </c>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>256-266</t>
+          <t>255-265</t>
         </is>
       </c>
       <c r="P157" s="3" t="n">
@@ -24871,7 +24871,7 @@
       </c>
       <c r="O158" s="3" t="inlineStr">
         <is>
-          <t>602-609</t>
+          <t>596-603</t>
         </is>
       </c>
       <c r="P158" s="3" t="n">
@@ -24960,7 +24960,7 @@
       </c>
       <c r="O159" s="3" t="inlineStr">
         <is>
-          <t>232-235</t>
+          <t>231-234</t>
         </is>
       </c>
       <c r="P159" s="3" t="n">
@@ -25049,7 +25049,7 @@
       </c>
       <c r="O160" s="3" t="inlineStr">
         <is>
-          <t>4638-4648</t>
+          <t>4632-4642</t>
         </is>
       </c>
       <c r="P160" s="3" t="n">
@@ -25138,7 +25138,7 @@
       </c>
       <c r="O161" s="3" t="inlineStr">
         <is>
-          <t>5288-5291</t>
+          <t>5277-5280</t>
         </is>
       </c>
       <c r="P161" s="3" t="n">
@@ -25231,7 +25231,7 @@
       </c>
       <c r="O162" s="3" t="inlineStr">
         <is>
-          <t>4860-4863</t>
+          <t>4851-4854</t>
         </is>
       </c>
       <c r="P162" s="3" t="n">
@@ -25320,7 +25320,7 @@
       </c>
       <c r="O163" s="3" t="inlineStr">
         <is>
-          <t>5294-5301</t>
+          <t>5283-5290</t>
         </is>
       </c>
       <c r="P163" s="3" t="n">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>4789-4794</t>
+          <t>4780-4785</t>
         </is>
       </c>
       <c r="P164" s="3" t="n">
@@ -25490,7 +25490,7 @@
       </c>
       <c r="O165" s="3" t="inlineStr">
         <is>
-          <t>4816-4838</t>
+          <t>4807-4829</t>
         </is>
       </c>
       <c r="P165" s="3" t="n">
@@ -25579,7 +25579,7 @@
       </c>
       <c r="O166" s="3" t="inlineStr">
         <is>
-          <t>134-137</t>
+          <t>133-136</t>
         </is>
       </c>
       <c r="P166" s="3" t="n">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="Q166" s="3" t="inlineStr">
         <is>
-          <t>Which run and step produced a record, at which version, and from which AI exchange if any.</t>
+          <t>Which run and step produced a record, and from which AI exchange if any.</t>
         </is>
       </c>
       <c r="R166" s="3" t="inlineStr"/>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="O167" s="3" t="inlineStr">
         <is>
-          <t>142-145</t>
+          <t>141-144</t>
         </is>
       </c>
       <c r="P167" s="3" t="n">
@@ -25753,7 +25753,7 @@
       </c>
       <c r="O168" s="3" t="inlineStr">
         <is>
-          <t>134-137</t>
+          <t>133-136</t>
         </is>
       </c>
       <c r="P168" s="3" t="n">
@@ -25761,7 +25761,7 @@
       </c>
       <c r="Q168" s="3" t="inlineStr">
         <is>
-          <t>Which run and step produced a record, at which version, and from which AI exchange if any.</t>
+          <t>Which run and step produced a record, and from which AI exchange if any.</t>
         </is>
       </c>
       <c r="R168" s="3" t="inlineStr"/>
@@ -25842,7 +25842,7 @@
       </c>
       <c r="O169" s="3" t="inlineStr">
         <is>
-          <t>148-151</t>
+          <t>147-150</t>
         </is>
       </c>
       <c r="P169" s="3" t="n">
@@ -25931,7 +25931,7 @@
       </c>
       <c r="O170" s="3" t="inlineStr">
         <is>
-          <t>1400-1411</t>
+          <t>1394-1405</t>
         </is>
       </c>
       <c r="P170" s="3" t="n">
@@ -26020,7 +26020,7 @@
       </c>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>1012-1038</t>
+          <t>1006-1032</t>
         </is>
       </c>
       <c r="P171" s="3" t="n">
@@ -26105,7 +26105,7 @@
       </c>
       <c r="O172" s="3" t="inlineStr">
         <is>
-          <t>5303-5324</t>
+          <t>5292-5313</t>
         </is>
       </c>
       <c r="P172" s="3" t="n">
@@ -26198,7 +26198,7 @@
       </c>
       <c r="O173" s="3" t="inlineStr">
         <is>
-          <t>4851-4858</t>
+          <t>4842-4849</t>
         </is>
       </c>
       <c r="P173" s="3" t="n">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="O174" s="3" t="inlineStr">
         <is>
-          <t>4840-4849</t>
+          <t>4831-4840</t>
         </is>
       </c>
       <c r="P174" s="3" t="n">
@@ -26372,7 +26372,7 @@
       </c>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="P175" s="3" t="n">
@@ -26453,7 +26453,7 @@
       </c>
       <c r="O176" s="3" t="inlineStr">
         <is>
-          <t>169-171</t>
+          <t>168-170</t>
         </is>
       </c>
       <c r="P176" s="3" t="n">
@@ -26526,7 +26526,7 @@
       </c>
       <c r="O177" s="3" t="inlineStr">
         <is>
-          <t>2479-2487</t>
+          <t>2473-2481</t>
         </is>
       </c>
       <c r="P177" s="3" t="n">
@@ -26603,7 +26603,7 @@
       </c>
       <c r="O178" s="3" t="inlineStr">
         <is>
-          <t>2519-2523</t>
+          <t>2513-2517</t>
         </is>
       </c>
       <c r="P178" s="3" t="n">
@@ -26680,7 +26680,7 @@
       </c>
       <c r="O179" s="3" t="inlineStr">
         <is>
-          <t>2451-2454</t>
+          <t>2445-2448</t>
         </is>
       </c>
       <c r="P179" s="3" t="n">
@@ -26761,7 +26761,7 @@
       </c>
       <c r="O180" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P180" s="3" t="n">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>2456-2477</t>
+          <t>2450-2471</t>
         </is>
       </c>
       <c r="P181" s="3" t="n">
@@ -26911,7 +26911,7 @@
       </c>
       <c r="O182" s="3" t="inlineStr">
         <is>
-          <t>2451-2454</t>
+          <t>2445-2448</t>
         </is>
       </c>
       <c r="P182" s="3" t="n">
@@ -26988,7 +26988,7 @@
       </c>
       <c r="O183" s="3" t="inlineStr">
         <is>
-          <t>2489-2503</t>
+          <t>2483-2497</t>
         </is>
       </c>
       <c r="P183" s="3" t="n">
@@ -27065,7 +27065,7 @@
       </c>
       <c r="O184" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P184" s="3" t="n">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="O185" s="3" t="inlineStr">
         <is>
-          <t>1737-1790</t>
+          <t>1731-1784</t>
         </is>
       </c>
       <c r="P185" s="3" t="n">
@@ -27223,7 +27223,7 @@
       </c>
       <c r="O186" s="3" t="inlineStr">
         <is>
-          <t>353-358</t>
+          <t>347-352</t>
         </is>
       </c>
       <c r="P186" s="3" t="n">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="O187" s="3" t="inlineStr">
         <is>
-          <t>1725-1731</t>
+          <t>1719-1725</t>
         </is>
       </c>
       <c r="P187" s="3" t="n">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="O188" s="3" t="inlineStr">
         <is>
-          <t>360-365</t>
+          <t>354-359</t>
         </is>
       </c>
       <c r="P188" s="3" t="n">
@@ -27474,7 +27474,7 @@
       </c>
       <c r="O189" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P189" s="3" t="n">
@@ -27559,7 +27559,7 @@
       </c>
       <c r="O190" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P190" s="3" t="n">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="O191" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P191" s="3" t="n">
@@ -27721,7 +27721,7 @@
       </c>
       <c r="O192" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P192" s="3" t="n">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="O193" s="3" t="inlineStr">
         <is>
-          <t>1792-1802</t>
+          <t>1786-1796</t>
         </is>
       </c>
       <c r="P193" s="3" t="n">
@@ -27887,7 +27887,7 @@
       </c>
       <c r="O194" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P194" s="3" t="n">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="O195" s="3" t="inlineStr">
         <is>
-          <t>1737-1790</t>
+          <t>1731-1784</t>
         </is>
       </c>
       <c r="P195" s="3" t="n">
@@ -28057,7 +28057,7 @@
       </c>
       <c r="O196" s="3" t="inlineStr">
         <is>
-          <t>1804-1807</t>
+          <t>1798-1801</t>
         </is>
       </c>
       <c r="P196" s="3" t="n">
@@ -28126,7 +28126,7 @@
       </c>
       <c r="O197" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P197" s="3" t="n">
@@ -28199,7 +28199,7 @@
       </c>
       <c r="O198" s="3" t="inlineStr">
         <is>
-          <t>495-501</t>
+          <t>489-495</t>
         </is>
       </c>
       <c r="P198" s="3" t="n">
@@ -28272,7 +28272,7 @@
       </c>
       <c r="O199" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P199" s="3" t="n">
@@ -28345,7 +28345,7 @@
       </c>
       <c r="O200" s="3" t="inlineStr">
         <is>
-          <t>1737-1790</t>
+          <t>1731-1784</t>
         </is>
       </c>
       <c r="P200" s="3" t="n">
@@ -28422,7 +28422,7 @@
       </c>
       <c r="O201" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P201" s="3" t="n">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="O202" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P202" s="3" t="n">
@@ -28572,7 +28572,7 @@
       </c>
       <c r="O203" s="3" t="inlineStr">
         <is>
-          <t>2065-2068</t>
+          <t>2059-2062</t>
         </is>
       </c>
       <c r="P203" s="3" t="n">
@@ -28649,7 +28649,7 @@
       </c>
       <c r="O204" s="3" t="inlineStr">
         <is>
-          <t>2525-2547</t>
+          <t>2519-2541</t>
         </is>
       </c>
       <c r="P204" s="3" t="n">
@@ -28726,7 +28726,7 @@
       </c>
       <c r="O205" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P205" s="3" t="n">
@@ -28807,7 +28807,7 @@
       </c>
       <c r="O206" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P206" s="3" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="O207" s="3" t="inlineStr">
         <is>
-          <t>2519-2523</t>
+          <t>2513-2517</t>
         </is>
       </c>
       <c r="P207" s="3" t="n">
@@ -28957,7 +28957,7 @@
       </c>
       <c r="O208" s="3" t="inlineStr">
         <is>
-          <t>1694-1704</t>
+          <t>1688-1698</t>
         </is>
       </c>
       <c r="P208" s="3" t="n">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="O209" s="3" t="inlineStr">
         <is>
-          <t>92-95</t>
+          <t>91-94</t>
         </is>
       </c>
       <c r="P209" s="3" t="n">
@@ -29111,7 +29111,7 @@
       </c>
       <c r="O210" s="3" t="inlineStr">
         <is>
-          <t>1418-1419</t>
+          <t>1412-1413</t>
         </is>
       </c>
       <c r="P210" s="3" t="n">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="O211" s="3" t="inlineStr">
         <is>
-          <t>312-334</t>
+          <t>311-333</t>
         </is>
       </c>
       <c r="P211" s="3" t="n">
@@ -29265,7 +29265,7 @@
       </c>
       <c r="O212" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P212" s="3" t="n">
@@ -29342,7 +29342,7 @@
       </c>
       <c r="O213" s="3" t="inlineStr">
         <is>
-          <t>1682-1692</t>
+          <t>1676-1686</t>
         </is>
       </c>
       <c r="P213" s="3" t="n">
@@ -29419,7 +29419,7 @@
       </c>
       <c r="O214" s="3" t="inlineStr">
         <is>
-          <t>2519-2523</t>
+          <t>2513-2517</t>
         </is>
       </c>
       <c r="P214" s="3" t="n">
@@ -29492,7 +29492,7 @@
       </c>
       <c r="O215" s="3" t="inlineStr">
         <is>
-          <t>2230-2252</t>
+          <t>2224-2246</t>
         </is>
       </c>
       <c r="P215" s="3" t="n">
@@ -29569,7 +29569,7 @@
       </c>
       <c r="O216" s="3" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>86-88</t>
         </is>
       </c>
       <c r="P216" s="3" t="n">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="O217" s="3" t="inlineStr">
         <is>
-          <t>237-254</t>
+          <t>236-253</t>
         </is>
       </c>
       <c r="P217" s="3" t="n">
@@ -29727,7 +29727,7 @@
       </c>
       <c r="O218" s="3" t="inlineStr">
         <is>
-          <t>208-230</t>
+          <t>207-229</t>
         </is>
       </c>
       <c r="P218" s="3" t="n">
@@ -29812,7 +29812,7 @@
       </c>
       <c r="O219" s="3" t="inlineStr">
         <is>
-          <t>1358-1375</t>
+          <t>1352-1369</t>
         </is>
       </c>
       <c r="P219" s="3" t="n">
@@ -29901,7 +29901,7 @@
       </c>
       <c r="O220" s="3" t="inlineStr">
         <is>
-          <t>999-1007</t>
+          <t>993-1001</t>
         </is>
       </c>
       <c r="P220" s="3" t="n">
@@ -29990,7 +29990,7 @@
       </c>
       <c r="O221" s="3" t="inlineStr">
         <is>
-          <t>1160-1165</t>
+          <t>1154-1159</t>
         </is>
       </c>
       <c r="P221" s="3" t="n">
@@ -30079,7 +30079,7 @@
       </c>
       <c r="O222" s="3" t="inlineStr">
         <is>
-          <t>1155-1158</t>
+          <t>1149-1152</t>
         </is>
       </c>
       <c r="P222" s="3" t="n">
@@ -30168,7 +30168,7 @@
       </c>
       <c r="O223" s="3" t="inlineStr">
         <is>
-          <t>1144-1153</t>
+          <t>1138-1147</t>
         </is>
       </c>
       <c r="P223" s="3" t="n">
@@ -30253,7 +30253,7 @@
       </c>
       <c r="O224" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P224" s="3" t="n">
@@ -30342,7 +30342,7 @@
       </c>
       <c r="O225" s="3" t="inlineStr">
         <is>
-          <t>1167-1169</t>
+          <t>1161-1163</t>
         </is>
       </c>
       <c r="P225" s="3" t="n">
@@ -30431,7 +30431,7 @@
       </c>
       <c r="O226" s="3" t="inlineStr">
         <is>
-          <t>1155-1158</t>
+          <t>1149-1152</t>
         </is>
       </c>
       <c r="P226" s="3" t="n">
@@ -30524,7 +30524,7 @@
       </c>
       <c r="O227" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P227" s="3" t="n">
@@ -30613,7 +30613,7 @@
       </c>
       <c r="O228" s="3" t="inlineStr">
         <is>
-          <t>1228-1247</t>
+          <t>1222-1241</t>
         </is>
       </c>
       <c r="P228" s="3" t="n">
@@ -30702,7 +30702,7 @@
       </c>
       <c r="O229" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P229" s="3" t="n">
@@ -30791,7 +30791,7 @@
       </c>
       <c r="O230" s="3" t="inlineStr">
         <is>
-          <t>1211-1217</t>
+          <t>1205-1211</t>
         </is>
       </c>
       <c r="P230" s="3" t="n">
@@ -30876,7 +30876,7 @@
       </c>
       <c r="O231" s="3" t="inlineStr">
         <is>
-          <t>1219-1226</t>
+          <t>1213-1220</t>
         </is>
       </c>
       <c r="P231" s="3" t="n">
@@ -30965,7 +30965,7 @@
       </c>
       <c r="O232" s="3" t="inlineStr">
         <is>
-          <t>1211-1217</t>
+          <t>1205-1211</t>
         </is>
       </c>
       <c r="P232" s="3" t="n">
@@ -31054,7 +31054,7 @@
       </c>
       <c r="O233" s="3" t="inlineStr">
         <is>
-          <t>1219-1226</t>
+          <t>1213-1220</t>
         </is>
       </c>
       <c r="P233" s="3" t="n">
@@ -31147,7 +31147,7 @@
       </c>
       <c r="O234" s="3" t="inlineStr">
         <is>
-          <t>1065-1129</t>
+          <t>1059-1123</t>
         </is>
       </c>
       <c r="P234" s="3" t="n">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="O235" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P235" s="3" t="n">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="O236" s="3" t="inlineStr">
         <is>
-          <t>1051-1058</t>
+          <t>1045-1052</t>
         </is>
       </c>
       <c r="P236" s="3" t="n">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="O237" s="3" t="inlineStr">
         <is>
-          <t>1131-1142</t>
+          <t>1125-1136</t>
         </is>
       </c>
       <c r="P237" s="3" t="n">
@@ -31499,7 +31499,7 @@
       </c>
       <c r="O238" s="3" t="inlineStr">
         <is>
-          <t>1051-1058</t>
+          <t>1045-1052</t>
         </is>
       </c>
       <c r="P238" s="3" t="n">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="O239" s="3" t="inlineStr">
         <is>
-          <t>1193-1207</t>
+          <t>1187-1201</t>
         </is>
       </c>
       <c r="P239" s="3" t="n">
@@ -31673,7 +31673,7 @@
       </c>
       <c r="O240" s="3" t="inlineStr">
         <is>
-          <t>1171-1191</t>
+          <t>1165-1185</t>
         </is>
       </c>
       <c r="P240" s="3" t="n">
@@ -31762,7 +31762,7 @@
       </c>
       <c r="O241" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P241" s="3" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="O242" s="3" t="inlineStr">
         <is>
-          <t>1335-1356</t>
+          <t>1329-1350</t>
         </is>
       </c>
       <c r="P242" s="3" t="n">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="O243" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P243" s="3" t="n">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="O244" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P244" s="3" t="n">
@@ -32118,7 +32118,7 @@
       </c>
       <c r="O245" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P245" s="3" t="n">
@@ -32207,7 +32207,7 @@
       </c>
       <c r="O246" s="3" t="inlineStr">
         <is>
-          <t>1316-1333</t>
+          <t>1310-1327</t>
         </is>
       </c>
       <c r="P246" s="3" t="n">
@@ -32292,7 +32292,7 @@
       </c>
       <c r="O247" s="3" t="inlineStr">
         <is>
-          <t>1250-1285</t>
+          <t>1244-1279</t>
         </is>
       </c>
       <c r="P247" s="3" t="n">
@@ -32381,7 +32381,7 @@
       </c>
       <c r="O248" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P248" s="3" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="O249" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P249" s="3" t="n">
@@ -32555,7 +32555,7 @@
       </c>
       <c r="O250" s="3" t="inlineStr">
         <is>
-          <t>232-235</t>
+          <t>231-234</t>
         </is>
       </c>
       <c r="P250" s="3" t="n">
@@ -32632,7 +32632,7 @@
       </c>
       <c r="O251" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P251" s="3" t="n">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="O252" s="3" t="inlineStr">
         <is>
-          <t>2403-2409</t>
+          <t>2397-2403</t>
         </is>
       </c>
       <c r="P252" s="3" t="n">
@@ -32778,7 +32778,7 @@
       </c>
       <c r="O253" s="3" t="inlineStr">
         <is>
-          <t>422-493</t>
+          <t>416-487</t>
         </is>
       </c>
       <c r="P253" s="3" t="n">
@@ -32855,7 +32855,7 @@
       </c>
       <c r="O254" s="3" t="inlineStr">
         <is>
-          <t>353-358</t>
+          <t>347-352</t>
         </is>
       </c>
       <c r="P254" s="3" t="n">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="O255" s="3" t="inlineStr">
         <is>
-          <t>368-375</t>
+          <t>362-369</t>
         </is>
       </c>
       <c r="P255" s="3" t="n">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="O256" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P256" s="3" t="n">
@@ -33094,7 +33094,7 @@
       </c>
       <c r="O257" s="3" t="inlineStr">
         <is>
-          <t>392-420</t>
+          <t>386-414</t>
         </is>
       </c>
       <c r="P257" s="3" t="n">
@@ -33175,7 +33175,7 @@
       </c>
       <c r="O258" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P258" s="3" t="n">
@@ -33256,7 +33256,7 @@
       </c>
       <c r="O259" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P259" s="3" t="n">
@@ -33337,7 +33337,7 @@
       </c>
       <c r="O260" s="3" t="inlineStr">
         <is>
-          <t>384-390</t>
+          <t>378-384</t>
         </is>
       </c>
       <c r="P260" s="3" t="n">
@@ -33422,7 +33422,7 @@
       </c>
       <c r="O261" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P261" s="3" t="n">
@@ -33507,7 +33507,7 @@
       </c>
       <c r="O262" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P262" s="3" t="n">
@@ -33584,7 +33584,7 @@
       </c>
       <c r="O263" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P263" s="3" t="n">
@@ -33661,7 +33661,7 @@
       </c>
       <c r="O264" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P264" s="3" t="n">
@@ -33734,7 +33734,7 @@
       </c>
       <c r="O265" s="3" t="inlineStr">
         <is>
-          <t>1999-2011</t>
+          <t>1993-2005</t>
         </is>
       </c>
       <c r="P265" s="3" t="n">
@@ -33811,7 +33811,7 @@
       </c>
       <c r="O266" s="3" t="inlineStr">
         <is>
-          <t>3282-3286</t>
+          <t>3276-3280</t>
         </is>
       </c>
       <c r="P266" s="3" t="n">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="O267" s="3" t="inlineStr">
         <is>
-          <t>2098-2170</t>
+          <t>2092-2164</t>
         </is>
       </c>
       <c r="P267" s="3" t="n">
@@ -33961,7 +33961,7 @@
       </c>
       <c r="O268" s="3" t="inlineStr">
         <is>
-          <t>353-358</t>
+          <t>347-352</t>
         </is>
       </c>
       <c r="P268" s="3" t="n">
@@ -34042,7 +34042,7 @@
       </c>
       <c r="O269" s="3" t="inlineStr">
         <is>
-          <t>368-375</t>
+          <t>362-369</t>
         </is>
       </c>
       <c r="P269" s="3" t="n">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="O270" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P270" s="3" t="n">
@@ -34200,7 +34200,7 @@
       </c>
       <c r="O271" s="3" t="inlineStr">
         <is>
-          <t>2041-2055</t>
+          <t>2035-2049</t>
         </is>
       </c>
       <c r="P271" s="3" t="n">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="O272" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P272" s="3" t="n">
@@ -34362,7 +34362,7 @@
       </c>
       <c r="O273" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P273" s="3" t="n">
@@ -34439,7 +34439,7 @@
       </c>
       <c r="O274" s="3" t="inlineStr">
         <is>
-          <t>2381-2401</t>
+          <t>2375-2395</t>
         </is>
       </c>
       <c r="P274" s="3" t="n">
@@ -34520,7 +34520,7 @@
       </c>
       <c r="O275" s="3" t="inlineStr">
         <is>
-          <t>92-95</t>
+          <t>91-94</t>
         </is>
       </c>
       <c r="P275" s="3" t="n">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="O276" s="3" t="inlineStr">
         <is>
-          <t>1418-1419</t>
+          <t>1412-1413</t>
         </is>
       </c>
       <c r="P276" s="3" t="n">
@@ -34682,7 +34682,7 @@
       </c>
       <c r="O277" s="3" t="inlineStr">
         <is>
-          <t>1358-1375</t>
+          <t>1352-1369</t>
         </is>
       </c>
       <c r="P277" s="3" t="n">
@@ -34767,7 +34767,7 @@
       </c>
       <c r="O278" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P278" s="3" t="n">
@@ -34848,7 +34848,7 @@
       </c>
       <c r="O279" s="3" t="inlineStr">
         <is>
-          <t>2041-2055</t>
+          <t>2035-2049</t>
         </is>
       </c>
       <c r="P279" s="3" t="n">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="O280" s="3" t="inlineStr">
         <is>
-          <t>1828-1871</t>
+          <t>1822-1865</t>
         </is>
       </c>
       <c r="P280" s="3" t="n">
@@ -35018,7 +35018,7 @@
       </c>
       <c r="O281" s="3" t="inlineStr">
         <is>
-          <t>1418-1419</t>
+          <t>1412-1413</t>
         </is>
       </c>
       <c r="P281" s="3" t="n">
@@ -35103,7 +35103,7 @@
       </c>
       <c r="O282" s="3" t="inlineStr">
         <is>
-          <t>1814-1826</t>
+          <t>1808-1820</t>
         </is>
       </c>
       <c r="P282" s="3" t="n">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="O283" s="3" t="inlineStr">
         <is>
-          <t>1418-1419</t>
+          <t>1412-1413</t>
         </is>
       </c>
       <c r="P283" s="3" t="n">
@@ -35273,7 +35273,7 @@
       </c>
       <c r="O284" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P284" s="3" t="n">
@@ -35354,7 +35354,7 @@
       </c>
       <c r="O285" s="3" t="inlineStr">
         <is>
-          <t>1737-1790</t>
+          <t>1731-1784</t>
         </is>
       </c>
       <c r="P285" s="3" t="n">
@@ -35439,7 +35439,7 @@
       </c>
       <c r="O286" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P286" s="3" t="n">
@@ -35524,7 +35524,7 @@
       </c>
       <c r="O287" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P287" s="3" t="n">
@@ -35605,7 +35605,7 @@
       </c>
       <c r="O288" s="3" t="inlineStr">
         <is>
-          <t>1694-1704</t>
+          <t>1688-1698</t>
         </is>
       </c>
       <c r="P288" s="3" t="n">
@@ -35690,7 +35690,7 @@
       </c>
       <c r="O289" s="3" t="inlineStr">
         <is>
-          <t>172-174</t>
+          <t>171-173</t>
         </is>
       </c>
       <c r="P289" s="3" t="n">
@@ -35767,7 +35767,7 @@
       </c>
       <c r="O290" s="3" t="inlineStr">
         <is>
-          <t>2298-2309</t>
+          <t>2292-2303</t>
         </is>
       </c>
       <c r="P290" s="3" t="n">
@@ -35848,7 +35848,7 @@
       </c>
       <c r="O291" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P291" s="3" t="n">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="O292" s="3" t="inlineStr">
         <is>
-          <t>2041-2055</t>
+          <t>2035-2049</t>
         </is>
       </c>
       <c r="P292" s="3" t="n">
@@ -36014,7 +36014,7 @@
       </c>
       <c r="O293" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P293" s="3" t="n">
@@ -36095,7 +36095,7 @@
       </c>
       <c r="O294" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P294" s="3" t="n">
@@ -36180,7 +36180,7 @@
       </c>
       <c r="O295" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P295" s="3" t="n">
@@ -36257,7 +36257,7 @@
       </c>
       <c r="O296" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P296" s="3" t="n">
@@ -36334,7 +36334,7 @@
       </c>
       <c r="O297" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P297" s="3" t="n">
@@ -36415,7 +36415,7 @@
       </c>
       <c r="O298" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P298" s="3" t="n">
@@ -36492,7 +36492,7 @@
       </c>
       <c r="O299" s="3" t="inlineStr">
         <is>
-          <t>2340-2363</t>
+          <t>2334-2357</t>
         </is>
       </c>
       <c r="P299" s="3" t="n">
@@ -36573,7 +36573,7 @@
       </c>
       <c r="O300" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P300" s="3" t="n">
@@ -36658,7 +36658,7 @@
       </c>
       <c r="O301" s="3" t="inlineStr">
         <is>
-          <t>685-688</t>
+          <t>679-682</t>
         </is>
       </c>
       <c r="P301" s="3" t="n">
@@ -36743,7 +36743,7 @@
       </c>
       <c r="O302" s="3" t="inlineStr">
         <is>
-          <t>2065-2068</t>
+          <t>2059-2062</t>
         </is>
       </c>
       <c r="P302" s="3" t="n">
@@ -36828,7 +36828,7 @@
       </c>
       <c r="O303" s="3" t="inlineStr">
         <is>
-          <t>1999-2011</t>
+          <t>1993-2005</t>
         </is>
       </c>
       <c r="P303" s="3" t="n">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="O304" s="3" t="inlineStr">
         <is>
-          <t>2257-2284</t>
+          <t>2251-2278</t>
         </is>
       </c>
       <c r="P304" s="3" t="n">
@@ -36998,7 +36998,7 @@
       </c>
       <c r="O305" s="3" t="inlineStr">
         <is>
-          <t>169-171</t>
+          <t>168-170</t>
         </is>
       </c>
       <c r="P305" s="3" t="n">
@@ -37079,7 +37079,7 @@
       </c>
       <c r="O306" s="3" t="inlineStr">
         <is>
-          <t>1287-1302</t>
+          <t>1281-1296</t>
         </is>
       </c>
       <c r="P306" s="3" t="n">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="O307" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P307" s="3" t="n">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="O308" s="3" t="inlineStr">
         <is>
-          <t>1335-1356</t>
+          <t>1329-1350</t>
         </is>
       </c>
       <c r="P308" s="3" t="n">
@@ -37330,7 +37330,7 @@
       </c>
       <c r="O309" s="3" t="inlineStr">
         <is>
-          <t>1304-1314</t>
+          <t>1298-1308</t>
         </is>
       </c>
       <c r="P309" s="3" t="n">
@@ -37415,7 +37415,7 @@
       </c>
       <c r="O310" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P310" s="3" t="n">
@@ -37500,7 +37500,7 @@
       </c>
       <c r="O311" s="3" t="inlineStr">
         <is>
-          <t>1287-1302</t>
+          <t>1281-1296</t>
         </is>
       </c>
       <c r="P311" s="3" t="n">
@@ -37585,7 +37585,7 @@
       </c>
       <c r="O312" s="3" t="inlineStr">
         <is>
-          <t>2365-2378</t>
+          <t>2359-2372</t>
         </is>
       </c>
       <c r="P312" s="3" t="n">
@@ -37670,7 +37670,7 @@
       </c>
       <c r="O313" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P313" s="3" t="n">
@@ -37755,7 +37755,7 @@
       </c>
       <c r="O314" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P314" s="3" t="n">
@@ -37844,7 +37844,7 @@
       </c>
       <c r="O315" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P315" s="3" t="n">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="O316" s="3" t="inlineStr">
         <is>
-          <t>2197-2228</t>
+          <t>2191-2222</t>
         </is>
       </c>
       <c r="P316" s="3" t="n">
@@ -38018,7 +38018,7 @@
       </c>
       <c r="O317" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P317" s="3" t="n">
@@ -38107,7 +38107,7 @@
       </c>
       <c r="O318" s="3" t="inlineStr">
         <is>
-          <t>2041-2055</t>
+          <t>2035-2049</t>
         </is>
       </c>
       <c r="P318" s="3" t="n">
@@ -38200,7 +38200,7 @@
       </c>
       <c r="O319" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P319" s="3" t="n">
@@ -38289,7 +38289,7 @@
       </c>
       <c r="O320" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P320" s="3" t="n">
@@ -38378,7 +38378,7 @@
       </c>
       <c r="O321" s="3" t="inlineStr">
         <is>
-          <t>2230-2252</t>
+          <t>2224-2246</t>
         </is>
       </c>
       <c r="P321" s="3" t="n">
@@ -38471,7 +38471,7 @@
       </c>
       <c r="O322" s="3" t="inlineStr">
         <is>
-          <t>384-390</t>
+          <t>378-384</t>
         </is>
       </c>
       <c r="P322" s="3" t="n">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="O323" s="3" t="inlineStr">
         <is>
-          <t>2313-2338</t>
+          <t>2307-2332</t>
         </is>
       </c>
       <c r="P323" s="3" t="n">
@@ -38633,7 +38633,7 @@
       </c>
       <c r="O324" s="3" t="inlineStr">
         <is>
-          <t>353-358</t>
+          <t>347-352</t>
         </is>
       </c>
       <c r="P324" s="3" t="n">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="O325" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P325" s="3" t="n">
@@ -38799,7 +38799,7 @@
       </c>
       <c r="O326" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P326" s="3" t="n">
@@ -38880,7 +38880,7 @@
       </c>
       <c r="O327" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="P327" s="3" t="n">
@@ -38961,7 +38961,7 @@
       </c>
       <c r="O328" s="3" t="inlineStr">
         <is>
-          <t>2197-2228</t>
+          <t>2191-2222</t>
         </is>
       </c>
       <c r="P328" s="3" t="n">
@@ -39042,7 +39042,7 @@
       </c>
       <c r="O329" s="3" t="inlineStr">
         <is>
-          <t>2172-2195</t>
+          <t>2166-2189</t>
         </is>
       </c>
       <c r="P329" s="3" t="n">
@@ -39123,7 +39123,7 @@
       </c>
       <c r="O330" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P330" s="3" t="n">
@@ -39204,7 +39204,7 @@
       </c>
       <c r="O331" s="3" t="inlineStr">
         <is>
-          <t>2041-2055</t>
+          <t>2035-2049</t>
         </is>
       </c>
       <c r="P331" s="3" t="n">
@@ -39289,7 +39289,7 @@
       </c>
       <c r="O332" s="3" t="inlineStr">
         <is>
-          <t>347-351</t>
+          <t>341-345</t>
         </is>
       </c>
       <c r="P332" s="3" t="n">
@@ -39370,7 +39370,7 @@
       </c>
       <c r="O333" s="3" t="inlineStr">
         <is>
-          <t>1737-1790</t>
+          <t>1731-1784</t>
         </is>
       </c>
       <c r="P333" s="3" t="n">
@@ -39455,7 +39455,7 @@
       </c>
       <c r="O334" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P334" s="3" t="n">
@@ -39540,7 +39540,7 @@
       </c>
       <c r="O335" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P335" s="3" t="n">
@@ -39621,7 +39621,7 @@
       </c>
       <c r="O336" s="3" t="inlineStr">
         <is>
-          <t>2098-2170</t>
+          <t>2092-2164</t>
         </is>
       </c>
       <c r="P336" s="3" t="n">
@@ -39702,7 +39702,7 @@
       </c>
       <c r="O337" s="3" t="inlineStr">
         <is>
-          <t>379-382</t>
+          <t>373-376</t>
         </is>
       </c>
       <c r="P337" s="3" t="n">
@@ -39783,7 +39783,7 @@
       </c>
       <c r="O338" s="3" t="inlineStr">
         <is>
-          <t>353-358</t>
+          <t>347-352</t>
         </is>
       </c>
       <c r="P338" s="3" t="n">
@@ -39868,7 +39868,7 @@
       </c>
       <c r="O339" s="3" t="inlineStr">
         <is>
-          <t>368-375</t>
+          <t>362-369</t>
         </is>
       </c>
       <c r="P339" s="3" t="n">
@@ -39953,7 +39953,7 @@
       </c>
       <c r="O340" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P340" s="3" t="n">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="O341" s="3" t="inlineStr">
         <is>
-          <t>2412-2433</t>
+          <t>2406-2427</t>
         </is>
       </c>
       <c r="P341" s="3" t="n">
@@ -40095,7 +40095,7 @@
       </c>
       <c r="O342" s="3" t="inlineStr">
         <is>
-          <t>2403-2409</t>
+          <t>2397-2403</t>
         </is>
       </c>
       <c r="P342" s="3" t="n">
@@ -40172,7 +40172,7 @@
       </c>
       <c r="O343" s="3" t="inlineStr">
         <is>
-          <t>2065-2068</t>
+          <t>2059-2062</t>
         </is>
       </c>
       <c r="P343" s="3" t="n">
@@ -40249,7 +40249,7 @@
       </c>
       <c r="O344" s="3" t="inlineStr">
         <is>
-          <t>169-171</t>
+          <t>168-170</t>
         </is>
       </c>
       <c r="P344" s="3" t="n">
@@ -40322,7 +40322,7 @@
       </c>
       <c r="O345" s="3" t="inlineStr">
         <is>
-          <t>2435-2442</t>
+          <t>2429-2436</t>
         </is>
       </c>
       <c r="P345" s="3" t="n">
@@ -40399,7 +40399,7 @@
       </c>
       <c r="O346" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P346" s="3" t="n">
@@ -40480,7 +40480,7 @@
       </c>
       <c r="O347" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P347" s="3" t="n">
@@ -40549,7 +40549,7 @@
       </c>
       <c r="O348" s="3" t="inlineStr">
         <is>
-          <t>2652-2710</t>
+          <t>2646-2704</t>
         </is>
       </c>
       <c r="P348" s="3" t="n">
@@ -40622,7 +40622,7 @@
       </c>
       <c r="O349" s="3" t="inlineStr">
         <is>
-          <t>92-95</t>
+          <t>91-94</t>
         </is>
       </c>
       <c r="P349" s="3" t="n">
@@ -40695,7 +40695,7 @@
       </c>
       <c r="O350" s="3" t="inlineStr">
         <is>
-          <t>2712-2725</t>
+          <t>2706-2719</t>
         </is>
       </c>
       <c r="P350" s="3" t="n">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="O351" s="3" t="inlineStr">
         <is>
-          <t>495-501</t>
+          <t>489-495</t>
         </is>
       </c>
       <c r="P351" s="3" t="n">
@@ -40849,7 +40849,7 @@
       </c>
       <c r="O352" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P352" s="3" t="n">
@@ -40930,7 +40930,7 @@
       </c>
       <c r="O353" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P353" s="3" t="n">
@@ -41007,7 +41007,7 @@
       </c>
       <c r="O354" s="3" t="inlineStr">
         <is>
-          <t>2065-2068</t>
+          <t>2059-2062</t>
         </is>
       </c>
       <c r="P354" s="3" t="n">
@@ -41084,7 +41084,7 @@
       </c>
       <c r="O355" s="3" t="inlineStr">
         <is>
-          <t>495-501</t>
+          <t>489-495</t>
         </is>
       </c>
       <c r="P355" s="3" t="n">
@@ -41157,7 +41157,7 @@
       </c>
       <c r="O356" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P356" s="3" t="n">
@@ -41234,7 +41234,7 @@
       </c>
       <c r="O357" s="3" t="inlineStr">
         <is>
-          <t>2628-2650</t>
+          <t>2622-2644</t>
         </is>
       </c>
       <c r="P357" s="3" t="n">
@@ -41311,7 +41311,7 @@
       </c>
       <c r="O358" s="3" t="inlineStr">
         <is>
-          <t>179-182</t>
+          <t>178-181</t>
         </is>
       </c>
       <c r="P358" s="3" t="n">
@@ -41388,7 +41388,7 @@
       </c>
       <c r="O359" s="3" t="inlineStr">
         <is>
-          <t>172-174</t>
+          <t>171-173</t>
         </is>
       </c>
       <c r="P359" s="3" t="n">
@@ -41461,7 +41461,7 @@
       </c>
       <c r="O360" s="3" t="inlineStr">
         <is>
-          <t>2286-2296</t>
+          <t>2280-2290</t>
         </is>
       </c>
       <c r="P360" s="3" t="n">
@@ -41538,7 +41538,7 @@
       </c>
       <c r="O361" s="3" t="inlineStr">
         <is>
-          <t>2257-2284</t>
+          <t>2251-2278</t>
         </is>
       </c>
       <c r="P361" s="3" t="n">
@@ -41615,7 +41615,7 @@
       </c>
       <c r="O362" s="3" t="inlineStr">
         <is>
-          <t>2230-2252</t>
+          <t>2224-2246</t>
         </is>
       </c>
       <c r="P362" s="3" t="n">
@@ -41692,7 +41692,7 @@
       </c>
       <c r="O363" s="3" t="inlineStr">
         <is>
-          <t>535-554</t>
+          <t>529-548</t>
         </is>
       </c>
       <c r="P363" s="3" t="n">
@@ -41769,7 +41769,7 @@
       </c>
       <c r="O364" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P364" s="3" t="n">
@@ -41842,7 +41842,7 @@
       </c>
       <c r="O365" s="3" t="inlineStr">
         <is>
-          <t>1358-1375</t>
+          <t>1352-1369</t>
         </is>
       </c>
       <c r="P365" s="3" t="n">
@@ -41915,7 +41915,7 @@
       </c>
       <c r="O366" s="3" t="inlineStr">
         <is>
-          <t>999-1007</t>
+          <t>993-1001</t>
         </is>
       </c>
       <c r="P366" s="3" t="n">
@@ -41984,7 +41984,7 @@
       </c>
       <c r="O367" s="3" t="inlineStr">
         <is>
-          <t>960-997</t>
+          <t>954-991</t>
         </is>
       </c>
       <c r="P367" s="3" t="n">
@@ -42057,7 +42057,7 @@
       </c>
       <c r="O368" s="3" t="inlineStr">
         <is>
-          <t>999-1007</t>
+          <t>993-1001</t>
         </is>
       </c>
       <c r="P368" s="3" t="n">
@@ -42130,7 +42130,7 @@
       </c>
       <c r="O369" s="3" t="inlineStr">
         <is>
-          <t>1144-1153</t>
+          <t>1138-1147</t>
         </is>
       </c>
       <c r="P369" s="3" t="n">
@@ -42203,7 +42203,7 @@
       </c>
       <c r="O370" s="3" t="inlineStr">
         <is>
-          <t>934-940</t>
+          <t>928-934</t>
         </is>
       </c>
       <c r="P370" s="3" t="n">
@@ -42272,7 +42272,7 @@
       </c>
       <c r="O371" s="3" t="inlineStr">
         <is>
-          <t>942-958</t>
+          <t>936-952</t>
         </is>
       </c>
       <c r="P371" s="3" t="n">
@@ -42337,7 +42337,7 @@
       </c>
       <c r="O372" s="3" t="inlineStr">
         <is>
-          <t>2057-2063</t>
+          <t>2051-2057</t>
         </is>
       </c>
       <c r="P372" s="3" t="n">
@@ -42410,7 +42410,7 @@
       </c>
       <c r="O373" s="3" t="inlineStr">
         <is>
-          <t>2065-2068</t>
+          <t>2059-2062</t>
         </is>
       </c>
       <c r="P373" s="3" t="n">
@@ -42483,7 +42483,7 @@
       </c>
       <c r="O374" s="3" t="inlineStr">
         <is>
-          <t>2340-2363</t>
+          <t>2334-2357</t>
         </is>
       </c>
       <c r="P374" s="3" t="n">
@@ -42552,7 +42552,7 @@
       </c>
       <c r="O375" s="3" t="inlineStr">
         <is>
-          <t>1379-1390</t>
+          <t>1373-1384</t>
         </is>
       </c>
       <c r="P375" s="3" t="n">
@@ -42613,7 +42613,7 @@
       </c>
       <c r="O376" s="3" t="inlineStr">
         <is>
-          <t>154-164</t>
+          <t>153-163</t>
         </is>
       </c>
       <c r="P376" s="3" t="n">
@@ -42670,7 +42670,7 @@
       </c>
       <c r="O377" s="3" t="inlineStr">
         <is>
-          <t>2964-2966</t>
+          <t>2958-2960</t>
         </is>
       </c>
       <c r="P377" s="3" t="n">
@@ -42731,7 +42731,7 @@
       </c>
       <c r="O378" s="3" t="inlineStr">
         <is>
-          <t>2880-2962</t>
+          <t>2874-2956</t>
         </is>
       </c>
       <c r="P378" s="3" t="n">
@@ -42792,7 +42792,7 @@
       </c>
       <c r="O379" s="3" t="inlineStr">
         <is>
-          <t>3844-3920</t>
+          <t>3838-3914</t>
         </is>
       </c>
       <c r="P379" s="3" t="n">
@@ -42853,7 +42853,7 @@
       </c>
       <c r="O380" s="3" t="inlineStr">
         <is>
-          <t>148-151</t>
+          <t>147-150</t>
         </is>
       </c>
       <c r="P380" s="3" t="n">
@@ -42914,7 +42914,7 @@
       </c>
       <c r="O381" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P381" s="3" t="n">
@@ -42979,7 +42979,7 @@
       </c>
       <c r="O382" s="3" t="inlineStr">
         <is>
-          <t>785-807</t>
+          <t>779-801</t>
         </is>
       </c>
       <c r="P382" s="3" t="n">
@@ -43044,7 +43044,7 @@
       </c>
       <c r="O383" s="3" t="inlineStr">
         <is>
-          <t>810-867</t>
+          <t>804-861</t>
         </is>
       </c>
       <c r="P383" s="3" t="n">
@@ -43109,7 +43109,7 @@
       </c>
       <c r="O384" s="3" t="inlineStr">
         <is>
-          <t>738-783</t>
+          <t>732-777</t>
         </is>
       </c>
       <c r="P384" s="3" t="n">
@@ -43178,7 +43178,7 @@
       </c>
       <c r="O385" s="3" t="inlineStr">
         <is>
-          <t>611-613</t>
+          <t>605-607</t>
         </is>
       </c>
       <c r="P385" s="3" t="n">
@@ -43239,7 +43239,7 @@
       </c>
       <c r="O386" s="3" t="inlineStr">
         <is>
-          <t>3708-3738</t>
+          <t>3702-3732</t>
         </is>
       </c>
       <c r="P386" s="3" t="n">
@@ -43304,7 +43304,7 @@
       </c>
       <c r="O387" s="3" t="inlineStr">
         <is>
-          <t>3288-3293</t>
+          <t>3282-3287</t>
         </is>
       </c>
       <c r="P387" s="3" t="n">
@@ -43365,7 +43365,7 @@
       </c>
       <c r="O388" s="3" t="inlineStr">
         <is>
-          <t>3359-3384</t>
+          <t>3353-3378</t>
         </is>
       </c>
       <c r="P388" s="3" t="n">
@@ -43434,7 +43434,7 @@
       </c>
       <c r="O389" s="3" t="inlineStr">
         <is>
-          <t>3295-3300</t>
+          <t>3289-3294</t>
         </is>
       </c>
       <c r="P389" s="3" t="n">
@@ -43499,7 +43499,7 @@
       </c>
       <c r="O390" s="3" t="inlineStr">
         <is>
-          <t>3288-3293</t>
+          <t>3282-3287</t>
         </is>
       </c>
       <c r="P390" s="3" t="n">
@@ -43564,7 +43564,7 @@
       </c>
       <c r="O391" s="3" t="inlineStr">
         <is>
-          <t>3282-3286</t>
+          <t>3276-3280</t>
         </is>
       </c>
       <c r="P391" s="3" t="n">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="O392" s="3" t="inlineStr">
         <is>
-          <t>999-1007</t>
+          <t>993-1001</t>
         </is>
       </c>
       <c r="P392" s="3" t="n">
@@ -43686,7 +43686,7 @@
       </c>
       <c r="O393" s="3" t="inlineStr">
         <is>
-          <t>3755-3791</t>
+          <t>3749-3785</t>
         </is>
       </c>
       <c r="P393" s="3" t="n">
@@ -43751,7 +43751,7 @@
       </c>
       <c r="O394" s="3" t="inlineStr">
         <is>
-          <t>3669-3698</t>
+          <t>3663-3692</t>
         </is>
       </c>
       <c r="P394" s="3" t="n">
@@ -43820,7 +43820,7 @@
       </c>
       <c r="O395" s="3" t="inlineStr">
         <is>
-          <t>2978-2979</t>
+          <t>2972-2973</t>
         </is>
       </c>
       <c r="P395" s="3" t="n">
@@ -43889,7 +43889,7 @@
       </c>
       <c r="O396" s="3" t="inlineStr">
         <is>
-          <t>1358-1375</t>
+          <t>1352-1369</t>
         </is>
       </c>
       <c r="P396" s="3" t="n">
@@ -43962,7 +43962,7 @@
       </c>
       <c r="O397" s="3" t="inlineStr">
         <is>
-          <t>3651-3667</t>
+          <t>3645-3661</t>
         </is>
       </c>
       <c r="P397" s="3" t="n">
@@ -44035,7 +44035,7 @@
       </c>
       <c r="O398" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="P398" s="3" t="n">
@@ -44104,7 +44104,7 @@
       </c>
       <c r="O399" s="3" t="inlineStr">
         <is>
-          <t>3643-3649</t>
+          <t>3637-3643</t>
         </is>
       </c>
       <c r="P399" s="3" t="n">
@@ -44173,7 +44173,7 @@
       </c>
       <c r="O400" s="3" t="inlineStr">
         <is>
-          <t>3587-3640</t>
+          <t>3581-3634</t>
         </is>
       </c>
       <c r="P400" s="3" t="n">
@@ -44250,7 +44250,7 @@
       </c>
       <c r="O401" s="3" t="inlineStr">
         <is>
-          <t>3563-3585</t>
+          <t>3557-3579</t>
         </is>
       </c>
       <c r="P401" s="3" t="n">
@@ -44331,7 +44331,7 @@
       </c>
       <c r="O402" s="3" t="inlineStr">
         <is>
-          <t>232-235</t>
+          <t>231-234</t>
         </is>
       </c>
       <c r="P402" s="3" t="n">
@@ -44400,7 +44400,7 @@
       </c>
       <c r="O403" s="3" t="inlineStr">
         <is>
-          <t>3700-3705</t>
+          <t>3694-3699</t>
         </is>
       </c>
       <c r="P403" s="3" t="n">
@@ -44473,7 +44473,7 @@
       </c>
       <c r="O404" s="3" t="inlineStr">
         <is>
-          <t>3651-3667</t>
+          <t>3645-3661</t>
         </is>
       </c>
       <c r="P404" s="3" t="n">
@@ -44546,7 +44546,7 @@
       </c>
       <c r="O405" s="3" t="inlineStr">
         <is>
-          <t>999-1007</t>
+          <t>993-1001</t>
         </is>
       </c>
       <c r="P405" s="3" t="n">
@@ -44615,7 +44615,7 @@
       </c>
       <c r="O406" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="P406" s="3" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="O407" s="3" t="inlineStr">
         <is>
-          <t>3551-3561</t>
+          <t>3545-3555</t>
         </is>
       </c>
       <c r="P407" s="3" t="n">
@@ -44753,7 +44753,7 @@
       </c>
       <c r="O408" s="3" t="inlineStr">
         <is>
-          <t>999-1007</t>
+          <t>993-1001</t>
         </is>
       </c>
       <c r="P408" s="3" t="n">
@@ -44818,7 +44818,7 @@
       </c>
       <c r="O409" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="P409" s="3" t="n">
@@ -44883,7 +44883,7 @@
       </c>
       <c r="O410" s="3" t="inlineStr">
         <is>
-          <t>3743-3748</t>
+          <t>3737-3742</t>
         </is>
       </c>
       <c r="P410" s="3" t="n">
@@ -44944,7 +44944,7 @@
       </c>
       <c r="O411" s="3" t="inlineStr">
         <is>
-          <t>3750-3752</t>
+          <t>3744-3746</t>
         </is>
       </c>
       <c r="P411" s="3" t="n">
@@ -45005,7 +45005,7 @@
       </c>
       <c r="O412" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="P412" s="3" t="n">
@@ -45074,7 +45074,7 @@
       </c>
       <c r="O413" s="3" t="inlineStr">
         <is>
-          <t>3429-3463</t>
+          <t>3423-3457</t>
         </is>
       </c>
       <c r="P413" s="3" t="n">
@@ -45143,7 +45143,7 @@
       </c>
       <c r="O414" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="P414" s="3" t="n">
@@ -45212,7 +45212,7 @@
       </c>
       <c r="O415" s="3" t="inlineStr">
         <is>
-          <t>3181-3185</t>
+          <t>3175-3179</t>
         </is>
       </c>
       <c r="P415" s="3" t="n">
@@ -45285,7 +45285,7 @@
       </c>
       <c r="O416" s="3" t="inlineStr">
         <is>
-          <t>3156-3179</t>
+          <t>3150-3173</t>
         </is>
       </c>
       <c r="P416" s="3" t="n">
@@ -45362,7 +45362,7 @@
       </c>
       <c r="O417" s="3" t="inlineStr">
         <is>
-          <t>3095-3110</t>
+          <t>3089-3104</t>
         </is>
       </c>
       <c r="P417" s="3" t="n">
@@ -45435,7 +45435,7 @@
       </c>
       <c r="O418" s="3" t="inlineStr">
         <is>
-          <t>3112-3115</t>
+          <t>3106-3109</t>
         </is>
       </c>
       <c r="P418" s="3" t="n">
@@ -45508,7 +45508,7 @@
       </c>
       <c r="O419" s="3" t="inlineStr">
         <is>
-          <t>3959-3984</t>
+          <t>3953-3978</t>
         </is>
       </c>
       <c r="P419" s="3" t="n">
@@ -45589,7 +45589,7 @@
       </c>
       <c r="O420" s="3" t="inlineStr">
         <is>
-          <t>5288-5291</t>
+          <t>5277-5280</t>
         </is>
       </c>
       <c r="P420" s="3" t="n">
@@ -45674,7 +45674,7 @@
       </c>
       <c r="O421" s="3" t="inlineStr">
         <is>
-          <t>3986-4008</t>
+          <t>3980-4002</t>
         </is>
       </c>
       <c r="P421" s="3" t="n">
@@ -45759,7 +45759,7 @@
       </c>
       <c r="O422" s="3" t="inlineStr">
         <is>
-          <t>3095-3110</t>
+          <t>3089-3104</t>
         </is>
       </c>
       <c r="P422" s="3" t="n">
@@ -45840,7 +45840,7 @@
       </c>
       <c r="O423" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="P423" s="3" t="n">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="O424" s="3" t="inlineStr">
         <is>
-          <t>3117-3126</t>
+          <t>3111-3120</t>
         </is>
       </c>
       <c r="P424" s="3" t="n">
@@ -46002,7 +46002,7 @@
       </c>
       <c r="O425" s="3" t="inlineStr">
         <is>
-          <t>3192-3275</t>
+          <t>3186-3269</t>
         </is>
       </c>
       <c r="P425" s="3" t="n">
@@ -46087,7 +46087,7 @@
       </c>
       <c r="O426" s="3" t="inlineStr">
         <is>
-          <t>3079-3085</t>
+          <t>3073-3079</t>
         </is>
       </c>
       <c r="P426" s="3" t="n">
@@ -46168,7 +46168,7 @@
       </c>
       <c r="O427" s="3" t="inlineStr">
         <is>
-          <t>3278-3280</t>
+          <t>3272-3274</t>
         </is>
       </c>
       <c r="P427" s="3" t="n">
@@ -46257,7 +46257,7 @@
       </c>
       <c r="O428" s="3" t="inlineStr">
         <is>
-          <t>3079-3085</t>
+          <t>3073-3079</t>
         </is>
       </c>
       <c r="P428" s="3" t="n">
@@ -46326,7 +46326,7 @@
       </c>
       <c r="O429" s="3" t="inlineStr">
         <is>
-          <t>3487-3524</t>
+          <t>3481-3518</t>
         </is>
       </c>
       <c r="P429" s="3" t="n">
@@ -46399,7 +46399,7 @@
       </c>
       <c r="O430" s="3" t="inlineStr">
         <is>
-          <t>3295-3300</t>
+          <t>3289-3294</t>
         </is>
       </c>
       <c r="P430" s="3" t="n">
@@ -46472,7 +46472,7 @@
       </c>
       <c r="O431" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="P431" s="3" t="n">
@@ -46541,7 +46541,7 @@
       </c>
       <c r="O432" s="3" t="inlineStr">
         <is>
-          <t>3465-3483</t>
+          <t>3459-3477</t>
         </is>
       </c>
       <c r="P432" s="3" t="n">
@@ -46606,7 +46606,7 @@
       </c>
       <c r="O433" s="3" t="inlineStr">
         <is>
-          <t>3412-3427</t>
+          <t>3406-3421</t>
         </is>
       </c>
       <c r="P433" s="3" t="n">
@@ -46679,7 +46679,7 @@
       </c>
       <c r="O434" s="3" t="inlineStr">
         <is>
-          <t>3295-3300</t>
+          <t>3289-3294</t>
         </is>
       </c>
       <c r="P434" s="3" t="n">
@@ -46752,7 +46752,7 @@
       </c>
       <c r="O435" s="3" t="inlineStr">
         <is>
-          <t>3288-3293</t>
+          <t>3282-3287</t>
         </is>
       </c>
       <c r="P435" s="3" t="n">
@@ -46825,7 +46825,7 @@
       </c>
       <c r="O436" s="3" t="inlineStr">
         <is>
-          <t>3396-3399</t>
+          <t>3390-3393</t>
         </is>
       </c>
       <c r="P436" s="3" t="n">
@@ -46902,7 +46902,7 @@
       </c>
       <c r="O437" s="3" t="inlineStr">
         <is>
-          <t>3359-3384</t>
+          <t>3353-3378</t>
         </is>
       </c>
       <c r="P437" s="3" t="n">
@@ -46979,7 +46979,7 @@
       </c>
       <c r="O438" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="P438" s="3" t="n">
@@ -47052,7 +47052,7 @@
       </c>
       <c r="O439" s="3" t="inlineStr">
         <is>
-          <t>3402-3410</t>
+          <t>3396-3404</t>
         </is>
       </c>
       <c r="P439" s="3" t="n">
@@ -47129,7 +47129,7 @@
       </c>
       <c r="O440" s="3" t="inlineStr">
         <is>
-          <t>3396-3399</t>
+          <t>3390-3393</t>
         </is>
       </c>
       <c r="P440" s="3" t="n">
@@ -47210,7 +47210,7 @@
       </c>
       <c r="O441" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="P441" s="3" t="n">
@@ -47287,7 +47287,7 @@
       </c>
       <c r="O442" s="3" t="inlineStr">
         <is>
-          <t>3067-3071</t>
+          <t>3061-3065</t>
         </is>
       </c>
       <c r="P442" s="3" t="n">
@@ -47360,7 +47360,7 @@
       </c>
       <c r="O443" s="3" t="inlineStr">
         <is>
-          <t>3310-3334</t>
+          <t>3304-3328</t>
         </is>
       </c>
       <c r="P443" s="3" t="n">
@@ -47429,7 +47429,7 @@
       </c>
       <c r="O444" s="3" t="inlineStr">
         <is>
-          <t>3336-3357</t>
+          <t>3330-3351</t>
         </is>
       </c>
       <c r="P444" s="3" t="n">
@@ -47506,7 +47506,7 @@
       </c>
       <c r="O445" s="3" t="inlineStr">
         <is>
-          <t>3288-3293</t>
+          <t>3282-3287</t>
         </is>
       </c>
       <c r="P445" s="3" t="n">
@@ -47583,7 +47583,7 @@
       </c>
       <c r="O446" s="3" t="inlineStr">
         <is>
-          <t>3302-3308</t>
+          <t>3296-3302</t>
         </is>
       </c>
       <c r="P446" s="3" t="n">
@@ -47664,7 +47664,7 @@
       </c>
       <c r="O447" s="3" t="inlineStr">
         <is>
-          <t>208-230</t>
+          <t>207-229</t>
         </is>
       </c>
       <c r="P447" s="3" t="n">
@@ -47745,7 +47745,7 @@
       </c>
       <c r="O448" s="3" t="inlineStr">
         <is>
-          <t>3282-3286</t>
+          <t>3276-3280</t>
         </is>
       </c>
       <c r="P448" s="3" t="n">
@@ -47814,7 +47814,7 @@
       </c>
       <c r="O449" s="3" t="inlineStr">
         <is>
-          <t>3117-3126</t>
+          <t>3111-3120</t>
         </is>
       </c>
       <c r="P449" s="3" t="n">
@@ -47883,7 +47883,7 @@
       </c>
       <c r="O450" s="3" t="inlineStr">
         <is>
-          <t>3527-3546</t>
+          <t>3521-3540</t>
         </is>
       </c>
       <c r="P450" s="3" t="n">
@@ -47952,7 +47952,7 @@
       </c>
       <c r="O451" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="P451" s="3" t="n">
@@ -48021,7 +48021,7 @@
       </c>
       <c r="O452" s="3" t="inlineStr">
         <is>
-          <t>3429-3463</t>
+          <t>3423-3457</t>
         </is>
       </c>
       <c r="P452" s="3" t="n">
@@ -48086,7 +48086,7 @@
       </c>
       <c r="O453" s="3" t="inlineStr">
         <is>
-          <t>3804-3819</t>
+          <t>3798-3813</t>
         </is>
       </c>
       <c r="P453" s="3" t="n">
@@ -48151,7 +48151,7 @@
       </c>
       <c r="O454" s="3" t="inlineStr">
         <is>
-          <t>107-110</t>
+          <t>106-109</t>
         </is>
       </c>
       <c r="P454" s="3" t="n">
@@ -48212,7 +48212,7 @@
       </c>
       <c r="O455" s="3" t="inlineStr">
         <is>
-          <t>125-131</t>
+          <t>124-130</t>
         </is>
       </c>
       <c r="P455" s="3" t="n">
@@ -48281,7 +48281,7 @@
       </c>
       <c r="O456" s="3" t="inlineStr">
         <is>
-          <t>107-110</t>
+          <t>106-109</t>
         </is>
       </c>
       <c r="P456" s="3" t="n">
@@ -48350,7 +48350,7 @@
       </c>
       <c r="O457" s="3" t="inlineStr">
         <is>
-          <t>113-116</t>
+          <t>112-115</t>
         </is>
       </c>
       <c r="P457" s="3" t="n">
@@ -48415,7 +48415,7 @@
       </c>
       <c r="O458" s="3" t="inlineStr">
         <is>
-          <t>119-121</t>
+          <t>118-120</t>
         </is>
       </c>
       <c r="P458" s="3" t="n">
@@ -48480,7 +48480,7 @@
       </c>
       <c r="O459" s="3" t="inlineStr">
         <is>
-          <t>184-187</t>
+          <t>183-186</t>
         </is>
       </c>
       <c r="P459" s="3" t="n">
@@ -48553,7 +48553,7 @@
       </c>
       <c r="O460" s="3" t="inlineStr">
         <is>
-          <t>5288-5291</t>
+          <t>5277-5280</t>
         </is>
       </c>
       <c r="P460" s="3" t="n">
@@ -48622,7 +48622,7 @@
       </c>
       <c r="O461" s="3" t="inlineStr">
         <is>
-          <t>113-116</t>
+          <t>112-115</t>
         </is>
       </c>
       <c r="P461" s="3" t="n">
@@ -48687,7 +48687,7 @@
       </c>
       <c r="O462" s="3" t="inlineStr">
         <is>
-          <t>119-121</t>
+          <t>118-120</t>
         </is>
       </c>
       <c r="P462" s="3" t="n">
@@ -48752,7 +48752,7 @@
       </c>
       <c r="O463" s="3" t="inlineStr">
         <is>
-          <t>184-187</t>
+          <t>183-186</t>
         </is>
       </c>
       <c r="P463" s="3" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="O464" s="3" t="inlineStr">
         <is>
-          <t>3388-3394</t>
+          <t>3382-3388</t>
         </is>
       </c>
       <c r="P464" s="3" t="n">
@@ -48886,7 +48886,7 @@
       </c>
       <c r="O465" s="3" t="inlineStr">
         <is>
-          <t>5288-5291</t>
+          <t>5277-5280</t>
         </is>
       </c>
       <c r="P465" s="3" t="n">
@@ -48955,7 +48955,7 @@
       </c>
       <c r="O466" s="3" t="inlineStr">
         <is>
-          <t>189-191</t>
+          <t>188-190</t>
         </is>
       </c>
       <c r="P466" s="3" t="n">
@@ -49016,7 +49016,7 @@
       </c>
       <c r="O467" s="3" t="inlineStr">
         <is>
-          <t>3128-3154</t>
+          <t>3122-3148</t>
         </is>
       </c>
       <c r="P467" s="3" t="n">
@@ -49081,7 +49081,7 @@
       </c>
       <c r="O468" s="3" t="inlineStr">
         <is>
-          <t>999-1007</t>
+          <t>993-1001</t>
         </is>
       </c>
       <c r="P468" s="3" t="n">
@@ -49146,7 +49146,7 @@
       </c>
       <c r="O469" s="3" t="inlineStr">
         <is>
-          <t>3095-3110</t>
+          <t>3089-3104</t>
         </is>
       </c>
       <c r="P469" s="3" t="n">
@@ -49211,7 +49211,7 @@
       </c>
       <c r="O470" s="3" t="inlineStr">
         <is>
-          <t>3112-3115</t>
+          <t>3106-3109</t>
         </is>
       </c>
       <c r="P470" s="3" t="n">
@@ -49276,7 +49276,7 @@
       </c>
       <c r="O471" s="3" t="inlineStr">
         <is>
-          <t>3959-3984</t>
+          <t>3953-3978</t>
         </is>
       </c>
       <c r="P471" s="3" t="n">
@@ -49345,7 +49345,7 @@
       </c>
       <c r="O472" s="3" t="inlineStr">
         <is>
-          <t>3181-3185</t>
+          <t>3175-3179</t>
         </is>
       </c>
       <c r="P472" s="3" t="n">
@@ -49414,7 +49414,7 @@
       </c>
       <c r="O473" s="3" t="inlineStr">
         <is>
-          <t>3117-3126</t>
+          <t>3111-3120</t>
         </is>
       </c>
       <c r="P473" s="3" t="n">
@@ -49479,7 +49479,7 @@
       </c>
       <c r="O474" s="3" t="inlineStr">
         <is>
-          <t>2984-2987</t>
+          <t>2978-2981</t>
         </is>
       </c>
       <c r="P474" s="3" t="n">
@@ -49536,7 +49536,7 @@
       </c>
       <c r="O475" s="3" t="inlineStr">
         <is>
-          <t>3750-3752</t>
+          <t>3744-3746</t>
         </is>
       </c>
       <c r="P475" s="3" t="n">
@@ -49597,7 +49597,7 @@
       </c>
       <c r="O476" s="3" t="inlineStr">
         <is>
-          <t>3793-3802</t>
+          <t>3787-3796</t>
         </is>
       </c>
       <c r="P476" s="3" t="n">
@@ -49654,7 +49654,7 @@
       </c>
       <c r="O477" s="3" t="inlineStr">
         <is>
-          <t>3012-3024</t>
+          <t>3006-3018</t>
         </is>
       </c>
       <c r="P477" s="3" t="n">
@@ -49711,7 +49711,7 @@
       </c>
       <c r="O478" s="3" t="inlineStr">
         <is>
-          <t>3821-3841</t>
+          <t>3815-3835</t>
         </is>
       </c>
       <c r="P478" s="3" t="n">
@@ -49768,7 +49768,7 @@
       </c>
       <c r="O479" s="3" t="inlineStr">
         <is>
-          <t>3055-3064</t>
+          <t>3049-3058</t>
         </is>
       </c>
       <c r="P479" s="3" t="n">
@@ -49825,7 +49825,7 @@
       </c>
       <c r="O480" s="3" t="inlineStr">
         <is>
-          <t>1379-1390</t>
+          <t>1373-1384</t>
         </is>
       </c>
       <c r="P480" s="3" t="n">
@@ -49886,7 +49886,7 @@
       </c>
       <c r="O481" s="3" t="inlineStr">
         <is>
-          <t>169-171</t>
+          <t>168-170</t>
         </is>
       </c>
       <c r="P481" s="3" t="n">
@@ -49947,7 +49947,7 @@
       </c>
       <c r="O482" s="3" t="inlineStr">
         <is>
-          <t>3048-3053</t>
+          <t>3042-3047</t>
         </is>
       </c>
       <c r="P482" s="3" t="n">
@@ -50004,7 +50004,7 @@
       </c>
       <c r="O483" s="3" t="inlineStr">
         <is>
-          <t>175-177</t>
+          <t>174-176</t>
         </is>
       </c>
       <c r="P483" s="3" t="n">
@@ -50065,7 +50065,7 @@
       </c>
       <c r="O484" s="3" t="inlineStr">
         <is>
-          <t>154-164</t>
+          <t>153-163</t>
         </is>
       </c>
       <c r="P484" s="3" t="n">
@@ -50126,7 +50126,7 @@
       </c>
       <c r="O485" s="3" t="inlineStr">
         <is>
-          <t>3026-3046</t>
+          <t>3020-3040</t>
         </is>
       </c>
       <c r="P485" s="3" t="n">
@@ -50191,7 +50191,7 @@
       </c>
       <c r="O486" s="3" t="inlineStr">
         <is>
-          <t>2989-3010</t>
+          <t>2983-3004</t>
         </is>
       </c>
       <c r="P486" s="3" t="n">
@@ -50240,7 +50240,7 @@
       </c>
       <c r="O487" s="3" t="inlineStr">
         <is>
-          <t>5413-5415</t>
+          <t>5402-5404</t>
         </is>
       </c>
       <c r="P487" s="3" t="n">
@@ -50297,7 +50297,7 @@
       </c>
       <c r="O488" s="3" t="inlineStr">
         <is>
-          <t>4377-4392</t>
+          <t>4371-4386</t>
         </is>
       </c>
       <c r="P488" s="3" t="n">
@@ -50358,7 +50358,7 @@
       </c>
       <c r="O489" s="3" t="inlineStr">
         <is>
-          <t>4010-4367</t>
+          <t>4004-4361</t>
         </is>
       </c>
       <c r="P489" s="3" t="n">
@@ -50423,7 +50423,7 @@
       </c>
       <c r="O490" s="3" t="inlineStr">
         <is>
-          <t>3079-3085</t>
+          <t>3073-3079</t>
         </is>
       </c>
       <c r="P490" s="3" t="n">
@@ -50488,7 +50488,7 @@
       </c>
       <c r="O491" s="3" t="inlineStr">
         <is>
-          <t>3288-3293</t>
+          <t>3282-3287</t>
         </is>
       </c>
       <c r="P491" s="3" t="n">
@@ -50553,7 +50553,7 @@
       </c>
       <c r="O492" s="3" t="inlineStr">
         <is>
-          <t>1047-1049</t>
+          <t>1041-1043</t>
         </is>
       </c>
       <c r="P492" s="3" t="n">
@@ -50618,7 +50618,7 @@
       </c>
       <c r="O493" s="3" t="inlineStr">
         <is>
-          <t>3986-4008</t>
+          <t>3980-4002</t>
         </is>
       </c>
       <c r="P493" s="3" t="n">
@@ -50687,7 +50687,7 @@
       </c>
       <c r="O494" s="3" t="inlineStr">
         <is>
-          <t>3959-3984</t>
+          <t>3953-3978</t>
         </is>
       </c>
       <c r="P494" s="3" t="n">
@@ -50756,7 +50756,7 @@
       </c>
       <c r="O495" s="3" t="inlineStr">
         <is>
-          <t>3181-3185</t>
+          <t>3175-3179</t>
         </is>
       </c>
       <c r="P495" s="3" t="n">
@@ -50825,7 +50825,7 @@
       </c>
       <c r="O496" s="3" t="inlineStr">
         <is>
-          <t>3156-3179</t>
+          <t>3150-3173</t>
         </is>
       </c>
       <c r="P496" s="3" t="n">
@@ -50894,7 +50894,7 @@
       </c>
       <c r="O497" s="3" t="inlineStr">
         <is>
-          <t>4370-4375</t>
+          <t>4364-4369</t>
         </is>
       </c>
       <c r="P497" s="3" t="n">
@@ -50951,7 +50951,7 @@
       </c>
       <c r="O498" s="3" t="inlineStr">
         <is>
-          <t>148-151</t>
+          <t>147-150</t>
         </is>
       </c>
       <c r="P498" s="3" t="n">
@@ -51012,7 +51012,7 @@
       </c>
       <c r="O499" s="3" t="inlineStr">
         <is>
-          <t>3959-3984</t>
+          <t>3953-3978</t>
         </is>
       </c>
       <c r="P499" s="3" t="n">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="O500" s="3" t="inlineStr">
         <is>
-          <t>5269-5285</t>
+          <t>5258-5274</t>
         </is>
       </c>
       <c r="P500" s="3" t="n">
@@ -51126,7 +51126,7 @@
       </c>
       <c r="O501" s="3" t="inlineStr">
         <is>
-          <t>4797-4814</t>
+          <t>4788-4805</t>
         </is>
       </c>
       <c r="P501" s="3" t="n">
@@ -51183,7 +51183,7 @@
       </c>
       <c r="O502" s="3" t="inlineStr">
         <is>
-          <t>5473-5515</t>
+          <t>5462-5504</t>
         </is>
       </c>
       <c r="P502" s="3" t="n">
@@ -51240,7 +51240,7 @@
       </c>
       <c r="O503" s="3" t="inlineStr">
         <is>
-          <t>5439-5453</t>
+          <t>5428-5442</t>
         </is>
       </c>
       <c r="P503" s="3" t="n">
@@ -51293,7 +51293,7 @@
       </c>
       <c r="O504" s="3" t="inlineStr">
         <is>
-          <t>3959-3984</t>
+          <t>3953-3978</t>
         </is>
       </c>
       <c r="P504" s="3" t="n">
@@ -51354,7 +51354,7 @@
       </c>
       <c r="O505" s="3" t="inlineStr">
         <is>
-          <t>5528-5570</t>
+          <t>5517-5559</t>
         </is>
       </c>
       <c r="P505" s="3" t="n">
@@ -51415,7 +51415,7 @@
       </c>
       <c r="O506" s="3" t="inlineStr">
         <is>
-          <t>5517-5526</t>
+          <t>5506-5515</t>
         </is>
       </c>
       <c r="P506" s="3" t="n">
@@ -51468,7 +51468,7 @@
       </c>
       <c r="O507" s="3" t="inlineStr">
         <is>
-          <t>5455-5464</t>
+          <t>5444-5453</t>
         </is>
       </c>
       <c r="P507" s="3" t="n">
@@ -51529,7 +51529,7 @@
       </c>
       <c r="O508" s="3" t="inlineStr">
         <is>
-          <t>4599-4631</t>
+          <t>4593-4625</t>
         </is>
       </c>
       <c r="P508" s="3" t="n">
@@ -51594,7 +51594,7 @@
       </c>
       <c r="O509" s="3" t="inlineStr">
         <is>
-          <t>5455-5464</t>
+          <t>5444-5453</t>
         </is>
       </c>
       <c r="P509" s="3" t="n">
@@ -51655,7 +51655,7 @@
       </c>
       <c r="O510" s="3" t="inlineStr">
         <is>
-          <t>5466-5471</t>
+          <t>5455-5460</t>
         </is>
       </c>
       <c r="P510" s="3" t="n">
@@ -51708,7 +51708,7 @@
       </c>
       <c r="O511" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="P511" s="3" t="n">
@@ -51765,7 +51765,7 @@
       </c>
       <c r="O512" s="3" t="inlineStr">
         <is>
-          <t>5575-5596</t>
+          <t>5564-5585</t>
         </is>
       </c>
       <c r="P512" s="3" t="n">
@@ -51822,7 +51822,7 @@
       </c>
       <c r="O513" s="3" t="inlineStr">
         <is>
-          <t>4519-4536</t>
+          <t>4513-4530</t>
         </is>
       </c>
       <c r="P513" s="3" t="n">
@@ -51879,7 +51879,7 @@
       </c>
       <c r="O514" s="3" t="inlineStr">
         <is>
-          <t>5613-5634</t>
+          <t>5602-5623</t>
         </is>
       </c>
       <c r="P514" s="3" t="n">
@@ -51936,7 +51936,7 @@
       </c>
       <c r="O515" s="3" t="inlineStr">
         <is>
-          <t>5636-5646</t>
+          <t>5625-5635</t>
         </is>
       </c>
       <c r="P515" s="3" t="n">
@@ -51993,7 +51993,7 @@
       </c>
       <c r="O516" s="3" t="inlineStr">
         <is>
-          <t>4599-4631</t>
+          <t>4593-4625</t>
         </is>
       </c>
       <c r="P516" s="3" t="n">
@@ -52054,7 +52054,7 @@
       </c>
       <c r="O517" s="3" t="inlineStr">
         <is>
-          <t>5455-5464</t>
+          <t>5444-5453</t>
         </is>
       </c>
       <c r="P517" s="3" t="n">
@@ -52115,7 +52115,7 @@
       </c>
       <c r="O518" s="3" t="inlineStr">
         <is>
-          <t>5572-5573</t>
+          <t>5561-5562</t>
         </is>
       </c>
       <c r="P518" s="3" t="n">
@@ -52176,7 +52176,7 @@
       </c>
       <c r="O519" s="3" t="inlineStr">
         <is>
-          <t>5346-5388</t>
+          <t>5335-5377</t>
         </is>
       </c>
       <c r="P519" s="3" t="n">
@@ -52237,11 +52237,11 @@
       </c>
       <c r="O520" s="3" t="inlineStr">
         <is>
-          <t>4651-4757</t>
+          <t>4645-4750</t>
         </is>
       </c>
       <c r="P520" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q520" s="3" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
       </c>
       <c r="O521" s="3" t="inlineStr">
         <is>
-          <t>142-145</t>
+          <t>141-144</t>
         </is>
       </c>
       <c r="P521" s="3" t="n">
@@ -52367,7 +52367,7 @@
       </c>
       <c r="O522" s="3" t="inlineStr">
         <is>
-          <t>184-187</t>
+          <t>183-186</t>
         </is>
       </c>
       <c r="P522" s="3" t="n">
@@ -52432,7 +52432,7 @@
       </c>
       <c r="O523" s="3" t="inlineStr">
         <is>
-          <t>5327-5344</t>
+          <t>5316-5333</t>
         </is>
       </c>
       <c r="P523" s="3" t="n">
@@ -52489,7 +52489,7 @@
       </c>
       <c r="O524" s="3" t="inlineStr">
         <is>
-          <t>4876-4885</t>
+          <t>4867-4876</t>
         </is>
       </c>
       <c r="P524" s="3" t="n">
@@ -52554,7 +52554,7 @@
       </c>
       <c r="O525" s="3" t="inlineStr">
         <is>
-          <t>5288-5291</t>
+          <t>5277-5280</t>
         </is>
       </c>
       <c r="P525" s="3" t="n">
@@ -52619,7 +52619,7 @@
       </c>
       <c r="O526" s="3" t="inlineStr">
         <is>
-          <t>1400-1411</t>
+          <t>1394-1405</t>
         </is>
       </c>
       <c r="P526" s="3" t="n">
@@ -52684,7 +52684,7 @@
       </c>
       <c r="O527" s="3" t="inlineStr">
         <is>
-          <t>5455-5464</t>
+          <t>5444-5453</t>
         </is>
       </c>
       <c r="P527" s="3" t="n">
@@ -52749,7 +52749,7 @@
       </c>
       <c r="O528" s="3" t="inlineStr">
         <is>
-          <t>2968-2970</t>
+          <t>2962-2964</t>
         </is>
       </c>
       <c r="P528" s="3" t="n">
@@ -52814,7 +52814,7 @@
       </c>
       <c r="O529" s="3" t="inlineStr">
         <is>
-          <t>2964-2966</t>
+          <t>2958-2960</t>
         </is>
       </c>
       <c r="P529" s="3" t="n">
@@ -52879,7 +52879,7 @@
       </c>
       <c r="O530" s="3" t="inlineStr">
         <is>
-          <t>3844-3920</t>
+          <t>3838-3914</t>
         </is>
       </c>
       <c r="P530" s="3" t="n">
@@ -52944,11 +52944,11 @@
       </c>
       <c r="O531" s="3" t="inlineStr">
         <is>
-          <t>4956-4959</t>
+          <t>4947-4949</t>
         </is>
       </c>
       <c r="P531" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q531" s="3" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
       </c>
       <c r="O532" s="3" t="inlineStr">
         <is>
-          <t>154-164</t>
+          <t>153-163</t>
         </is>
       </c>
       <c r="P532" s="3" t="n">
@@ -53058,7 +53058,7 @@
       </c>
       <c r="O533" s="3" t="inlineStr">
         <is>
-          <t>5455-5464</t>
+          <t>5444-5453</t>
         </is>
       </c>
       <c r="P533" s="3" t="n">
@@ -53626,7 +53626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -53673,7 +53673,7 @@
         <v>56</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -53687,7 +53687,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>26</v>
@@ -53708,7 +53708,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>68</v>
@@ -53729,7 +53729,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>42</v>
@@ -53750,7 +53750,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>73</v>
@@ -53771,7 +53771,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>32</v>
@@ -53792,10 +53792,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>2</v>
@@ -53809,94 +53809,94 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>the prompts</t>
+          <t>element helpers</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>attribute; child_named; local_name</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>element helpers</t>
+          <t>baseline slicing: what a document's shape says</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>attribute; child_named; local_name</t>
+          <t>attribute_text; discover_families; discover_table_shape; first_numbering; infer_levels; table_rows; without_page_furniture; written_numbering</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>baseline slicing: what a document's shape says</t>
+          <t>the fidelity ledger</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>367</v>
+        <v>550</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>189</v>
+        <v>314</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>attribute_text; discover_families; discover_table_shape; first_numbering; infer_levels; table_rows; without_page_furniture; written_numbering</t>
+          <t>account; account_lines; account_of_package; atom; atoms_of_docx; atoms_of_markup; atoms_of_pdf; atoms_of_plain_text; bag; bag_of; kept_and_relocated; marks_of_rendering; minus; tokens</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>the fidelity ledger</t>
+          <t>the shape digest and the rules it asks for</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>556</v>
+        <v>864</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>314</v>
+        <v>25</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>account; account_lines; account_of_package; atom; atoms_of_docx; atoms_of_markup; atoms_of_pdf; atoms_of_plain_text; bag; bag_of; kept_and_relocated; marks_of_rendering; minus; tokens</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>the shape digest and the rules it asks for</t>
+          <t>asking how to read a package</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
@@ -53906,14 +53906,14 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>asking how to read a package</t>
+          <t>the reading floor</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -53923,11 +53923,11 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>the reading floor</t>
+          <t>the front door: what a file is, and how it becomes markup</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
@@ -53940,607 +53940,607 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>the front door: what a file is, and how it becomes markup</t>
+          <t>what a file is</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>decode_text; detect_format; looks_binary; sniff_zip</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>what a file is</t>
+          <t>which files of a folder are documents</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>909</v>
+        <v>1003</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>decode_text; detect_format; looks_binary; sniff_zip</t>
+          <t>input_files</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>which files of a folder are documents</t>
+          <t>formats the tool reads by converting them</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1009</v>
+        <v>1034</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>31</v>
+        <v>352</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>input_files</t>
+          <t>converted; delimited_rows; delimited_to_markup; delimited_words; delimiter_of; element; latex_body; latex_to_markup; latex_words; markdown_inline; markdown_to_markup; markdown_words; reason_for; rtf_to_text; spreadsheet_to_markup; svg_embedded_pictures; svg_rows; svg_texts; svg_to_markup; svg_why_no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>formats the tool reads by converting them</t>
+          <t>the three Inputs folders of a project</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1040</v>
+        <v>1386</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>352</v>
+        <v>25</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>converted; delimited_rows; delimited_to_markup; delimited_words; delimiter_of; element; latex_body; latex_to_markup; latex_words; markdown_inline; markdown_to_markup; markdown_words; reason_for; rtf_to_text; spreadsheet_to_markup; svg_embedded_pictures; svg_rows; svg_texts; svg_to_markup; svg_why_no</t>
+          <t>list_input_files</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>the three Inputs folders of a project</t>
+          <t>the methodology and the documentation, read into units</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1392</v>
+        <v>1411</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>list_input_files</t>
+          <t>NotReadable</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>the methodology and the documentation, read into units</t>
+          <t>the linear-notation parser</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>NotReadable</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>the linear-notation parser</t>
+          <t>reference data of the reader</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9</v>
+        <v>294</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>FormulaReader; inline_formula; load_notation; parse_formula; read_equation; tokenize_formula</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>reference data of the reader</t>
+          <t>equation markup -&gt; linear notation</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1430</v>
+        <v>1718</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>294</v>
+        <v>149</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>FormulaReader; inline_formula; load_notation; parse_formula; read_equation; tokenize_formula</t>
+          <t>bracketed; latex_group; latex_to_linear; math_children; math_to_linear; strip_outer_brackets</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>equation markup -&gt; linear notation</t>
+          <t>format from content, and repairs</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1724</v>
+        <v>1867</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>bracketed; latex_group; latex_to_linear; math_children; math_to_linear; strip_outer_brackets</t>
+          <t>TolerantReader; parse_markup; repair_markup</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>format from content, and repairs</t>
+          <t>tag rules and the block walker</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1873</v>
+        <v>2007</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>TolerantReader; parse_markup; repair_markup</t>
+          <t>load_tag_rules</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>tag rules and the block walker</t>
+          <t>discovering an unfamiliar schema</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2013</v>
+        <v>2032</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>25</v>
+        <v>373</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>load_tag_rules</t>
+          <t>WalkState; blocks_from_markup; element_text; equation_block; figure_block; new_block; not_read_block; picture_words; read_picture; svg_blocks; svg_reference; table_block; table_from_rows; walk_element; walk_mixed; walk_svg_markup</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>discovering an unfamiliar schema</t>
+          <t>MHTML (a web page saved as one file)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2038</v>
+        <v>2405</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>373</v>
+        <v>33</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>WalkState; blocks_from_markup; element_text; equation_block; figure_block; new_block; not_read_block; picture_words; read_picture; svg_blocks; svg_reference; table_block; table_from_rows; walk_element; walk_mixed; walk_svg_markup</t>
+          <t>blocks_from_mhtml; title_block</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MHTML (a web page saved as one file)</t>
+          <t>.docx</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2411</v>
+        <v>2438</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>33</v>
+        <v>179</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>blocks_from_mhtml; title_block</t>
+          <t>blocks_from_docx; docx_figure; docx_number_formats; docx_paragraph_facts; docx_paragraph_parts; note_blocks; safe_xml; word_value</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>.docx</t>
+          <t>.pdf</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2444</v>
+        <v>2617</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>blocks_from_docx; docx_figure; docx_number_formats; docx_paragraph_facts; docx_paragraph_parts; note_blocks; safe_xml; word_value</t>
+          <t>blocks_from_pdf; blocks_from_pdf_text_only; pdf_lines</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>.pdf</t>
+          <t>levels, references, chunks</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2623</v>
+        <v>2721</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>blocks_from_pdf; blocks_from_pdf_text_only; pdf_lines</t>
+          <t>block_is_under_reconstructed; blocks_to_chunks; fold_lists</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>levels, references, chunks</t>
+          <t>the two steps</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>2727</v>
+        <v>2814</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>block_is_under_reconstructed; blocks_to_chunks; fold_lists</t>
+          <t>atoms_of_file; read_corner; read_documentation; read_file_blocks; read_methodology</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>the two steps</t>
+          <t>the model package, read into units</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>2820</v>
+        <v>2968</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>154</v>
+        <v>7</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>atoms_of_file; read_corner; read_documentation; read_file_blocks; read_methodology</t>
+          <t>NotParsed</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>the model package, read into units</t>
+          <t>safe unpacking and inventory</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="C33" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="D33" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>NotParsed</t>
+          <t>is_archive; is_exported; loose_package; read_description; strip_top_folder; unpack_package; unpack_zip</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>safe unpacking and inventory</t>
+          <t>the R tokenizer</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>2981</v>
+        <v>3067</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>is_archive; is_exported; loose_package; read_description; strip_top_folder; unpack_package; unpack_zip</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>the R tokenizer</t>
+          <t>the R parser</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Node</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>the R parser</t>
+          <t>R code, read by flowR</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3077</v>
+        <v>3084</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>13</v>
+        <v>297</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Node</t>
+          <t>assignment_parts; callee_name; code_facts; flowr_answer; flowr_files; flowr_node; flowr_package; has_arithmetic; namespaced; number_token; parse_r_source; parse_r_sources; top_level; unparse; walk</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>R code, read by flowR</t>
+          <t>units from R source</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>3090</v>
+        <v>3381</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>297</v>
+        <v>98</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>assignment_parts; callee_name; code_facts; flowr_answer; flowr_files; flowr_node; flowr_package; has_arithmetic; namespaced; number_token; parse_r_source; parse_r_sources; top_level; unparse; walk</t>
+          <t>code_detail; draft; function_units; self_contained; statement_units; units_from_r_source</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>units from R source</t>
+          <t>roxygen blocks and help pages</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>3387</v>
+        <v>3479</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>code_detail; draft; function_units; self_contained; statement_units; units_from_r_source</t>
+          <t>roxygen_units; vignette_units</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>roxygen blocks and help pages</t>
+          <t>stored parameter data</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>3485</v>
+        <v>3542</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>roxygen_units; vignette_units</t>
+          <t>cell_text; data_object_unit; data_object_unit_from_rows; decode_data_file; expand; table_display; table_of</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>stored parameter data</t>
+          <t>which code reads which data</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>3548</v>
+        <v>3701</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>cell_text; data_object_unit; data_object_unit_from_rows; decode_data_file; expand; table_display; table_of</t>
+          <t>data_reads</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>which code reads which data</t>
+          <t>step 04: read-package</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>3707</v>
+        <v>3734</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>33</v>
+        <v>182</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>data_reads</t>
+          <t>file_units; finalise_units; is_data_file; is_parsed_r_file; link_documentation_units; package_rows; read_package</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>step 04: read-package</t>
+          <t>the data flow of a package: the implementation map's backbone</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>3740</v>
+        <v>3916</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>182</v>
+        <v>23</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>file_units; finalise_units; is_data_file; is_parsed_r_file; link_documentation_units; package_rows; read_package</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>the data flow of a package: the implementation map's backbone</t>
+          <t>flowR: the program the data flow is read with</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>3922</v>
+        <v>3939</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>23</v>
+        <v>484</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Dataflow; decided_outputs; flowr_read; flowr_ready; trace_dataflow; walk_nodes</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>flowR: the program the data flow is read with</t>
+          <t>the graph and the map</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>3945</v>
+        <v>4423</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>484</v>
+        <v>2</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Dataflow; decided_outputs; flowr_read; flowr_ready; trace_dataflow; walk_nodes</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>the graph and the map</t>
+          <t>the ledger and the graph in memory</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>4429</v>
+        <v>4425</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0</v>
@@ -54550,14 +54550,14 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>the ledger and the graph in memory</t>
+          <t>words: splitting, stemming, word lists</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
         <v>4431</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>0</v>
@@ -54567,14 +54567,14 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>words: splitting, stemming, word lists</t>
+          <t>S3: explicit references as written</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>4437</v>
+        <v>4439</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>0</v>
@@ -54584,14 +54584,14 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>S3: explicit references as written</t>
+          <t>the skill map-implementation: the implementation map's agents</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4445</v>
+        <v>4442</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -54601,14 +54601,14 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>the skill map-implementation: the implementation map's agents</t>
+          <t>step 05: build-graph</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>4448</v>
+        <v>4451</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>0</v>
@@ -54618,11 +54618,11 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>step 05: build-graph</t>
+          <t>what each piece of code does, in plain words</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>4457</v>
+        <v>4455</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>4</v>
@@ -54635,308 +54635,291 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>what each piece of code does, in plain words</t>
+          <t>a fault inside the tool</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>4461</v>
+        <v>4459</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>EngineFault</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>a fault inside the tool</t>
+          <t>the run: its folder, its record and its two deliverables</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>4465</v>
+        <v>4464</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>EngineFault</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>the run: its folder, its record and its two deliverables</t>
+          <t>settings (allow-list)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>4470</v>
+        <v>4468</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>make_settings</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>settings (allow-list)</t>
+          <t>paths and project setup</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>4474</v>
+        <v>4492</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>make_settings</t>
+          <t>RunPaths; check_model_id; new_run_id; open_run; pick_scratch_root; setup_project</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>paths and project setup</t>
+          <t>live values (the token)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>4498</v>
+        <v>4591</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>RunPaths; check_model_id; new_run_id; open_run; pick_scratch_root; setup_project</t>
+          <t>LiveValues</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>live values (the token)</t>
+          <t>the audit store</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>4597</v>
+        <v>4627</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>LiveValues</t>
+          <t>AuditStore; copy_whole; open_store; parts_of</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>the audit store</t>
+          <t>the wrapper around chat()</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>4633</v>
+        <v>4766</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>140</v>
+        <v>8</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>AuditStore; copy_whole; open_store; parts_of</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>the wrapper around chat()</t>
+          <t>the pipeline runner</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>4773</v>
+        <v>4774</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>log_line; record_step; run_pipeline; run_step; step_failure; update_manifest</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>the pipeline runner</t>
+          <t>step 01: prepare-run</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>4781</v>
+        <v>4856</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>log_line; record_step; run_pipeline; run_step; step_failure; update_manifest</t>
+          <t>engine_file_hashes; fingerprint_file; prepare_run; previous_run_inputs</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>step 01: prepare-run</t>
+          <t>Output.xlsx</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>4865</v>
+        <v>4919</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>63</v>
+        <v>234</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>engine_file_hashes; fingerprint_file; prepare_run; previous_run_inputs</t>
+          <t>blank_row; check_written_totals; implementation_map; plain_cell; rows_chunks; rows_model_units; rows_package_info; run_identity; sheet_rows</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Output.xlsx</t>
+          <t>the workbook layout</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>4928</v>
+        <v>5153</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>236</v>
+        <v>123</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>blank_row; check_written_totals; implementation_map; plain_cell; rows_chunks; rows_model_units; rows_package_info; run_identity; sheet_rows</t>
+          <t>build_workbook; load_layout; write_sheet</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>the workbook layout</t>
+          <t>rebuilding the outputs</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>5164</v>
+        <v>5276</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>build_workbook; load_layout; write_sheet</t>
+          <t>file_sha256; progress_text; rebuild_outputs</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>rebuilding the outputs</t>
+          <t>determinations</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>5287</v>
+        <v>5315</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>file_sha256; progress_text; rebuild_outputs</t>
+          <t>build_map; combine; contents_of; read_inputs; verify_evidence_pack</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>determinations</t>
+          <t>the notebook: four cells, each one call</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>5326</v>
+        <v>5416</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>101</v>
+        <v>221</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>build_map; combine; contents_of; read_inputs; verify_evidence_pack</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>the notebook: four cells, each one call</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>5427</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
           <t>check_chat; databricks_user; install; live; notebook_folder; notebook_settings; open_current; pip_said; review; setup; verify</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E65"/>
+  <autoFilter ref="A1:E64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
